--- a/downloads/勞動基金月度揭露_可持續更新.xlsx
+++ b/downloads/勞動基金月度揭露_可持續更新.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="177">
   <si>
     <t>勞動基金運用局｜四大基金月度儀表板</t>
   </si>
@@ -22,7 +22,7 @@
     <t>資料期間</t>
   </si>
   <si>
-    <t>202606</t>
+    <t>202607</t>
   </si>
   <si>
     <t>基金</t>
@@ -319,7 +319,7 @@
     <t>道富</t>
   </si>
   <si>
-    <t>100-1全球基本面指數被動股票型（續約2）</t>
+    <t>100-1全球基本面指數被動股票型（續約3）</t>
   </si>
   <si>
     <t>100-1全球不動產有價證券型（續約2）</t>
@@ -364,159 +364,159 @@
     <t>北美信託</t>
   </si>
   <si>
+    <t>L&amp;G</t>
+  </si>
+  <si>
+    <t>Geode</t>
+  </si>
+  <si>
+    <t>104-2全球基礎建設有價證券型（續約2）</t>
+  </si>
+  <si>
+    <t>Magellan</t>
+  </si>
+  <si>
+    <t>RREEF</t>
+  </si>
+  <si>
+    <t>105-1亞太混合指數增值股票型(續約)</t>
+  </si>
+  <si>
+    <t>106-1全球ESG混合指數被動股票型(續約)</t>
+  </si>
+  <si>
+    <t>DWS</t>
+  </si>
+  <si>
+    <t>106-1絕對報酬債券型(續約)</t>
+  </si>
+  <si>
+    <t>American Century</t>
+  </si>
+  <si>
+    <t>富達</t>
+  </si>
+  <si>
+    <t>TCW</t>
+  </si>
+  <si>
+    <t>107-1絕對報酬股票型（續約）</t>
+  </si>
+  <si>
+    <t>CPR</t>
+  </si>
+  <si>
+    <t>Nomura</t>
+  </si>
+  <si>
+    <t>荷寶</t>
+  </si>
+  <si>
+    <t>109-1全球美元公司增值債券型(續約)</t>
+  </si>
+  <si>
+    <t>Insight</t>
+  </si>
+  <si>
+    <t>110-1全球基礎建設有價證券型</t>
+  </si>
+  <si>
+    <t>CBRE</t>
+  </si>
+  <si>
+    <t>Clearbridge</t>
+  </si>
+  <si>
+    <t>110-1全球多元資產型</t>
+  </si>
+  <si>
+    <t>Ninety One</t>
+  </si>
+  <si>
+    <t>Schroders</t>
+  </si>
+  <si>
+    <t>T. Rowe Price</t>
+  </si>
+  <si>
+    <t>111-1全球氣候變遷增值股票型</t>
+  </si>
+  <si>
     <t>LGIM</t>
   </si>
   <si>
-    <t>Geode</t>
-  </si>
-  <si>
-    <t>104-2全球基礎建設有價證券型（續約）</t>
-  </si>
-  <si>
-    <t>Magellan</t>
-  </si>
-  <si>
-    <t>RREEF</t>
-  </si>
-  <si>
-    <t>105-1全球多元資產型(續約)</t>
+    <t>摩根士丹利</t>
+  </si>
+  <si>
+    <t>111-2絕對報酬債券型</t>
+  </si>
+  <si>
+    <t>PGIM</t>
+  </si>
+  <si>
+    <t>112-1全球被動股票型</t>
+  </si>
+  <si>
+    <t>Amundi</t>
+  </si>
+  <si>
+    <t>113-1全球永續不動產有價證券型</t>
+  </si>
+  <si>
+    <t>Center Square</t>
+  </si>
+  <si>
+    <t>114-1全球氣候轉型被動股票型</t>
+  </si>
+  <si>
+    <t>HSBC</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>96國際平衡型(續約4)</t>
+  </si>
+  <si>
+    <t>97-1全球增值債券型(續約3)</t>
+  </si>
+  <si>
+    <t>97-1全球增值股票型(續約3)</t>
+  </si>
+  <si>
+    <t>98-1亞太(日本除外)主動股票型(續約3)</t>
+  </si>
+  <si>
+    <t>100-1全球基本面指數被動股票型(續約3)</t>
+  </si>
+  <si>
+    <t>瑞銀</t>
+  </si>
+  <si>
+    <t>101-1全球低波動指數被動股票型(續約2)</t>
+  </si>
+  <si>
+    <t>102-1年全球高股利增值股票型(續約2)</t>
+  </si>
+  <si>
+    <t>102-2全球基礎建設有價證券型(續約2)</t>
+  </si>
+  <si>
+    <t>Lazard</t>
+  </si>
+  <si>
+    <t>102-2全球不動產有價證券型(續約2)</t>
+  </si>
+  <si>
+    <t>信安</t>
+  </si>
+  <si>
+    <t>105-1全球多元資產型(續約2)</t>
   </si>
   <si>
     <t>Allianz</t>
   </si>
   <si>
-    <t>DWS</t>
-  </si>
-  <si>
-    <t>柏瑞</t>
-  </si>
-  <si>
-    <t>105-1亞太混合指數增值股票型(續約)</t>
-  </si>
-  <si>
-    <t>106-1全球ESG混合指數被動股票型(續約)</t>
-  </si>
-  <si>
-    <t>106-1絕對報酬債券型(續約)</t>
-  </si>
-  <si>
-    <t>American Century</t>
-  </si>
-  <si>
-    <t>富達</t>
-  </si>
-  <si>
-    <t>TCW</t>
-  </si>
-  <si>
-    <t>107-1絕對報酬股票型（續約）</t>
-  </si>
-  <si>
-    <t>CPR</t>
-  </si>
-  <si>
-    <t>Nomura</t>
-  </si>
-  <si>
-    <t>荷寶</t>
-  </si>
-  <si>
-    <t>109-1全球美元公司增值債券型（續約）</t>
-  </si>
-  <si>
-    <t>Insight</t>
-  </si>
-  <si>
-    <t>110-1全球基礎建設有價證券型</t>
-  </si>
-  <si>
-    <t>CBRE</t>
-  </si>
-  <si>
-    <t>Clearbridge</t>
-  </si>
-  <si>
-    <t>110-1全球多元資產型</t>
-  </si>
-  <si>
-    <t>Ninety One</t>
-  </si>
-  <si>
-    <t>Schroders</t>
-  </si>
-  <si>
-    <t>T. Rowe Price</t>
-  </si>
-  <si>
-    <t>111-1全球氣候變遷增值股票型</t>
-  </si>
-  <si>
-    <t>摩根士丹利</t>
-  </si>
-  <si>
-    <t>111-2絕對報酬債券型</t>
-  </si>
-  <si>
-    <t>PGIM</t>
-  </si>
-  <si>
-    <t>112-1全球被動股票型</t>
-  </si>
-  <si>
-    <t>Amundi</t>
-  </si>
-  <si>
-    <t>113-1全球永續不動產有價證券型</t>
-  </si>
-  <si>
-    <t>Center Square</t>
-  </si>
-  <si>
-    <t>114-1全球氣候轉型被動股票型</t>
-  </si>
-  <si>
-    <t>HSBC</t>
-  </si>
-  <si>
-    <t>UBS</t>
-  </si>
-  <si>
-    <t>96國際平衡型(續約4)</t>
-  </si>
-  <si>
-    <t>97-1全球增值債券型(續約3)</t>
-  </si>
-  <si>
-    <t>97-1全球增值股票型(續約3)</t>
-  </si>
-  <si>
-    <t>98-1亞太(日本除外)主動股票型(續約3)</t>
-  </si>
-  <si>
-    <t>100-1全球基本面指數被動股票型(續約2)</t>
-  </si>
-  <si>
-    <t>瑞銀</t>
-  </si>
-  <si>
-    <t>101-1全球低波動指數被動股票型(續約2)</t>
-  </si>
-  <si>
-    <t>102-1年全球高股利增值股票型(續約2)</t>
-  </si>
-  <si>
-    <t>102-2全球基礎建設有價證券型(續約2)</t>
-  </si>
-  <si>
-    <t>Lazard</t>
-  </si>
-  <si>
-    <t>102-2全球不動產有價證券型(續約2)</t>
-  </si>
-  <si>
-    <t>信安</t>
-  </si>
-  <si>
     <t>107-1絕對報酬股票型(續約)</t>
   </si>
   <si>
@@ -535,9 +535,6 @@
     <t>104-1全球高品質被動股票型(續約2)</t>
   </si>
   <si>
-    <t>L&amp;G</t>
-  </si>
-  <si>
     <t>104-2全球基礎建設有價證券型(續約2)</t>
   </si>
   <si>
@@ -545,12 +542,6 @@
   </si>
   <si>
     <t>信安環球</t>
-  </si>
-  <si>
-    <t>104-1全球主權信用增值債券型(續約2)</t>
-  </si>
-  <si>
-    <t>109-1全球美元公司增值債券型(續約)</t>
   </si>
   <si>
     <t>111-1全球氣候變遷股票型</t>
@@ -989,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>5796350429763</v>
+        <v>5971891365843</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -997,7 +988,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>1162258442448</v>
+        <v>1201392132968</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1005,7 +996,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>1682071104275</v>
+        <v>1656620647003</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1013,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1">
-        <v>904331257518</v>
+        <v>886247346634</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1065,10 +1056,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="1">
-        <v>2039012229569</v>
+        <v>2045726190154</v>
       </c>
       <c r="D2" s="5">
-        <v>0.3518</v>
+        <v>0.34259999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1079,10 +1070,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="1">
-        <v>498218329846</v>
+        <v>478291754572</v>
       </c>
       <c r="D3" s="5">
-        <v>0.086</v>
+        <v>0.0801</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1093,10 +1084,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="1">
-        <v>153766771194</v>
+        <v>152803509826</v>
       </c>
       <c r="D4" s="5">
-        <v>0.0265</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,10 +1098,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>249685462861</v>
+        <v>251734539206</v>
       </c>
       <c r="D5" s="5">
-        <v>0.0431</v>
+        <v>0.0421</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1121,10 +1112,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>301498149513</v>
+        <v>311555741999</v>
       </c>
       <c r="D6" s="5">
-        <v>0.052000000000000005</v>
+        <v>0.052199999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,10 +1126,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>835843516155</v>
+        <v>851340644551</v>
       </c>
       <c r="D7" s="5">
-        <v>0.1442</v>
+        <v>0.1426</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1149,10 +1140,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>715655062812</v>
+        <v>721154157630</v>
       </c>
       <c r="D8" s="5">
-        <v>0.1235</v>
+        <v>0.1208</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1163,10 +1154,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="1">
-        <v>74774832699</v>
+        <v>84027862506</v>
       </c>
       <c r="D9" s="5">
-        <v>0.0129</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1177,10 +1168,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="1">
-        <v>45413620644</v>
+        <v>46158624415</v>
       </c>
       <c r="D10" s="5">
-        <v>0.0078000000000000005</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1191,10 +1182,10 @@
         <v>22</v>
       </c>
       <c r="C11" s="1">
-        <v>3757338200194</v>
+        <v>3926165175689</v>
       </c>
       <c r="D11" s="5">
-        <v>0.6481999999999999</v>
+        <v>0.6574</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1205,10 +1196,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="1">
-        <v>1096284105994</v>
+        <v>1171597084307</v>
       </c>
       <c r="D12" s="5">
-        <v>0.1891</v>
+        <v>0.1962</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1219,10 +1210,10 @@
         <v>24</v>
       </c>
       <c r="C13" s="1">
-        <v>2661054094200</v>
+        <v>2754568091382</v>
       </c>
       <c r="D13" s="5">
-        <v>0.45909999999999995</v>
+        <v>0.4612</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1233,10 +1224,10 @@
         <v>25</v>
       </c>
       <c r="C14" s="1">
-        <v>585932807329</v>
+        <v>596266506088</v>
       </c>
       <c r="D14" s="5">
-        <v>0.1011</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1247,10 +1238,10 @@
         <v>26</v>
       </c>
       <c r="C15" s="1">
-        <v>1518091521122</v>
+        <v>1574426402328</v>
       </c>
       <c r="D15" s="5">
-        <v>0.2619</v>
+        <v>0.2636</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1261,10 +1252,10 @@
         <v>27</v>
       </c>
       <c r="C16" s="1">
-        <v>557029765749</v>
+        <v>583875182966</v>
       </c>
       <c r="D16" s="5">
-        <v>0.09609999999999999</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1275,7 +1266,7 @@
         <v>28</v>
       </c>
       <c r="C17" s="1">
-        <v>5796350429763</v>
+        <v>5971891365843</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -1289,10 +1280,10 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>515241051164</v>
+        <v>542814149168</v>
       </c>
       <c r="D18" s="5">
-        <v>0.44329999999999997</v>
+        <v>0.4518</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1303,10 +1294,10 @@
         <v>14</v>
       </c>
       <c r="C19" s="1">
-        <v>206753965948</v>
+        <v>243818801079</v>
       </c>
       <c r="D19" s="5">
-        <v>0.1779</v>
+        <v>0.2029</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1317,10 +1308,10 @@
         <v>15</v>
       </c>
       <c r="C20" s="1">
-        <v>70907889232</v>
+        <v>73524579727</v>
       </c>
       <c r="D20" s="5">
-        <v>0.061</v>
+        <v>0.061200000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,10 +1322,10 @@
         <v>16</v>
       </c>
       <c r="C21" s="1">
-        <v>87428925594</v>
+        <v>86936556465</v>
       </c>
       <c r="D21" s="5">
-        <v>0.07519999999999999</v>
+        <v>0.0724</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,10 +1336,10 @@
         <v>17</v>
       </c>
       <c r="C22" s="1">
-        <v>95909996878</v>
+        <v>86679774630</v>
       </c>
       <c r="D22" s="5">
-        <v>0.0825</v>
+        <v>0.0721</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1359,10 +1350,10 @@
         <v>18</v>
       </c>
       <c r="C23" s="1">
-        <v>54240273512</v>
+        <v>51854437267</v>
       </c>
       <c r="D23" s="5">
-        <v>0.0467</v>
+        <v>0.0432</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1373,10 +1364,10 @@
         <v>19</v>
       </c>
       <c r="C24" s="1">
-        <v>30843423120</v>
+        <v>29814460239</v>
       </c>
       <c r="D24" s="5">
-        <v>0.0265</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1387,10 +1378,10 @@
         <v>20</v>
       </c>
       <c r="C25" s="1">
-        <v>23396850392</v>
+        <v>22039977028</v>
       </c>
       <c r="D25" s="5">
-        <v>0.0202</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,10 +1406,10 @@
         <v>22</v>
       </c>
       <c r="C27" s="1">
-        <v>647017391284</v>
+        <v>658577983800</v>
       </c>
       <c r="D27" s="5">
-        <v>0.5567</v>
+        <v>0.5482</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1429,10 +1420,10 @@
         <v>23</v>
       </c>
       <c r="C28" s="1">
-        <v>177545692702</v>
+        <v>183853928809</v>
       </c>
       <c r="D28" s="5">
-        <v>0.1527</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1443,10 +1434,10 @@
         <v>24</v>
       </c>
       <c r="C29" s="1">
-        <v>469471698582</v>
+        <v>474724054991</v>
       </c>
       <c r="D29" s="5">
-        <v>0.40399999999999997</v>
+        <v>0.39520000000000005</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1457,10 +1448,10 @@
         <v>25</v>
       </c>
       <c r="C30" s="1">
-        <v>108036669123</v>
+        <v>110143623315</v>
       </c>
       <c r="D30" s="5">
-        <v>0.09300000000000001</v>
+        <v>0.0917</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,10 +1462,10 @@
         <v>26</v>
       </c>
       <c r="C31" s="1">
-        <v>241307746600</v>
+        <v>243869586211</v>
       </c>
       <c r="D31" s="5">
-        <v>0.2076</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,10 +1476,10 @@
         <v>27</v>
       </c>
       <c r="C32" s="1">
-        <v>120127282859</v>
+        <v>120710845465</v>
       </c>
       <c r="D32" s="5">
-        <v>0.10339999999999999</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1499,7 +1490,7 @@
         <v>28</v>
       </c>
       <c r="C33" s="1">
-        <v>1162258442448</v>
+        <v>1201392132968</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -1513,10 +1504,10 @@
         <v>13</v>
       </c>
       <c r="C34" s="1">
-        <v>1150279925641</v>
+        <v>1130233744952</v>
       </c>
       <c r="D34" s="5">
-        <v>0.6839</v>
+        <v>0.6822</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,10 +1518,10 @@
         <v>14</v>
       </c>
       <c r="C35" s="1">
-        <v>171077941843</v>
+        <v>162858626420</v>
       </c>
       <c r="D35" s="5">
-        <v>0.1017</v>
+        <v>0.0983</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1541,10 +1532,10 @@
         <v>15</v>
       </c>
       <c r="C36" s="1">
-        <v>41231589691</v>
+        <v>43160086648</v>
       </c>
       <c r="D36" s="5">
-        <v>0.0245</v>
+        <v>0.026099999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,10 +1546,10 @@
         <v>16</v>
       </c>
       <c r="C37" s="1">
-        <v>71222141881</v>
+        <v>72726377661</v>
       </c>
       <c r="D37" s="5">
-        <v>0.0424</v>
+        <v>0.043899999999999995</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1569,7 +1560,7 @@
         <v>29</v>
       </c>
       <c r="C38" s="1">
-        <v>1571085838</v>
+        <v>1569739937</v>
       </c>
       <c r="D38" s="5">
         <v>0.0009</v>
@@ -1583,10 +1574,10 @@
         <v>30</v>
       </c>
       <c r="C39" s="1">
-        <v>1470000000</v>
+        <v>750000000</v>
       </c>
       <c r="D39" s="5">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1597,10 +1588,10 @@
         <v>31</v>
       </c>
       <c r="C40" s="1">
-        <v>34901907729</v>
+        <v>33959565172</v>
       </c>
       <c r="D40" s="5">
-        <v>0.0207</v>
+        <v>0.020499999999999997</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1611,10 +1602,10 @@
         <v>17</v>
       </c>
       <c r="C41" s="1">
-        <v>533711674491</v>
+        <v>513267409855</v>
       </c>
       <c r="D41" s="5">
-        <v>0.3173</v>
+        <v>0.3098</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1625,10 +1616,10 @@
         <v>18</v>
       </c>
       <c r="C42" s="1">
-        <v>295093584168</v>
+        <v>301941939259</v>
       </c>
       <c r="D42" s="5">
-        <v>0.17550000000000002</v>
+        <v>0.1822</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1639,10 +1630,10 @@
         <v>19</v>
       </c>
       <c r="C43" s="1">
-        <v>190548255833</v>
+        <v>190717945389</v>
       </c>
       <c r="D43" s="5">
-        <v>0.1133</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1653,10 +1644,10 @@
         <v>20</v>
       </c>
       <c r="C44" s="1">
-        <v>93683868839</v>
+        <v>100125263652</v>
       </c>
       <c r="D44" s="5">
-        <v>0.0557</v>
+        <v>0.0604</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1667,10 +1658,10 @@
         <v>21</v>
       </c>
       <c r="C45" s="1">
-        <v>10861459496</v>
+        <v>11098730218</v>
       </c>
       <c r="D45" s="5">
-        <v>0.006500000000000001</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1681,10 +1672,10 @@
         <v>22</v>
       </c>
       <c r="C46" s="1">
-        <v>531791178634</v>
+        <v>526386902051</v>
       </c>
       <c r="D46" s="5">
-        <v>0.3161</v>
+        <v>0.3178</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,10 +1686,10 @@
         <v>23</v>
       </c>
       <c r="C47" s="1">
-        <v>78246504107</v>
+        <v>68461127545</v>
       </c>
       <c r="D47" s="5">
-        <v>0.04650000000000001</v>
+        <v>0.041299999999999996</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,10 +1700,10 @@
         <v>24</v>
       </c>
       <c r="C48" s="1">
-        <v>453544674527</v>
+        <v>457925774506</v>
       </c>
       <c r="D48" s="5">
-        <v>0.2696</v>
+        <v>0.27649999999999997</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,10 +1714,10 @@
         <v>25</v>
       </c>
       <c r="C49" s="1">
-        <v>93935170986</v>
+        <v>94809693597</v>
       </c>
       <c r="D49" s="5">
-        <v>0.0558</v>
+        <v>0.057300000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1737,10 +1728,10 @@
         <v>26</v>
       </c>
       <c r="C50" s="1">
-        <v>221221954191</v>
+        <v>224986107597</v>
       </c>
       <c r="D50" s="5">
-        <v>0.1315</v>
+        <v>0.1358</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,10 +1742,10 @@
         <v>27</v>
       </c>
       <c r="C51" s="1">
-        <v>138387549350</v>
+        <v>138129973312</v>
       </c>
       <c r="D51" s="5">
-        <v>0.0823</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,7 +1756,7 @@
         <v>28</v>
       </c>
       <c r="C52" s="1">
-        <v>1682071104275</v>
+        <v>1656620647003</v>
       </c>
       <c r="D52" s="5">
         <v>1</v>
@@ -1779,10 +1770,10 @@
         <v>13</v>
       </c>
       <c r="C53" s="1">
-        <v>1150279925641</v>
+        <v>1130233744952</v>
       </c>
       <c r="D53" s="5">
-        <v>0.6839</v>
+        <v>0.6822</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,10 +1784,10 @@
         <v>22</v>
       </c>
       <c r="C54" s="1">
-        <v>1150279925641</v>
+        <v>1130233744952</v>
       </c>
       <c r="D54" s="5">
-        <v>0.6839</v>
+        <v>0.6822</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,10 +1798,10 @@
         <v>13</v>
       </c>
       <c r="C55" s="1">
-        <v>557783030776</v>
+        <v>542143193531</v>
       </c>
       <c r="D55" s="5">
-        <v>0.6168</v>
+        <v>0.6117</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,10 +1812,10 @@
         <v>14</v>
       </c>
       <c r="C56" s="1">
-        <v>52236032009</v>
+        <v>42496498692</v>
       </c>
       <c r="D56" s="5">
-        <v>0.057800000000000004</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,10 +1840,10 @@
         <v>15</v>
       </c>
       <c r="C58" s="1">
-        <v>14888322458</v>
+        <v>15470496937</v>
       </c>
       <c r="D58" s="5">
-        <v>0.0165</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1863,10 +1854,10 @@
         <v>16</v>
       </c>
       <c r="C59" s="1">
-        <v>59952028202</v>
+        <v>61212952203</v>
       </c>
       <c r="D59" s="5">
-        <v>0.0662</v>
+        <v>0.0691</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1877,10 +1868,10 @@
         <v>17</v>
       </c>
       <c r="C60" s="1">
-        <v>242437576267</v>
+        <v>232196292425</v>
       </c>
       <c r="D60" s="5">
-        <v>0.2681</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1891,10 +1882,10 @@
         <v>18</v>
       </c>
       <c r="C61" s="1">
-        <v>188269071840</v>
+        <v>190766953274</v>
       </c>
       <c r="D61" s="5">
-        <v>0.2082</v>
+        <v>0.2152</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,10 +1896,10 @@
         <v>19</v>
       </c>
       <c r="C62" s="1">
-        <v>108189687089</v>
+        <v>108506446162</v>
       </c>
       <c r="D62" s="5">
-        <v>0.11960000000000001</v>
+        <v>0.12240000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,10 +1910,10 @@
         <v>20</v>
       </c>
       <c r="C63" s="1">
-        <v>57427295679</v>
+        <v>59219852253</v>
       </c>
       <c r="D63" s="5">
-        <v>0.0635</v>
+        <v>0.0668</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1933,10 +1924,10 @@
         <v>21</v>
       </c>
       <c r="C64" s="1">
-        <v>22652089072</v>
+        <v>23040654859</v>
       </c>
       <c r="D64" s="5">
-        <v>0.025099999999999997</v>
+        <v>0.026000000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,10 +1938,10 @@
         <v>22</v>
       </c>
       <c r="C65" s="1">
-        <v>346548226742</v>
+        <v>344104153103</v>
       </c>
       <c r="D65" s="5">
-        <v>0.3832</v>
+        <v>0.3883</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,10 +1952,10 @@
         <v>23</v>
       </c>
       <c r="C66" s="1">
-        <v>105625756568</v>
+        <v>100575817739</v>
       </c>
       <c r="D66" s="5">
-        <v>0.1168</v>
+        <v>0.11349999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,10 +1966,10 @@
         <v>24</v>
       </c>
       <c r="C67" s="1">
-        <v>240922470174</v>
+        <v>243528335364</v>
       </c>
       <c r="D67" s="5">
-        <v>0.2664</v>
+        <v>0.2748</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1989,10 +1980,10 @@
         <v>25</v>
       </c>
       <c r="C68" s="1">
-        <v>42716622221</v>
+        <v>43171984301</v>
       </c>
       <c r="D68" s="5">
-        <v>0.0473</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2003,10 +1994,10 @@
         <v>26</v>
       </c>
       <c r="C69" s="1">
-        <v>168606130386</v>
+        <v>170076314183</v>
       </c>
       <c r="D69" s="5">
-        <v>0.1864</v>
+        <v>0.19190000000000002</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,10 +2008,10 @@
         <v>27</v>
       </c>
       <c r="C70" s="1">
-        <v>29599717567</v>
+        <v>30280036880</v>
       </c>
       <c r="D70" s="5">
-        <v>0.0327</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2031,7 +2022,7 @@
         <v>28</v>
       </c>
       <c r="C71" s="1">
-        <v>904331257518</v>
+        <v>886247346634</v>
       </c>
       <c r="D71" s="5">
         <v>1</v>
@@ -2045,10 +2036,10 @@
         <v>13</v>
       </c>
       <c r="C72" s="1">
-        <v>557783030776</v>
+        <v>542143193531</v>
       </c>
       <c r="D72" s="5">
-        <v>0.6168</v>
+        <v>0.6117</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2059,10 +2050,10 @@
         <v>22</v>
       </c>
       <c r="C73" s="1">
-        <v>346548226742</v>
+        <v>344104153103</v>
       </c>
       <c r="D73" s="5">
-        <v>0.3832</v>
+        <v>0.3883</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2073,10 +2064,10 @@
         <v>18</v>
       </c>
       <c r="C74" s="1">
-        <v>429191542014</v>
+        <v>434295288638</v>
       </c>
       <c r="D74" s="5">
-        <v>0.4746</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2078,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
@@ -2136,7 +2127,7 @@
         <v>53037175831</v>
       </c>
       <c r="E2" s="1">
-        <v>117216440397</v>
+        <v>103171495458</v>
       </c>
       <c r="F2" t="s">
         <v>42</v>
@@ -2145,7 +2136,7 @@
         <v>NaN</v>
       </c>
       <c r="H2" s="5">
-        <v>0.0475</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2162,7 +2153,7 @@
         <v>6829066771</v>
       </c>
       <c r="E3" s="1">
-        <v>26944336638</v>
+        <v>23175252518</v>
       </c>
       <c r="F3" t="s">
         <v>42</v>
@@ -2171,7 +2162,7 @@
         <v>NaN</v>
       </c>
       <c r="H3" s="5">
-        <v>0.2065</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2188,7 +2179,7 @@
         <v>25455695879</v>
       </c>
       <c r="E4" s="1">
-        <v>66490441397</v>
+        <v>58059587887</v>
       </c>
       <c r="F4" t="s">
         <v>42</v>
@@ -2197,7 +2188,7 @@
         <v>NaN</v>
       </c>
       <c r="H4" s="5">
-        <v>0.1149</v>
+        <v>0.1198</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2214,7 +2205,7 @@
         <v>7430070832</v>
       </c>
       <c r="E5" s="1">
-        <v>15401269847</v>
+        <v>12830277484</v>
       </c>
       <c r="F5" t="s">
         <v>42</v>
@@ -2223,7 +2214,7 @@
         <v>NaN</v>
       </c>
       <c r="H5" s="5">
-        <v>0.1149</v>
+        <v>0.1198</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2240,7 +2231,7 @@
         <v>10445113310</v>
       </c>
       <c r="E6" s="1">
-        <v>29252741164</v>
+        <v>26081939969</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
@@ -2249,7 +2240,7 @@
         <v>NaN</v>
       </c>
       <c r="H6" s="5">
-        <v>0.2161</v>
+        <v>0.22089999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2266,7 +2257,7 @@
         <v>29101525086</v>
       </c>
       <c r="E7" s="1">
-        <v>89558163782</v>
+        <v>79596508766</v>
       </c>
       <c r="F7" t="s">
         <v>42</v>
@@ -2275,7 +2266,7 @@
         <v>NaN</v>
       </c>
       <c r="H7" s="5">
-        <v>1.9264</v>
+        <v>1.6263999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2292,7 +2283,7 @@
         <v>15198354580</v>
       </c>
       <c r="E8" s="1">
-        <v>46662272660</v>
+        <v>40396399644</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
@@ -2301,7 +2292,7 @@
         <v>NaN</v>
       </c>
       <c r="H8" s="5">
-        <v>0.1142</v>
+        <v>0.1191</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2318,7 +2309,7 @@
         <v>20913151881</v>
       </c>
       <c r="E9" s="1">
-        <v>46007771615</v>
+        <v>38985680063</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
@@ -2327,7 +2318,7 @@
         <v>NaN</v>
       </c>
       <c r="H9" s="5">
-        <v>0.1142</v>
+        <v>0.1191</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2344,7 +2335,7 @@
         <v>37517851631</v>
       </c>
       <c r="E10" s="1">
-        <v>60767826884</v>
+        <v>56336151382</v>
       </c>
       <c r="F10" t="s">
         <v>42</v>
@@ -2353,7 +2344,7 @@
         <v>NaN</v>
       </c>
       <c r="H10" s="5">
-        <v>0.45189999999999997</v>
+        <v>0.36619999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2370,7 +2361,7 @@
         <v>39053243767</v>
       </c>
       <c r="E11" s="1">
-        <v>60714886085</v>
+        <v>55897686273</v>
       </c>
       <c r="F11" t="s">
         <v>42</v>
@@ -2379,7 +2370,7 @@
         <v>NaN</v>
       </c>
       <c r="H11" s="5">
-        <v>0.45189999999999997</v>
+        <v>0.36619999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2396,7 +2387,7 @@
         <v>15841461125</v>
       </c>
       <c r="E12" s="1">
-        <v>45210757604</v>
+        <v>41322318010</v>
       </c>
       <c r="F12" t="s">
         <v>42</v>
@@ -2405,7 +2396,7 @@
         <v>NaN</v>
       </c>
       <c r="H12" s="5">
-        <v>0.2253</v>
+        <v>0.2302</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2422,7 +2413,7 @@
         <v>23658255796</v>
       </c>
       <c r="E13" s="1">
-        <v>40548223163</v>
+        <v>40415302192</v>
       </c>
       <c r="F13" t="s">
         <v>42</v>
@@ -2431,7 +2422,7 @@
         <v>NaN</v>
       </c>
       <c r="H13" s="5">
-        <v>0.6662</v>
+        <v>0.6726000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2448,7 +2439,7 @@
         <v>20210724588</v>
       </c>
       <c r="E14" s="1">
-        <v>34180153225</v>
+        <v>34144349128</v>
       </c>
       <c r="F14" t="s">
         <v>42</v>
@@ -2457,7 +2448,7 @@
         <v>NaN</v>
       </c>
       <c r="H14" s="5">
-        <v>0.6662</v>
+        <v>0.6726000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2474,7 +2465,7 @@
         <v>19554752074</v>
       </c>
       <c r="E15" s="1">
-        <v>33489971132</v>
+        <v>33339520716</v>
       </c>
       <c r="F15" t="s">
         <v>42</v>
@@ -2483,7 +2474,7 @@
         <v>NaN</v>
       </c>
       <c r="H15" s="5">
-        <v>0.6662</v>
+        <v>0.6726000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2500,7 +2491,7 @@
         <v>16812903049</v>
       </c>
       <c r="E16" s="1">
-        <v>28490812845</v>
+        <v>28296630865</v>
       </c>
       <c r="F16" t="s">
         <v>42</v>
@@ -2509,7 +2500,7 @@
         <v>NaN</v>
       </c>
       <c r="H16" s="5">
-        <v>0.6662</v>
+        <v>0.6726000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2526,7 +2517,7 @@
         <v>24098049298</v>
       </c>
       <c r="E17" s="1">
-        <v>41442870125</v>
+        <v>41223752467</v>
       </c>
       <c r="F17" t="s">
         <v>42</v>
@@ -2535,7 +2526,7 @@
         <v>NaN</v>
       </c>
       <c r="H17" s="5">
-        <v>0.6662</v>
+        <v>0.6726000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2552,7 +2543,7 @@
         <v>4799121512</v>
       </c>
       <c r="E18" s="1">
-        <v>15643167621</v>
+        <v>12929826184</v>
       </c>
       <c r="F18" t="s">
         <v>42</v>
@@ -2561,7 +2552,7 @@
         <v>NaN</v>
       </c>
       <c r="H18" s="5">
-        <v>0.195</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -2578,7 +2569,7 @@
         <v>3601238896</v>
       </c>
       <c r="E19" s="1">
-        <v>8855866454</v>
+        <v>7926139191</v>
       </c>
       <c r="F19" t="s">
         <v>42</v>
@@ -2587,7 +2578,7 @@
         <v>NaN</v>
       </c>
       <c r="H19" s="5">
-        <v>0.195</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -2604,7 +2595,7 @@
         <v>15088712403</v>
       </c>
       <c r="E20" s="1">
-        <v>51353992119</v>
+        <v>44447329187</v>
       </c>
       <c r="F20" t="s">
         <v>42</v>
@@ -2613,7 +2604,7 @@
         <v>NaN</v>
       </c>
       <c r="H20" s="5">
-        <v>0.2051</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2630,7 +2621,7 @@
         <v>5018453600</v>
       </c>
       <c r="E21" s="1">
-        <v>14706636821</v>
+        <v>12530478206</v>
       </c>
       <c r="F21" t="s">
         <v>42</v>
@@ -2639,7 +2630,7 @@
         <v>NaN</v>
       </c>
       <c r="H21" s="5">
-        <v>0.2051</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2656,7 +2647,7 @@
         <v>6382621945</v>
       </c>
       <c r="E22" s="1">
-        <v>15881715753</v>
+        <v>13603740058</v>
       </c>
       <c r="F22" t="s">
         <v>42</v>
@@ -2665,7 +2656,7 @@
         <v>NaN</v>
       </c>
       <c r="H22" s="5">
-        <v>0.2051</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2682,7 +2673,7 @@
         <v>7096535878</v>
       </c>
       <c r="E23" s="1">
-        <v>19290103216</v>
+        <v>17348896195</v>
       </c>
       <c r="F23" t="s">
         <v>42</v>
@@ -2691,7 +2682,7 @@
         <v>NaN</v>
       </c>
       <c r="H23" s="5">
-        <v>0.2051</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2708,7 +2699,7 @@
         <v>8254694051</v>
       </c>
       <c r="E24" s="1">
-        <v>27561119140</v>
+        <v>25518246126</v>
       </c>
       <c r="F24" t="s">
         <v>42</v>
@@ -2717,7 +2708,7 @@
         <v>NaN</v>
       </c>
       <c r="H24" s="5">
-        <v>2.3322</v>
+        <v>2.0934</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -2734,7 +2725,7 @@
         <v>12775472416</v>
       </c>
       <c r="E25" s="1">
-        <v>43969364295</v>
+        <v>40249195792</v>
       </c>
       <c r="F25" t="s">
         <v>42</v>
@@ -2743,7 +2734,7 @@
         <v>NaN</v>
       </c>
       <c r="H25" s="5">
-        <v>2.3322</v>
+        <v>2.0934</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -2760,7 +2751,7 @@
         <v>9403481285</v>
       </c>
       <c r="E26" s="1">
-        <v>32458320697</v>
+        <v>29896625207</v>
       </c>
       <c r="F26" t="s">
         <v>42</v>
@@ -2769,7 +2760,7 @@
         <v>NaN</v>
       </c>
       <c r="H26" s="5">
-        <v>2.3322</v>
+        <v>2.0934</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -2786,7 +2777,7 @@
         <v>12635490783</v>
       </c>
       <c r="E27" s="1">
-        <v>42692132366</v>
+        <v>39498492066</v>
       </c>
       <c r="F27" t="s">
         <v>42</v>
@@ -2795,7 +2786,7 @@
         <v>NaN</v>
       </c>
       <c r="H27" s="5">
-        <v>2.3322</v>
+        <v>2.0934</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -2812,7 +2803,7 @@
         <v>10445956159</v>
       </c>
       <c r="E28" s="1">
-        <v>36519687730</v>
+        <v>33972525542</v>
       </c>
       <c r="F28" t="s">
         <v>42</v>
@@ -2821,7 +2812,7 @@
         <v>NaN</v>
       </c>
       <c r="H28" s="5">
-        <v>2.3322</v>
+        <v>2.0934</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -2838,7 +2829,7 @@
         <v>7235716436</v>
       </c>
       <c r="E29" s="1">
-        <v>24603215571</v>
+        <v>22662104792</v>
       </c>
       <c r="F29" t="s">
         <v>42</v>
@@ -2847,7 +2838,7 @@
         <v>NaN</v>
       </c>
       <c r="H29" s="5">
-        <v>2.3322</v>
+        <v>2.0934</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -2864,7 +2855,7 @@
         <v>4439275178</v>
       </c>
       <c r="E30" s="1">
-        <v>15667722077</v>
+        <v>14479782645</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
@@ -2873,7 +2864,7 @@
         <v>NaN</v>
       </c>
       <c r="H30" s="5">
-        <v>2.3322</v>
+        <v>2.0934</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -2890,7 +2881,7 @@
         <v>13613817760</v>
       </c>
       <c r="E31" s="1">
-        <v>34959497939</v>
+        <v>30231598199</v>
       </c>
       <c r="F31" t="s">
         <v>42</v>
@@ -2899,7 +2890,7 @@
         <v>NaN</v>
       </c>
       <c r="H31" s="5">
-        <v>0.12380000000000001</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -2916,7 +2907,7 @@
         <v>11400361947</v>
       </c>
       <c r="E32" s="1">
-        <v>34832121681</v>
+        <v>30148968555</v>
       </c>
       <c r="F32" t="s">
         <v>42</v>
@@ -2925,7 +2916,7 @@
         <v>NaN</v>
       </c>
       <c r="H32" s="5">
-        <v>0.12380000000000001</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -2942,7 +2933,7 @@
         <v>13638402860</v>
       </c>
       <c r="E33" s="1">
-        <v>34541020017</v>
+        <v>28605010963</v>
       </c>
       <c r="F33" t="s">
         <v>42</v>
@@ -2951,7 +2942,7 @@
         <v>NaN</v>
       </c>
       <c r="H33" s="5">
-        <v>0.12380000000000001</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -2968,7 +2959,7 @@
         <v>20601693072</v>
       </c>
       <c r="E34" s="1">
-        <v>65584458258</v>
+        <v>56940962295</v>
       </c>
       <c r="F34" t="s">
         <v>42</v>
@@ -2977,7 +2968,7 @@
         <v>NaN</v>
       </c>
       <c r="H34" s="5">
-        <v>0.12380000000000001</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -2994,7 +2985,7 @@
         <v>19457627824</v>
       </c>
       <c r="E35" s="1">
-        <v>46512828487</v>
+        <v>42021514983</v>
       </c>
       <c r="F35" t="s">
         <v>42</v>
@@ -3003,7 +2994,7 @@
         <v>NaN</v>
       </c>
       <c r="H35" s="5">
-        <v>0.12380000000000001</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3020,7 +3011,7 @@
         <v>9724896734</v>
       </c>
       <c r="E36" s="1">
-        <v>25543932311</v>
+        <v>21096859167</v>
       </c>
       <c r="F36" t="s">
         <v>42</v>
@@ -3029,7 +3020,7 @@
         <v>NaN</v>
       </c>
       <c r="H36" s="5">
-        <v>0.12380000000000001</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3046,7 +3037,7 @@
         <v>17743902371</v>
       </c>
       <c r="E37" s="1">
-        <v>18275932892</v>
+        <v>16416991185</v>
       </c>
       <c r="F37" t="s">
         <v>42</v>
@@ -3055,7 +3046,7 @@
         <v>NaN</v>
       </c>
       <c r="H37" s="5">
-        <v>0.0083</v>
+        <v>0.013600000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3072,7 +3063,7 @@
         <v>25118214883</v>
       </c>
       <c r="E38" s="1">
-        <v>26467785253</v>
+        <v>22752979420</v>
       </c>
       <c r="F38" t="s">
         <v>42</v>
@@ -3081,7 +3072,7 @@
         <v>NaN</v>
       </c>
       <c r="H38" s="5">
-        <v>0.0083</v>
+        <v>0.013600000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3098,7 +3089,7 @@
         <v>18706659825</v>
       </c>
       <c r="E39" s="1">
-        <v>19431931249</v>
+        <v>16064777486</v>
       </c>
       <c r="F39" t="s">
         <v>42</v>
@@ -3107,7 +3098,7 @@
         <v>NaN</v>
       </c>
       <c r="H39" s="5">
-        <v>0.0083</v>
+        <v>0.013600000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -3124,7 +3115,7 @@
         <v>23159171521</v>
       </c>
       <c r="E40" s="1">
-        <v>24223983214</v>
+        <v>21117075101</v>
       </c>
       <c r="F40" t="s">
         <v>42</v>
@@ -3133,7 +3124,7 @@
         <v>NaN</v>
       </c>
       <c r="H40" s="5">
-        <v>0.0083</v>
+        <v>0.013600000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3150,7 +3141,7 @@
         <v>34803007809</v>
       </c>
       <c r="E41" s="1">
-        <v>34909980939</v>
+        <v>30727399354</v>
       </c>
       <c r="F41" t="s">
         <v>42</v>
@@ -3159,7 +3150,7 @@
         <v>NaN</v>
       </c>
       <c r="H41" s="5">
-        <v>0.0083</v>
+        <v>0.013600000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3176,7 +3167,7 @@
         <v>3000000000</v>
       </c>
       <c r="E42" s="1">
-        <v>8119040401</v>
+        <v>7088003475</v>
       </c>
       <c r="F42" t="s">
         <v>42</v>
@@ -3185,7 +3176,7 @@
         <v>NaN</v>
       </c>
       <c r="H42" s="5">
-        <v>1.6469999999999998</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3202,7 +3193,7 @@
         <v>3000000000</v>
       </c>
       <c r="E43" s="1">
-        <v>8006808777</v>
+        <v>7046409838</v>
       </c>
       <c r="F43" t="s">
         <v>42</v>
@@ -3211,7 +3202,7 @@
         <v>NaN</v>
       </c>
       <c r="H43" s="5">
-        <v>1.6469999999999998</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3228,7 +3219,7 @@
         <v>3000000000</v>
       </c>
       <c r="E44" s="1">
-        <v>8142867535</v>
+        <v>7058698601</v>
       </c>
       <c r="F44" t="s">
         <v>42</v>
@@ -3237,7 +3228,7 @@
         <v>NaN</v>
       </c>
       <c r="H44" s="5">
-        <v>1.6469999999999998</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3254,7 +3245,7 @@
         <v>3000000000</v>
       </c>
       <c r="E45" s="1">
-        <v>8347803573</v>
+        <v>7299682641</v>
       </c>
       <c r="F45" t="s">
         <v>42</v>
@@ -3263,7 +3254,7 @@
         <v>NaN</v>
       </c>
       <c r="H45" s="5">
-        <v>1.6469999999999998</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -3280,7 +3271,7 @@
         <v>3000000000</v>
       </c>
       <c r="E46" s="1">
-        <v>8107453650</v>
+        <v>6973552798</v>
       </c>
       <c r="F46" t="s">
         <v>42</v>
@@ -3289,7 +3280,7 @@
         <v>NaN</v>
       </c>
       <c r="H46" s="5">
-        <v>1.6469999999999998</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3306,7 +3297,7 @@
         <v>8000000000</v>
       </c>
       <c r="E47" s="1">
-        <v>24503226743</v>
+        <v>21201075224</v>
       </c>
       <c r="F47" t="s">
         <v>42</v>
@@ -3315,7 +3306,7 @@
         <v>NaN</v>
       </c>
       <c r="H47" s="5">
-        <v>0.276</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -3332,7 +3323,7 @@
         <v>8000000000</v>
       </c>
       <c r="E48" s="1">
-        <v>19847858127</v>
+        <v>16562402836</v>
       </c>
       <c r="F48" t="s">
         <v>42</v>
@@ -3341,7 +3332,7 @@
         <v>NaN</v>
       </c>
       <c r="H48" s="5">
-        <v>0.276</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -3358,7 +3349,7 @@
         <v>8000000000</v>
       </c>
       <c r="E49" s="1">
-        <v>22881002147</v>
+        <v>20580006389</v>
       </c>
       <c r="F49" t="s">
         <v>42</v>
@@ -3367,7 +3358,7 @@
         <v>NaN</v>
       </c>
       <c r="H49" s="5">
-        <v>0.276</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -3384,7 +3375,7 @@
         <v>8000000000</v>
       </c>
       <c r="E50" s="1">
-        <v>21083206379</v>
+        <v>17031604335</v>
       </c>
       <c r="F50" t="s">
         <v>42</v>
@@ -3393,7 +3384,7 @@
         <v>NaN</v>
       </c>
       <c r="H50" s="5">
-        <v>0.276</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -3410,7 +3401,7 @@
         <v>8000000000</v>
       </c>
       <c r="E51" s="1">
-        <v>28004991296</v>
+        <v>24613117899</v>
       </c>
       <c r="F51" t="s">
         <v>42</v>
@@ -3419,7 +3410,7 @@
         <v>NaN</v>
       </c>
       <c r="H51" s="5">
-        <v>0.276</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -3436,7 +3427,7 @@
         <v>8000000000</v>
       </c>
       <c r="E52" s="1">
-        <v>24946592925</v>
+        <v>21079896694</v>
       </c>
       <c r="F52" t="s">
         <v>42</v>
@@ -3445,7 +3436,7 @@
         <v>NaN</v>
       </c>
       <c r="H52" s="5">
-        <v>0.276</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -3462,7 +3453,7 @@
         <v>7000000000</v>
       </c>
       <c r="E53" s="1">
-        <v>14188624135</v>
+        <v>12706419190</v>
       </c>
       <c r="F53" t="s">
         <v>42</v>
@@ -3471,7 +3462,7 @@
         <v>NaN</v>
       </c>
       <c r="H53" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -3488,7 +3479,7 @@
         <v>7000000000</v>
       </c>
       <c r="E54" s="1">
-        <v>21422349865</v>
+        <v>18530231676</v>
       </c>
       <c r="F54" t="s">
         <v>42</v>
@@ -3497,7 +3488,7 @@
         <v>NaN</v>
       </c>
       <c r="H54" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -3514,7 +3505,7 @@
         <v>7000000000</v>
       </c>
       <c r="E55" s="1">
-        <v>18428471954</v>
+        <v>15293632896</v>
       </c>
       <c r="F55" t="s">
         <v>42</v>
@@ -3523,7 +3514,7 @@
         <v>NaN</v>
       </c>
       <c r="H55" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -3540,7 +3531,7 @@
         <v>7000000000</v>
       </c>
       <c r="E56" s="1">
-        <v>18686912565</v>
+        <v>15089595873</v>
       </c>
       <c r="F56" t="s">
         <v>42</v>
@@ -3549,7 +3540,7 @@
         <v>NaN</v>
       </c>
       <c r="H56" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -3566,7 +3557,7 @@
         <v>7000000000</v>
       </c>
       <c r="E57" s="1">
-        <v>22439815890</v>
+        <v>19452951069</v>
       </c>
       <c r="F57" t="s">
         <v>42</v>
@@ -3575,7 +3566,7 @@
         <v>NaN</v>
       </c>
       <c r="H57" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -3592,7 +3583,7 @@
         <v>7000000000</v>
       </c>
       <c r="E58" s="1">
-        <v>12176003848</v>
+        <v>9121413882</v>
       </c>
       <c r="F58" t="s">
         <v>42</v>
@@ -3601,7 +3592,7 @@
         <v>NaN</v>
       </c>
       <c r="H58" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -3618,7 +3609,7 @@
         <v>7000000000</v>
       </c>
       <c r="E59" s="1">
-        <v>16346491624</v>
+        <v>14552780847</v>
       </c>
       <c r="F59" t="s">
         <v>42</v>
@@ -3627,7 +3618,7 @@
         <v>NaN</v>
       </c>
       <c r="H59" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -3641,10 +3632,10 @@
         <v>57</v>
       </c>
       <c r="D60" s="1">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="E60" s="1">
-        <v>10665887383</v>
+        <v>13507194558</v>
       </c>
       <c r="F60" t="s">
         <v>42</v>
@@ -3653,7 +3644,7 @@
         <v>NaN</v>
       </c>
       <c r="H60" s="5">
-        <v>1.3033000000000001</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -3667,10 +3658,10 @@
         <v>72</v>
       </c>
       <c r="D61" s="1">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="E61" s="1">
-        <v>9736490954</v>
+        <v>12874751853</v>
       </c>
       <c r="F61" t="s">
         <v>42</v>
@@ -3679,7 +3670,7 @@
         <v>NaN</v>
       </c>
       <c r="H61" s="5">
-        <v>1.3033000000000001</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -3693,10 +3684,10 @@
         <v>73</v>
       </c>
       <c r="D62" s="1">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="E62" s="1">
-        <v>10202284557</v>
+        <v>13017408018</v>
       </c>
       <c r="F62" t="s">
         <v>42</v>
@@ -3705,7 +3696,7 @@
         <v>NaN</v>
       </c>
       <c r="H62" s="5">
-        <v>1.3033000000000001</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -3719,10 +3710,10 @@
         <v>63</v>
       </c>
       <c r="D63" s="1">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="E63" s="1">
-        <v>9797690852</v>
+        <v>12735007874</v>
       </c>
       <c r="F63" t="s">
         <v>42</v>
@@ -3731,7 +3722,7 @@
         <v>NaN</v>
       </c>
       <c r="H63" s="5">
-        <v>1.3033000000000001</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -3745,10 +3736,10 @@
         <v>41</v>
       </c>
       <c r="D64" s="1">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="E64" s="1">
-        <v>9797987866</v>
+        <v>12823234724</v>
       </c>
       <c r="F64" t="s">
         <v>42</v>
@@ -3757,7 +3748,7 @@
         <v>NaN</v>
       </c>
       <c r="H64" s="5">
-        <v>1.3033000000000001</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -3771,10 +3762,10 @@
         <v>74</v>
       </c>
       <c r="D65" s="1">
-        <v>5500000000</v>
+        <v>9000000000</v>
       </c>
       <c r="E65" s="1">
-        <v>10017346808</v>
+        <v>12903392256</v>
       </c>
       <c r="F65" t="s">
         <v>42</v>
@@ -3783,7 +3774,7 @@
         <v>NaN</v>
       </c>
       <c r="H65" s="5">
-        <v>1.3033000000000001</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -3800,7 +3791,7 @@
         <v>9000000000</v>
       </c>
       <c r="E66" s="1">
-        <v>14275597029</v>
+        <v>12279463586</v>
       </c>
       <c r="F66" t="s">
         <v>42</v>
@@ -3809,7 +3800,7 @@
         <v>NaN</v>
       </c>
       <c r="H66" s="5">
-        <v>0.0391</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -3826,7 +3817,7 @@
         <v>9000000000</v>
       </c>
       <c r="E67" s="1">
-        <v>14863361502</v>
+        <v>13053425511</v>
       </c>
       <c r="F67" t="s">
         <v>42</v>
@@ -3835,7 +3826,7 @@
         <v>NaN</v>
       </c>
       <c r="H67" s="5">
-        <v>0.0391</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -3852,7 +3843,7 @@
         <v>9000000000</v>
       </c>
       <c r="E68" s="1">
-        <v>15573219651</v>
+        <v>13497748336</v>
       </c>
       <c r="F68" t="s">
         <v>42</v>
@@ -3861,7 +3852,7 @@
         <v>NaN</v>
       </c>
       <c r="H68" s="5">
-        <v>0.0391</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -3878,7 +3869,7 @@
         <v>9000000000</v>
       </c>
       <c r="E69" s="1">
-        <v>14710501824</v>
+        <v>12623775612</v>
       </c>
       <c r="F69" t="s">
         <v>42</v>
@@ -3887,7 +3878,7 @@
         <v>NaN</v>
       </c>
       <c r="H69" s="5">
-        <v>0.0391</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -3904,7 +3895,7 @@
         <v>9000000000</v>
       </c>
       <c r="E70" s="1">
-        <v>14746594539</v>
+        <v>13042654095</v>
       </c>
       <c r="F70" t="s">
         <v>42</v>
@@ -3913,7 +3904,7 @@
         <v>NaN</v>
       </c>
       <c r="H70" s="5">
-        <v>0.0391</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -3927,10 +3918,10 @@
         <v>78</v>
       </c>
       <c r="D71" s="1">
-        <v>1500000000</v>
+        <v>5000000000</v>
       </c>
       <c r="E71" s="1">
-        <v>1544532768</v>
+        <v>4902240425</v>
       </c>
       <c r="F71" t="s">
         <v>42</v>
@@ -3939,24 +3930,24 @@
         <v>NaN</v>
       </c>
       <c r="H71" s="5">
-        <v>0.0037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D72" s="1">
-        <v>1500000000</v>
+        <v>15603507854</v>
       </c>
       <c r="E72" s="1">
-        <v>1528889549</v>
+        <v>32320138788</v>
       </c>
       <c r="F72" t="s">
         <v>42</v>
@@ -3965,24 +3956,24 @@
         <v>NaN</v>
       </c>
       <c r="H72" s="5">
-        <v>0.0037</v>
+        <v>0.0947</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D73" s="1">
-        <v>1500000000</v>
+        <v>13492877440</v>
       </c>
       <c r="E73" s="1">
-        <v>1474347055</v>
+        <v>26790911817</v>
       </c>
       <c r="F73" t="s">
         <v>42</v>
@@ -3991,24 +3982,24 @@
         <v>NaN</v>
       </c>
       <c r="H73" s="5">
-        <v>0.0037</v>
+        <v>0.0947</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D74" s="1">
-        <v>1500000000</v>
+        <v>6530798735</v>
       </c>
       <c r="E74" s="1">
-        <v>1489331693</v>
+        <v>13425179562</v>
       </c>
       <c r="F74" t="s">
         <v>42</v>
@@ -4017,24 +4008,24 @@
         <v>NaN</v>
       </c>
       <c r="H74" s="5">
-        <v>0.0037</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="D75" s="1">
-        <v>1500000000</v>
+        <v>27357530009</v>
       </c>
       <c r="E75" s="1">
-        <v>1492945981</v>
+        <v>78465559204</v>
       </c>
       <c r="F75" t="s">
         <v>42</v>
@@ -4043,7 +4034,7 @@
         <v>NaN</v>
       </c>
       <c r="H75" s="5">
-        <v>0.0037</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -4051,16 +4042,16 @@
         <v>6</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D76" s="1">
-        <v>15603507854</v>
+        <v>4800107976</v>
       </c>
       <c r="E76" s="1">
-        <v>38359381288</v>
+        <v>12931832350</v>
       </c>
       <c r="F76" t="s">
         <v>42</v>
@@ -4069,7 +4060,7 @@
         <v>NaN</v>
       </c>
       <c r="H76" s="5">
-        <v>0.0894</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -4077,16 +4068,16 @@
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D77" s="1">
-        <v>13492877440</v>
+        <v>2601947821</v>
       </c>
       <c r="E77" s="1">
-        <v>32352469472</v>
+        <v>6928377916</v>
       </c>
       <c r="F77" t="s">
         <v>42</v>
@@ -4095,7 +4086,7 @@
         <v>NaN</v>
       </c>
       <c r="H77" s="5">
-        <v>0.0894</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -4103,16 +4094,16 @@
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D78" s="1">
-        <v>6530798735</v>
+        <v>15089937312</v>
       </c>
       <c r="E78" s="1">
-        <v>14343878377</v>
+        <v>44451751213</v>
       </c>
       <c r="F78" t="s">
         <v>42</v>
@@ -4121,7 +4112,7 @@
         <v>NaN</v>
       </c>
       <c r="H78" s="5">
-        <v>1.1018999999999999</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -4129,16 +4120,16 @@
         <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D79" s="1">
-        <v>27357530009</v>
+        <v>3019107110</v>
       </c>
       <c r="E79" s="1">
-        <v>90231466119</v>
+        <v>10627945460</v>
       </c>
       <c r="F79" t="s">
         <v>42</v>
@@ -4147,7 +4138,7 @@
         <v>NaN</v>
       </c>
       <c r="H79" s="5">
-        <v>0.12710000000000002</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -4155,16 +4146,16 @@
         <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D80" s="1">
-        <v>4800107976</v>
+        <v>4384957618</v>
       </c>
       <c r="E80" s="1">
-        <v>15645123639</v>
+        <v>11811294891</v>
       </c>
       <c r="F80" t="s">
         <v>42</v>
@@ -4173,7 +4164,7 @@
         <v>NaN</v>
       </c>
       <c r="H80" s="5">
-        <v>0.195</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -4181,16 +4172,16 @@
         <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D81" s="1">
-        <v>2601947821</v>
+        <v>5597524598</v>
       </c>
       <c r="E81" s="1">
-        <v>7826480914</v>
+        <v>15904763483</v>
       </c>
       <c r="F81" t="s">
         <v>42</v>
@@ -4199,7 +4190,7 @@
         <v>NaN</v>
       </c>
       <c r="H81" s="5">
-        <v>0.195</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -4207,16 +4198,16 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
         <v>57</v>
       </c>
       <c r="D82" s="1">
-        <v>15089937312</v>
+        <v>1000000000</v>
       </c>
       <c r="E82" s="1">
-        <v>51358244668</v>
+        <v>2330215349</v>
       </c>
       <c r="F82" t="s">
         <v>42</v>
@@ -4225,7 +4216,7 @@
         <v>NaN</v>
       </c>
       <c r="H82" s="5">
-        <v>0.2051</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -4233,16 +4224,16 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D83" s="1">
-        <v>3019107110</v>
+        <v>1000000000</v>
       </c>
       <c r="E83" s="1">
-        <v>12455309447</v>
+        <v>2302140221</v>
       </c>
       <c r="F83" t="s">
         <v>42</v>
@@ -4251,7 +4242,7 @@
         <v>NaN</v>
       </c>
       <c r="H83" s="5">
-        <v>0.2051</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -4259,16 +4250,16 @@
         <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D84" s="1">
-        <v>4384957618</v>
+        <v>1000000000</v>
       </c>
       <c r="E84" s="1">
-        <v>13791567566</v>
+        <v>2297488877</v>
       </c>
       <c r="F84" t="s">
         <v>42</v>
@@ -4277,7 +4268,7 @@
         <v>NaN</v>
       </c>
       <c r="H84" s="5">
-        <v>0.2051</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -4285,16 +4276,16 @@
         <v>6</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D85" s="1">
-        <v>5597524598</v>
+        <v>1000000000</v>
       </c>
       <c r="E85" s="1">
-        <v>17686130717</v>
+        <v>2374031106</v>
       </c>
       <c r="F85" t="s">
         <v>42</v>
@@ -4303,7 +4294,7 @@
         <v>NaN</v>
       </c>
       <c r="H85" s="5">
-        <v>0.2051</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -4314,13 +4305,13 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D86" s="1">
         <v>1000000000</v>
       </c>
       <c r="E86" s="1">
-        <v>2706686839</v>
+        <v>2293703108</v>
       </c>
       <c r="F86" t="s">
         <v>42</v>
@@ -4329,7 +4320,7 @@
         <v>NaN</v>
       </c>
       <c r="H86" s="5">
-        <v>1.6469999999999998</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -4337,16 +4328,16 @@
         <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D87" s="1">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="E87" s="1">
-        <v>2669200613</v>
+        <v>5395348747</v>
       </c>
       <c r="F87" t="s">
         <v>42</v>
@@ -4355,7 +4346,7 @@
         <v>NaN</v>
       </c>
       <c r="H87" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -4363,16 +4354,16 @@
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D88" s="1">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="E88" s="1">
-        <v>2714567903</v>
+        <v>7802702228</v>
       </c>
       <c r="F88" t="s">
         <v>42</v>
@@ -4381,7 +4372,7 @@
         <v>NaN</v>
       </c>
       <c r="H88" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -4389,16 +4380,16 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C89" t="s">
         <v>47</v>
       </c>
       <c r="D89" s="1">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="E89" s="1">
-        <v>2782915914</v>
+        <v>6513458038</v>
       </c>
       <c r="F89" t="s">
         <v>42</v>
@@ -4407,7 +4398,7 @@
         <v>NaN</v>
       </c>
       <c r="H89" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -4415,16 +4406,16 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C90" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D90" s="1">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="E90" s="1">
-        <v>2703351908</v>
+        <v>6612291633</v>
       </c>
       <c r="F90" t="s">
         <v>42</v>
@@ -4433,7 +4424,7 @@
         <v>NaN</v>
       </c>
       <c r="H90" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -4444,13 +4435,13 @@
         <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D91" s="1">
         <v>3000000000</v>
       </c>
       <c r="E91" s="1">
-        <v>6050588599</v>
+        <v>8185169896</v>
       </c>
       <c r="F91" t="s">
         <v>42</v>
@@ -4459,7 +4450,7 @@
         <v>NaN</v>
       </c>
       <c r="H91" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -4470,13 +4461,13 @@
         <v>85</v>
       </c>
       <c r="C92" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D92" s="1">
         <v>3000000000</v>
       </c>
       <c r="E92" s="1">
-        <v>9020550899</v>
+        <v>3966553054</v>
       </c>
       <c r="F92" t="s">
         <v>42</v>
@@ -4485,7 +4476,7 @@
         <v>NaN</v>
       </c>
       <c r="H92" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -4496,13 +4487,13 @@
         <v>85</v>
       </c>
       <c r="C93" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D93" s="1">
         <v>3000000000</v>
       </c>
       <c r="E93" s="1">
-        <v>7844558558</v>
+        <v>6160765344</v>
       </c>
       <c r="F93" t="s">
         <v>42</v>
@@ -4511,24 +4502,24 @@
         <v>NaN</v>
       </c>
       <c r="H93" s="5">
-        <v>0.1632</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D94" s="1">
-        <v>3000000000</v>
+        <v>6006437351</v>
       </c>
       <c r="E94" s="1">
-        <v>8188549495</v>
+        <v>15506059249</v>
       </c>
       <c r="F94" t="s">
         <v>42</v>
@@ -4537,24 +4528,24 @@
         <v>NaN</v>
       </c>
       <c r="H94" s="5">
-        <v>0.1632</v>
+        <v>0.1689</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C95" t="s">
         <v>41</v>
       </c>
       <c r="D95" s="1">
-        <v>3000000000</v>
+        <v>10115864773</v>
       </c>
       <c r="E95" s="1">
-        <v>9442116713</v>
+        <v>25210400997</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
@@ -4563,24 +4554,24 @@
         <v>NaN</v>
       </c>
       <c r="H95" s="5">
-        <v>0.1632</v>
+        <v>0.12210000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D96" s="1">
-        <v>3000000000</v>
+        <v>1511398000</v>
       </c>
       <c r="E96" s="1">
-        <v>5294936141</v>
+        <v>3818517195</v>
       </c>
       <c r="F96" t="s">
         <v>42</v>
@@ -4589,24 +4580,24 @@
         <v>NaN</v>
       </c>
       <c r="H96" s="5">
-        <v>0.1632</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C97" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D97" s="1">
-        <v>3000000000</v>
+        <v>2849479862</v>
       </c>
       <c r="E97" s="1">
-        <v>6920131080</v>
+        <v>6954213572</v>
       </c>
       <c r="F97" t="s">
         <v>42</v>
@@ -4615,7 +4606,7 @@
         <v>NaN</v>
       </c>
       <c r="H97" s="5">
-        <v>0.1632</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -4623,16 +4614,16 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C98" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D98" s="1">
-        <v>6006437351</v>
+        <v>1370065623</v>
       </c>
       <c r="E98" s="1">
-        <v>17417419373</v>
+        <v>3603308455</v>
       </c>
       <c r="F98" t="s">
         <v>42</v>
@@ -4641,7 +4632,7 @@
         <v>NaN</v>
       </c>
       <c r="H98" s="5">
-        <v>0.1641</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -4649,16 +4640,16 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C99" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D99" s="1">
-        <v>10115864773</v>
+        <v>1045683565</v>
       </c>
       <c r="E99" s="1">
-        <v>28677443414</v>
+        <v>2468400903</v>
       </c>
       <c r="F99" t="s">
         <v>42</v>
@@ -4667,7 +4658,7 @@
         <v>NaN</v>
       </c>
       <c r="H99" s="5">
-        <v>0.1173</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -4678,13 +4669,13 @@
         <v>88</v>
       </c>
       <c r="C100" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D100" s="1">
-        <v>1511398000</v>
+        <v>1478582277</v>
       </c>
       <c r="E100" s="1">
-        <v>4627164442</v>
+        <v>2792913358</v>
       </c>
       <c r="F100" t="s">
         <v>42</v>
@@ -4693,7 +4684,7 @@
         <v>NaN</v>
       </c>
       <c r="H100" s="5">
-        <v>0.16269999999999998</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -4704,13 +4695,13 @@
         <v>88</v>
       </c>
       <c r="C101" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D101" s="1">
-        <v>2849479862</v>
+        <v>1492252844</v>
       </c>
       <c r="E101" s="1">
-        <v>8047220641</v>
+        <v>3454968458</v>
       </c>
       <c r="F101" t="s">
         <v>42</v>
@@ -4719,24 +4710,24 @@
         <v>NaN</v>
       </c>
       <c r="H101" s="5">
-        <v>0.16269999999999998</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C102" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D102" s="1">
-        <v>1370065623</v>
+        <v>3000000000</v>
       </c>
       <c r="E102" s="1">
-        <v>4036054782</v>
+        <v>3958912304</v>
       </c>
       <c r="F102" t="s">
         <v>42</v>
@@ -4745,24 +4736,24 @@
         <v>NaN</v>
       </c>
       <c r="H102" s="5">
-        <v>0.16269999999999998</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C103" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D103" s="1">
-        <v>1045683565</v>
+        <v>3000000000</v>
       </c>
       <c r="E103" s="1">
-        <v>2901665565</v>
+        <v>3975895368</v>
       </c>
       <c r="F103" t="s">
         <v>42</v>
@@ -4771,24 +4762,24 @@
         <v>NaN</v>
       </c>
       <c r="H103" s="5">
-        <v>0.16269999999999998</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C104" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D104" s="1">
-        <v>1478582277</v>
+        <v>400000000</v>
       </c>
       <c r="E104" s="1">
-        <v>3260399353</v>
+        <v>381187393</v>
       </c>
       <c r="F104" t="s">
         <v>42</v>
@@ -4797,24 +4788,24 @@
         <v>NaN</v>
       </c>
       <c r="H104" s="5">
-        <v>0.16269999999999998</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D105" s="1">
-        <v>1492252844</v>
+        <v>400000000</v>
       </c>
       <c r="E105" s="1">
-        <v>3842006225</v>
+        <v>333326095</v>
       </c>
       <c r="F105" t="s">
         <v>42</v>
@@ -4823,7 +4814,7 @@
         <v>NaN</v>
       </c>
       <c r="H105" s="5">
-        <v>0.16269999999999998</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -4831,16 +4822,16 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C106" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="D106" s="1">
-        <v>1500000000</v>
+        <v>400000000</v>
       </c>
       <c r="E106" s="1">
-        <v>2578748972</v>
+        <v>341538111</v>
       </c>
       <c r="F106" t="s">
         <v>42</v>
@@ -4849,111 +4840,7 @@
         <v>NaN</v>
       </c>
       <c r="H106" s="5">
-        <v>1.3033000000000001</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>8</v>
-      </c>
-      <c r="B107" t="s">
-        <v>71</v>
-      </c>
-      <c r="C107" t="s">
-        <v>41</v>
-      </c>
-      <c r="D107" s="1">
-        <v>1500000000</v>
-      </c>
-      <c r="E107" s="1">
-        <v>2578036800</v>
-      </c>
-      <c r="F107" t="s">
-        <v>42</v>
-      </c>
-      <c r="G107" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H107" s="5">
-        <v>1.3033000000000001</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>8</v>
-      </c>
-      <c r="B108" t="s">
-        <v>77</v>
-      </c>
-      <c r="C108" t="s">
-        <v>78</v>
-      </c>
-      <c r="D108" s="1">
-        <v>400000000</v>
-      </c>
-      <c r="E108" s="1">
-        <v>411779281</v>
-      </c>
-      <c r="F108" t="s">
-        <v>42</v>
-      </c>
-      <c r="G108" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H108" s="5">
-        <v>0.0037</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>8</v>
-      </c>
-      <c r="B109" t="s">
-        <v>77</v>
-      </c>
-      <c r="C109" t="s">
-        <v>63</v>
-      </c>
-      <c r="D109" s="1">
-        <v>400000000</v>
-      </c>
-      <c r="E109" s="1">
-        <v>393141106</v>
-      </c>
-      <c r="F109" t="s">
-        <v>42</v>
-      </c>
-      <c r="G109" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H109" s="5">
-        <v>0.0037</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>8</v>
-      </c>
-      <c r="B110" t="s">
-        <v>77</v>
-      </c>
-      <c r="C110" t="s">
-        <v>41</v>
-      </c>
-      <c r="D110" s="1">
-        <v>400000000</v>
-      </c>
-      <c r="E110" s="1">
-        <v>396870715</v>
-      </c>
-      <c r="F110" t="s">
-        <v>42</v>
-      </c>
-      <c r="G110" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H110" s="5">
-        <v>0.0037</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4964,7 +4851,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
@@ -5013,7 +4900,7 @@
         <v>900495639</v>
       </c>
       <c r="E2" s="1">
-        <v>904273863</v>
+        <v>897752897</v>
       </c>
       <c r="F2" t="s">
         <v>91</v>
@@ -5022,7 +4909,7 @@
         <v>NaN</v>
       </c>
       <c r="H2" s="5">
-        <v>0.0022</v>
+        <v>-0.0048</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -5039,7 +4926,7 @@
         <v>1338657958</v>
       </c>
       <c r="E3" s="1">
-        <v>1341820410</v>
+        <v>1334569313</v>
       </c>
       <c r="F3" t="s">
         <v>91</v>
@@ -5048,7 +4935,7 @@
         <v>NaN</v>
       </c>
       <c r="H3" s="5">
-        <v>0.0022</v>
+        <v>-0.0048</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -5065,7 +4952,7 @@
         <v>2408967886</v>
       </c>
       <c r="E4" s="1">
-        <v>2387519613</v>
+        <v>2364612047</v>
       </c>
       <c r="F4" t="s">
         <v>91</v>
@@ -5074,7 +4961,7 @@
         <v>NaN</v>
       </c>
       <c r="H4" s="5">
-        <v>-0.0684</v>
+        <v>-0.07490000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -5088,10 +4975,10 @@
         <v>76</v>
       </c>
       <c r="D5" s="1">
-        <v>1834805538</v>
+        <v>2034805538</v>
       </c>
       <c r="E5" s="1">
-        <v>3376689378</v>
+        <v>3608745347</v>
       </c>
       <c r="F5" t="s">
         <v>91</v>
@@ -5100,7 +4987,7 @@
         <v>NaN</v>
       </c>
       <c r="H5" s="5">
-        <v>0.6742</v>
+        <v>0.6754000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -5117,7 +5004,7 @@
         <v>1585120883</v>
       </c>
       <c r="E6" s="1">
-        <v>2650009158</v>
+        <v>2656287171</v>
       </c>
       <c r="F6" t="s">
         <v>91</v>
@@ -5126,7 +5013,7 @@
         <v>NaN</v>
       </c>
       <c r="H6" s="5">
-        <v>0.6742</v>
+        <v>0.6754000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -5143,7 +5030,7 @@
         <v>656507639</v>
       </c>
       <c r="E7" s="1">
-        <v>1293736356</v>
+        <v>1304933202</v>
       </c>
       <c r="F7" t="s">
         <v>91</v>
@@ -5152,7 +5039,7 @@
         <v>NaN</v>
       </c>
       <c r="H7" s="5">
-        <v>0.927</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -5169,7 +5056,7 @@
         <v>1321092316</v>
       </c>
       <c r="E8" s="1">
-        <v>2354366982</v>
+        <v>2348868079</v>
       </c>
       <c r="F8" t="s">
         <v>91</v>
@@ -5178,7 +5065,7 @@
         <v>NaN</v>
       </c>
       <c r="H8" s="5">
-        <v>0.8691</v>
+        <v>0.8704999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -5195,7 +5082,7 @@
         <v>1783655177</v>
       </c>
       <c r="E9" s="1">
-        <v>3169367035</v>
+        <v>3175972208</v>
       </c>
       <c r="F9" t="s">
         <v>91</v>
@@ -5204,7 +5091,7 @@
         <v>NaN</v>
       </c>
       <c r="H9" s="5">
-        <v>0.8691</v>
+        <v>0.8704999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -5218,10 +5105,10 @@
         <v>100</v>
       </c>
       <c r="D10" s="1">
-        <v>934565605</v>
+        <v>1683240295</v>
       </c>
       <c r="E10" s="1">
-        <v>1683240295</v>
+        <v>1714089252</v>
       </c>
       <c r="F10" t="s">
         <v>91</v>
@@ -5230,7 +5117,7 @@
         <v>NaN</v>
       </c>
       <c r="H10" s="5">
-        <v>0.7609</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -5244,10 +5131,10 @@
         <v>76</v>
       </c>
       <c r="D11" s="1">
-        <v>939726931</v>
+        <v>1687228552</v>
       </c>
       <c r="E11" s="1">
-        <v>1687228552</v>
+        <v>1711777799</v>
       </c>
       <c r="F11" t="s">
         <v>91</v>
@@ -5256,7 +5143,7 @@
         <v>NaN</v>
       </c>
       <c r="H11" s="5">
-        <v>0.7609</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -5273,7 +5160,7 @@
         <v>2555932432</v>
       </c>
       <c r="E12" s="1">
-        <v>2862400816</v>
+        <v>2941839542</v>
       </c>
       <c r="F12" t="s">
         <v>91</v>
@@ -5299,7 +5186,7 @@
         <v>1417127452</v>
       </c>
       <c r="E13" s="1">
-        <v>1509443756</v>
+        <v>1552479450</v>
       </c>
       <c r="F13" t="s">
         <v>91</v>
@@ -5325,7 +5212,7 @@
         <v>618843493</v>
       </c>
       <c r="E14" s="1">
-        <v>777512698</v>
+        <v>769778438</v>
       </c>
       <c r="F14" t="s">
         <v>91</v>
@@ -5334,7 +5221,7 @@
         <v>NaN</v>
       </c>
       <c r="H14" s="5">
-        <v>0.2836</v>
+        <v>0.2728</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -5351,7 +5238,7 @@
         <v>1263392347</v>
       </c>
       <c r="E15" s="1">
-        <v>1620549706</v>
+        <v>1666508211</v>
       </c>
       <c r="F15" t="s">
         <v>91</v>
@@ -5360,7 +5247,7 @@
         <v>NaN</v>
       </c>
       <c r="H15" s="5">
-        <v>0.2961</v>
+        <v>0.3337</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -5377,7 +5264,7 @@
         <v>1352011599</v>
       </c>
       <c r="E16" s="1">
-        <v>1731937050</v>
+        <v>1781352129</v>
       </c>
       <c r="F16" t="s">
         <v>91</v>
@@ -5386,7 +5273,7 @@
         <v>NaN</v>
       </c>
       <c r="H16" s="5">
-        <v>0.2961</v>
+        <v>0.3337</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -5403,7 +5290,7 @@
         <v>1796000834</v>
       </c>
       <c r="E17" s="1">
-        <v>2103142921</v>
+        <v>2098200969</v>
       </c>
       <c r="F17" t="s">
         <v>91</v>
@@ -5412,7 +5299,7 @@
         <v>NaN</v>
       </c>
       <c r="H17" s="5">
-        <v>0.444</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -5429,7 +5316,7 @@
         <v>1164480846</v>
       </c>
       <c r="E18" s="1">
-        <v>1718286608</v>
+        <v>1785160367</v>
       </c>
       <c r="F18" t="s">
         <v>91</v>
@@ -5438,7 +5325,7 @@
         <v>NaN</v>
       </c>
       <c r="H18" s="5">
-        <v>0.444</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -5455,7 +5342,7 @@
         <v>1507914919</v>
       </c>
       <c r="E19" s="1">
-        <v>2214513943</v>
+        <v>2290978822</v>
       </c>
       <c r="F19" t="s">
         <v>91</v>
@@ -5464,7 +5351,7 @@
         <v>NaN</v>
       </c>
       <c r="H19" s="5">
-        <v>0.444</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -5481,7 +5368,7 @@
         <v>1186559371</v>
       </c>
       <c r="E20" s="1">
-        <v>1368088535</v>
+        <v>1352096519</v>
       </c>
       <c r="F20" t="s">
         <v>91</v>
@@ -5490,7 +5377,7 @@
         <v>NaN</v>
       </c>
       <c r="H20" s="5">
-        <v>0.1496</v>
+        <v>0.1376</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -5507,7 +5394,7 @@
         <v>670392768</v>
       </c>
       <c r="E21" s="1">
-        <v>768686725</v>
+        <v>760653316</v>
       </c>
       <c r="F21" t="s">
         <v>91</v>
@@ -5516,7 +5403,7 @@
         <v>NaN</v>
       </c>
       <c r="H21" s="5">
-        <v>0.1496</v>
+        <v>0.1376</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -5533,7 +5420,7 @@
         <v>941561542</v>
       </c>
       <c r="E22" s="1">
-        <v>1077741805</v>
+        <v>1065528056</v>
       </c>
       <c r="F22" t="s">
         <v>91</v>
@@ -5542,7 +5429,7 @@
         <v>NaN</v>
       </c>
       <c r="H22" s="5">
-        <v>0.1496</v>
+        <v>0.1376</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -5559,7 +5446,7 @@
         <v>3222313413</v>
       </c>
       <c r="E23" s="1">
-        <v>3975580764</v>
+        <v>3904111203</v>
       </c>
       <c r="F23" t="s">
         <v>91</v>
@@ -5568,7 +5455,7 @@
         <v>NaN</v>
       </c>
       <c r="H23" s="5">
-        <v>0.2305</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -5585,7 +5472,7 @@
         <v>3208355339</v>
       </c>
       <c r="E24" s="1">
-        <v>3924793719</v>
+        <v>3866001108</v>
       </c>
       <c r="F24" t="s">
         <v>91</v>
@@ -5594,7 +5481,7 @@
         <v>NaN</v>
       </c>
       <c r="H24" s="5">
-        <v>0.2305</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -5611,7 +5498,7 @@
         <v>3189006741</v>
       </c>
       <c r="E25" s="1">
-        <v>3922563590</v>
+        <v>3853735625</v>
       </c>
       <c r="F25" t="s">
         <v>91</v>
@@ -5620,7 +5507,7 @@
         <v>NaN</v>
       </c>
       <c r="H25" s="5">
-        <v>0.2305</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -5637,7 +5524,7 @@
         <v>1159305130</v>
       </c>
       <c r="E26" s="1">
-        <v>1314198402</v>
+        <v>1318692011</v>
       </c>
       <c r="F26" t="s">
         <v>91</v>
@@ -5646,7 +5533,7 @@
         <v>NaN</v>
       </c>
       <c r="H26" s="5">
-        <v>0.1182</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -5663,7 +5550,7 @@
         <v>1668471152</v>
       </c>
       <c r="E27" s="1">
-        <v>1837050463</v>
+        <v>1836404740</v>
       </c>
       <c r="F27" t="s">
         <v>91</v>
@@ -5672,7 +5559,7 @@
         <v>NaN</v>
       </c>
       <c r="H27" s="5">
-        <v>0.1182</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -5683,13 +5570,13 @@
         <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="D28" s="1">
-        <v>878698278</v>
+        <v>949175052</v>
       </c>
       <c r="E28" s="1">
-        <v>1216881012</v>
+        <v>1656860388</v>
       </c>
       <c r="F28" t="s">
         <v>91</v>
@@ -5698,7 +5585,7 @@
         <v>NaN</v>
       </c>
       <c r="H28" s="5">
-        <v>0</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -5706,16 +5593,16 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D29" s="1">
-        <v>1645715430</v>
+        <v>641552002</v>
       </c>
       <c r="E29" s="1">
-        <v>2051054273</v>
+        <v>1179392915</v>
       </c>
       <c r="F29" t="s">
         <v>91</v>
@@ -5724,7 +5611,7 @@
         <v>NaN</v>
       </c>
       <c r="H29" s="5">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -5732,16 +5619,16 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
         <v>123</v>
       </c>
       <c r="D30" s="1">
-        <v>1175711371</v>
+        <v>848715051</v>
       </c>
       <c r="E30" s="1">
-        <v>1508632702</v>
+        <v>1520309377</v>
       </c>
       <c r="F30" t="s">
         <v>91</v>
@@ -5750,7 +5637,7 @@
         <v>NaN</v>
       </c>
       <c r="H30" s="5">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -5758,16 +5645,16 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D31" s="1">
-        <v>315326657</v>
+        <v>849045562</v>
       </c>
       <c r="E31" s="1">
-        <v>422609458</v>
+        <v>1538613293</v>
       </c>
       <c r="F31" t="s">
         <v>91</v>
@@ -5776,7 +5663,7 @@
         <v>NaN</v>
       </c>
       <c r="H31" s="5">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -5784,16 +5671,16 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="D32" s="1">
-        <v>949175052</v>
+        <v>762047560</v>
       </c>
       <c r="E32" s="1">
-        <v>1718850535</v>
+        <v>1408516487</v>
       </c>
       <c r="F32" t="s">
         <v>91</v>
@@ -5802,7 +5689,7 @@
         <v>NaN</v>
       </c>
       <c r="H32" s="5">
-        <v>0.7368000000000001</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -5810,16 +5697,16 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="D33" s="1">
-        <v>641552002</v>
+        <v>427360620</v>
       </c>
       <c r="E33" s="1">
-        <v>1185258602</v>
+        <v>523380643</v>
       </c>
       <c r="F33" t="s">
         <v>91</v>
@@ -5828,7 +5715,7 @@
         <v>NaN</v>
       </c>
       <c r="H33" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -5836,16 +5723,16 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" t="s">
         <v>126</v>
       </c>
-      <c r="C34" t="s">
-        <v>123</v>
-      </c>
       <c r="D34" s="1">
-        <v>848715051</v>
+        <v>905211657</v>
       </c>
       <c r="E34" s="1">
-        <v>1521841215</v>
+        <v>1164994046</v>
       </c>
       <c r="F34" t="s">
         <v>91</v>
@@ -5854,7 +5741,7 @@
         <v>NaN</v>
       </c>
       <c r="H34" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -5862,16 +5749,16 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="D35" s="1">
-        <v>849045562</v>
+        <v>1039618153</v>
       </c>
       <c r="E35" s="1">
-        <v>1540819815</v>
+        <v>1287714646</v>
       </c>
       <c r="F35" t="s">
         <v>91</v>
@@ -5880,7 +5767,7 @@
         <v>NaN</v>
       </c>
       <c r="H35" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -5888,16 +5775,16 @@
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D36" s="1">
-        <v>762047560</v>
+        <v>1006698949</v>
       </c>
       <c r="E36" s="1">
-        <v>1412257857</v>
+        <v>1523316004</v>
       </c>
       <c r="F36" t="s">
         <v>91</v>
@@ -5906,7 +5793,7 @@
         <v>NaN</v>
       </c>
       <c r="H36" s="5">
-        <v>0.9181999999999999</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -5914,16 +5801,16 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D37" s="1">
-        <v>427360620</v>
+        <v>867219463</v>
       </c>
       <c r="E37" s="1">
-        <v>522878367</v>
+        <v>1147513598</v>
       </c>
       <c r="F37" t="s">
         <v>91</v>
@@ -5932,7 +5819,7 @@
         <v>NaN</v>
       </c>
       <c r="H37" s="5">
-        <v>0</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -5940,16 +5827,16 @@
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
         <v>129</v>
       </c>
       <c r="D38" s="1">
-        <v>905211657</v>
+        <v>938885217</v>
       </c>
       <c r="E38" s="1">
-        <v>1162781169</v>
+        <v>1316573361</v>
       </c>
       <c r="F38" t="s">
         <v>91</v>
@@ -5958,7 +5845,7 @@
         <v>NaN</v>
       </c>
       <c r="H38" s="5">
-        <v>0</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -5966,16 +5853,16 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="D39" s="1">
-        <v>1039618153</v>
+        <v>806462703</v>
       </c>
       <c r="E39" s="1">
-        <v>1288075614</v>
+        <v>1142750317</v>
       </c>
       <c r="F39" t="s">
         <v>91</v>
@@ -5984,7 +5871,7 @@
         <v>NaN</v>
       </c>
       <c r="H39" s="5">
-        <v>0</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -5992,16 +5879,16 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="D40" s="1">
-        <v>1006698949</v>
+        <v>559865985</v>
       </c>
       <c r="E40" s="1">
-        <v>1499061173</v>
+        <v>792418771</v>
       </c>
       <c r="F40" t="s">
         <v>91</v>
@@ -6010,7 +5897,7 @@
         <v>NaN</v>
       </c>
       <c r="H40" s="5">
-        <v>0.373</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -6018,16 +5905,16 @@
         <v>5</v>
       </c>
       <c r="B41" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" t="s">
         <v>131</v>
       </c>
-      <c r="C41" t="s">
-        <v>110</v>
-      </c>
       <c r="D41" s="1">
-        <v>867219463</v>
+        <v>506416368</v>
       </c>
       <c r="E41" s="1">
-        <v>1138462866</v>
+        <v>697308846</v>
       </c>
       <c r="F41" t="s">
         <v>91</v>
@@ -6036,7 +5923,7 @@
         <v>NaN</v>
       </c>
       <c r="H41" s="5">
-        <v>0.373</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6044,16 +5931,16 @@
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D42" s="1">
-        <v>938885217</v>
+        <v>441937598</v>
       </c>
       <c r="E42" s="1">
-        <v>1306411183</v>
+        <v>621979937</v>
       </c>
       <c r="F42" t="s">
         <v>91</v>
@@ -6062,7 +5949,7 @@
         <v>NaN</v>
       </c>
       <c r="H42" s="5">
-        <v>0.373</v>
+        <v>0.4412</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -6070,16 +5957,16 @@
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D43" s="1">
-        <v>806462703</v>
+        <v>1059063706</v>
       </c>
       <c r="E43" s="1">
-        <v>1089442729</v>
+        <v>1049063723</v>
       </c>
       <c r="F43" t="s">
         <v>91</v>
@@ -6088,7 +5975,7 @@
         <v>NaN</v>
       </c>
       <c r="H43" s="5">
-        <v>0.373</v>
+        <v>-0.0070999999999999995</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -6096,16 +5983,16 @@
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="D44" s="1">
-        <v>559865985</v>
+        <v>558802476</v>
       </c>
       <c r="E44" s="1">
-        <v>755063861</v>
+        <v>554364692</v>
       </c>
       <c r="F44" t="s">
         <v>91</v>
@@ -6114,7 +6001,7 @@
         <v>NaN</v>
       </c>
       <c r="H44" s="5">
-        <v>0.373</v>
+        <v>-0.0070999999999999995</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -6122,16 +6009,16 @@
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="D45" s="1">
-        <v>506416368</v>
+        <v>674765647</v>
       </c>
       <c r="E45" s="1">
-        <v>666220874</v>
+        <v>668540853</v>
       </c>
       <c r="F45" t="s">
         <v>91</v>
@@ -6140,7 +6027,7 @@
         <v>NaN</v>
       </c>
       <c r="H45" s="5">
-        <v>0.373</v>
+        <v>-0.0070999999999999995</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -6148,16 +6035,16 @@
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="D46" s="1">
-        <v>441937598</v>
+        <v>430000000</v>
       </c>
       <c r="E46" s="1">
-        <v>589558972</v>
+        <v>578472486</v>
       </c>
       <c r="F46" t="s">
         <v>91</v>
@@ -6166,7 +6053,7 @@
         <v>NaN</v>
       </c>
       <c r="H46" s="5">
-        <v>0.373</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -6174,16 +6061,16 @@
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
         <v>136</v>
       </c>
       <c r="D47" s="1">
-        <v>1059063706</v>
+        <v>700000000</v>
       </c>
       <c r="E47" s="1">
-        <v>1066146323</v>
+        <v>957679882</v>
       </c>
       <c r="F47" t="s">
         <v>91</v>
@@ -6192,7 +6079,7 @@
         <v>NaN</v>
       </c>
       <c r="H47" s="5">
-        <v>0.008100000000000001</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -6200,16 +6087,16 @@
         <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D48" s="1">
-        <v>558802476</v>
+        <v>350000000</v>
       </c>
       <c r="E48" s="1">
-        <v>563258369</v>
+        <v>487745804</v>
       </c>
       <c r="F48" t="s">
         <v>91</v>
@@ -6218,7 +6105,7 @@
         <v>NaN</v>
       </c>
       <c r="H48" s="5">
-        <v>0.008100000000000001</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -6226,16 +6113,16 @@
         <v>5</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D49" s="1">
-        <v>674765647</v>
+        <v>430000000</v>
       </c>
       <c r="E49" s="1">
-        <v>679241622</v>
+        <v>583830731</v>
       </c>
       <c r="F49" t="s">
         <v>91</v>
@@ -6244,7 +6131,7 @@
         <v>NaN</v>
       </c>
       <c r="H49" s="5">
-        <v>0.008100000000000001</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -6255,13 +6142,13 @@
         <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D50" s="1">
-        <v>430000000</v>
+        <v>400000000</v>
       </c>
       <c r="E50" s="1">
-        <v>580461284</v>
+        <v>515794235</v>
       </c>
       <c r="F50" t="s">
         <v>91</v>
@@ -6270,7 +6157,7 @@
         <v>NaN</v>
       </c>
       <c r="H50" s="5">
-        <v>0.39149999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -6281,13 +6168,13 @@
         <v>137</v>
       </c>
       <c r="C51" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="D51" s="1">
-        <v>700000000</v>
+        <v>400000000</v>
       </c>
       <c r="E51" s="1">
-        <v>959489456</v>
+        <v>487389833</v>
       </c>
       <c r="F51" t="s">
         <v>91</v>
@@ -6296,7 +6183,7 @@
         <v>NaN</v>
       </c>
       <c r="H51" s="5">
-        <v>0.39149999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -6307,13 +6194,13 @@
         <v>137</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D52" s="1">
-        <v>350000000</v>
+        <v>400000000</v>
       </c>
       <c r="E52" s="1">
-        <v>493495061</v>
+        <v>491940624</v>
       </c>
       <c r="F52" t="s">
         <v>91</v>
@@ -6322,7 +6209,7 @@
         <v>NaN</v>
       </c>
       <c r="H52" s="5">
-        <v>0.39149999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -6333,13 +6220,13 @@
         <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D53" s="1">
-        <v>430000000</v>
+        <v>400000000</v>
       </c>
       <c r="E53" s="1">
-        <v>577076771</v>
+        <v>538651033</v>
       </c>
       <c r="F53" t="s">
         <v>91</v>
@@ -6348,7 +6235,7 @@
         <v>NaN</v>
       </c>
       <c r="H53" s="5">
-        <v>0.39149999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -6356,16 +6243,16 @@
         <v>5</v>
       </c>
       <c r="B54" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" t="s">
         <v>140</v>
-      </c>
-      <c r="C54" t="s">
-        <v>129</v>
       </c>
       <c r="D54" s="1">
         <v>400000000</v>
       </c>
       <c r="E54" s="1">
-        <v>530861963</v>
+        <v>509014558</v>
       </c>
       <c r="F54" t="s">
         <v>91</v>
@@ -6382,16 +6269,16 @@
         <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="D55" s="1">
         <v>400000000</v>
       </c>
       <c r="E55" s="1">
-        <v>490825152</v>
+        <v>617340295</v>
       </c>
       <c r="F55" t="s">
         <v>91</v>
@@ -6408,16 +6295,16 @@
         <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D56" s="1">
         <v>400000000</v>
       </c>
       <c r="E56" s="1">
-        <v>491407437</v>
+        <v>593041556</v>
       </c>
       <c r="F56" t="s">
         <v>91</v>
@@ -6434,16 +6321,16 @@
         <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D57" s="1">
         <v>400000000</v>
       </c>
       <c r="E57" s="1">
-        <v>538748367</v>
+        <v>603262281</v>
       </c>
       <c r="F57" t="s">
         <v>91</v>
@@ -6460,16 +6347,16 @@
         <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D58" s="1">
         <v>400000000</v>
       </c>
       <c r="E58" s="1">
-        <v>512385696</v>
+        <v>580538915</v>
       </c>
       <c r="F58" t="s">
         <v>91</v>
@@ -6486,16 +6373,16 @@
         <v>5</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C59" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="D59" s="1">
         <v>400000000</v>
       </c>
       <c r="E59" s="1">
-        <v>625894366</v>
+        <v>616317921</v>
       </c>
       <c r="F59" t="s">
         <v>91</v>
@@ -6515,13 +6402,13 @@
         <v>144</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D60" s="1">
-        <v>400000000</v>
+        <v>600000000</v>
       </c>
       <c r="E60" s="1">
-        <v>599547682</v>
+        <v>687485218</v>
       </c>
       <c r="F60" t="s">
         <v>91</v>
@@ -6541,13 +6428,13 @@
         <v>144</v>
       </c>
       <c r="C61" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D61" s="1">
-        <v>400000000</v>
+        <v>500000000</v>
       </c>
       <c r="E61" s="1">
-        <v>606502238</v>
+        <v>585326949</v>
       </c>
       <c r="F61" t="s">
         <v>91</v>
@@ -6567,13 +6454,13 @@
         <v>144</v>
       </c>
       <c r="C62" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="D62" s="1">
-        <v>400000000</v>
+        <v>500000000</v>
       </c>
       <c r="E62" s="1">
-        <v>578856765</v>
+        <v>592402750</v>
       </c>
       <c r="F62" t="s">
         <v>91</v>
@@ -6593,13 +6480,13 @@
         <v>144</v>
       </c>
       <c r="C63" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="D63" s="1">
-        <v>400000000</v>
+        <v>600000000</v>
       </c>
       <c r="E63" s="1">
-        <v>621800879</v>
+        <v>688857784</v>
       </c>
       <c r="F63" t="s">
         <v>91</v>
@@ -6616,16 +6503,16 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="D64" s="1">
-        <v>600000000</v>
+        <v>500000000</v>
       </c>
       <c r="E64" s="1">
-        <v>689474316</v>
+        <v>557844230</v>
       </c>
       <c r="F64" t="s">
         <v>91</v>
@@ -6642,16 +6529,16 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="D65" s="1">
         <v>500000000</v>
       </c>
       <c r="E65" s="1">
-        <v>587169093</v>
+        <v>574633525</v>
       </c>
       <c r="F65" t="s">
         <v>91</v>
@@ -6671,13 +6558,13 @@
         <v>146</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="D66" s="1">
-        <v>500000000</v>
+        <v>400000000</v>
       </c>
       <c r="E66" s="1">
-        <v>593735886</v>
+        <v>532527714</v>
       </c>
       <c r="F66" t="s">
         <v>91</v>
@@ -6686,7 +6573,7 @@
         <v>NaN</v>
       </c>
       <c r="H66" s="5">
-        <v>0</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -6697,13 +6584,13 @@
         <v>146</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="D67" s="1">
-        <v>600000000</v>
+        <v>400000000</v>
       </c>
       <c r="E67" s="1">
-        <v>685961345</v>
+        <v>544159304</v>
       </c>
       <c r="F67" t="s">
         <v>91</v>
@@ -6712,7 +6599,7 @@
         <v>NaN</v>
       </c>
       <c r="H67" s="5">
-        <v>0</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -6723,13 +6610,13 @@
         <v>146</v>
       </c>
       <c r="C68" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="D68" s="1">
-        <v>500000000</v>
+        <v>400000000</v>
       </c>
       <c r="E68" s="1">
-        <v>557731817</v>
+        <v>546139746</v>
       </c>
       <c r="F68" t="s">
         <v>91</v>
@@ -6738,7 +6625,7 @@
         <v>NaN</v>
       </c>
       <c r="H68" s="5">
-        <v>0</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -6749,13 +6636,13 @@
         <v>146</v>
       </c>
       <c r="C69" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D69" s="1">
-        <v>500000000</v>
+        <v>400000000</v>
       </c>
       <c r="E69" s="1">
-        <v>573497628</v>
+        <v>546102748</v>
       </c>
       <c r="F69" t="s">
         <v>91</v>
@@ -6764,7 +6651,7 @@
         <v>NaN</v>
       </c>
       <c r="H69" s="5">
-        <v>0</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -6775,13 +6662,13 @@
         <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="D70" s="1">
         <v>400000000</v>
       </c>
       <c r="E70" s="1">
-        <v>533036158</v>
+        <v>450426531</v>
       </c>
       <c r="F70" t="s">
         <v>91</v>
@@ -6790,7 +6677,7 @@
         <v>NaN</v>
       </c>
       <c r="H70" s="5">
-        <v>0.434</v>
+        <v>0.1201</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -6801,13 +6688,13 @@
         <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="D71" s="1">
         <v>400000000</v>
       </c>
       <c r="E71" s="1">
-        <v>543970609</v>
+        <v>458409894</v>
       </c>
       <c r="F71" t="s">
         <v>91</v>
@@ -6816,7 +6703,7 @@
         <v>NaN</v>
       </c>
       <c r="H71" s="5">
-        <v>0.434</v>
+        <v>0.1201</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -6827,13 +6714,13 @@
         <v>148</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D72" s="1">
         <v>400000000</v>
       </c>
       <c r="E72" s="1">
-        <v>544895177</v>
+        <v>454110042</v>
       </c>
       <c r="F72" t="s">
         <v>91</v>
@@ -6842,7 +6729,7 @@
         <v>NaN</v>
       </c>
       <c r="H72" s="5">
-        <v>0.434</v>
+        <v>0.1201</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -6853,13 +6740,13 @@
         <v>148</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D73" s="1">
         <v>400000000</v>
       </c>
       <c r="E73" s="1">
-        <v>545430771</v>
+        <v>453176548</v>
       </c>
       <c r="F73" t="s">
         <v>91</v>
@@ -6868,7 +6755,7 @@
         <v>NaN</v>
       </c>
       <c r="H73" s="5">
-        <v>0.434</v>
+        <v>0.1201</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -6885,7 +6772,7 @@
         <v>400000000</v>
       </c>
       <c r="E74" s="1">
-        <v>437857077</v>
+        <v>423356755</v>
       </c>
       <c r="F74" t="s">
         <v>91</v>
@@ -6894,7 +6781,7 @@
         <v>NaN</v>
       </c>
       <c r="H74" s="5">
-        <v>0.1201</v>
+        <v>0.1043</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -6911,7 +6798,7 @@
         <v>400000000</v>
       </c>
       <c r="E75" s="1">
-        <v>446072975</v>
+        <v>421747465</v>
       </c>
       <c r="F75" t="s">
         <v>91</v>
@@ -6920,7 +6807,7 @@
         <v>NaN</v>
       </c>
       <c r="H75" s="5">
-        <v>0.1201</v>
+        <v>0.1043</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -6931,13 +6818,13 @@
         <v>150</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D76" s="1">
         <v>400000000</v>
       </c>
       <c r="E76" s="1">
-        <v>443552741</v>
+        <v>421814640</v>
       </c>
       <c r="F76" t="s">
         <v>91</v>
@@ -6946,7 +6833,7 @@
         <v>NaN</v>
       </c>
       <c r="H76" s="5">
-        <v>0.1201</v>
+        <v>0.1043</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -6957,13 +6844,13 @@
         <v>150</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D77" s="1">
         <v>400000000</v>
       </c>
       <c r="E77" s="1">
-        <v>442377627</v>
+        <v>422040147</v>
       </c>
       <c r="F77" t="s">
         <v>91</v>
@@ -6972,24 +6859,24 @@
         <v>NaN</v>
       </c>
       <c r="H77" s="5">
-        <v>0.1201</v>
+        <v>0.1043</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="D78" s="1">
-        <v>400000000</v>
+        <v>753144454</v>
       </c>
       <c r="E78" s="1">
-        <v>420213973</v>
+        <v>1000473186</v>
       </c>
       <c r="F78" t="s">
         <v>91</v>
@@ -6998,24 +6885,24 @@
         <v>NaN</v>
       </c>
       <c r="H78" s="5">
-        <v>0.0969</v>
+        <v>0.2753</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C79" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="D79" s="1">
-        <v>400000000</v>
+        <v>1003724736</v>
       </c>
       <c r="E79" s="1">
-        <v>418936760</v>
+        <v>955925026</v>
       </c>
       <c r="F79" t="s">
         <v>91</v>
@@ -7024,24 +6911,24 @@
         <v>NaN</v>
       </c>
       <c r="H79" s="5">
-        <v>0.0969</v>
+        <v>-0.07490000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C80" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D80" s="1">
-        <v>400000000</v>
+        <v>1018693762</v>
       </c>
       <c r="E80" s="1">
-        <v>419048449</v>
+        <v>951725548</v>
       </c>
       <c r="F80" t="s">
         <v>91</v>
@@ -7050,24 +6937,24 @@
         <v>NaN</v>
       </c>
       <c r="H80" s="5">
-        <v>0.0969</v>
+        <v>-0.07490000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C81" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="D81" s="1">
-        <v>400000000</v>
+        <v>456987544</v>
       </c>
       <c r="E81" s="1">
-        <v>419200289</v>
+        <v>1504388734</v>
       </c>
       <c r="F81" t="s">
         <v>91</v>
@@ -7076,7 +6963,7 @@
         <v>NaN</v>
       </c>
       <c r="H81" s="5">
-        <v>0.0969</v>
+        <v>0.6754000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -7084,16 +6971,16 @@
         <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C82" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D82" s="1">
-        <v>753144454</v>
+        <v>181124998</v>
       </c>
       <c r="E82" s="1">
-        <v>1016210408</v>
+        <v>388876019</v>
       </c>
       <c r="F82" t="s">
         <v>91</v>
@@ -7102,7 +6989,7 @@
         <v>NaN</v>
       </c>
       <c r="H82" s="5">
-        <v>0.281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -7110,16 +6997,16 @@
         <v>6</v>
       </c>
       <c r="B83" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D83" s="1">
-        <v>1003724736</v>
+        <v>303753501</v>
       </c>
       <c r="E83" s="1">
-        <v>965136838</v>
+        <v>308345333</v>
       </c>
       <c r="F83" t="s">
         <v>91</v>
@@ -7128,7 +7015,7 @@
         <v>NaN</v>
       </c>
       <c r="H83" s="5">
-        <v>-0.0684</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -7136,16 +7023,16 @@
         <v>6</v>
       </c>
       <c r="B84" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C84" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D84" s="1">
-        <v>1018693762</v>
+        <v>456179013</v>
       </c>
       <c r="E84" s="1">
-        <v>959369331</v>
+        <v>464380516</v>
       </c>
       <c r="F84" t="s">
         <v>91</v>
@@ -7154,7 +7041,7 @@
         <v>NaN</v>
       </c>
       <c r="H84" s="5">
-        <v>-0.0684</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -7165,13 +7052,13 @@
         <v>157</v>
       </c>
       <c r="C85" t="s">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="D85" s="1">
-        <v>956987544</v>
+        <v>361201485</v>
       </c>
       <c r="E85" s="1">
-        <v>1997179617</v>
+        <v>367521178</v>
       </c>
       <c r="F85" t="s">
         <v>91</v>
@@ -7180,7 +7067,7 @@
         <v>NaN</v>
       </c>
       <c r="H85" s="5">
-        <v>0.6742</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -7188,16 +7075,16 @@
         <v>6</v>
       </c>
       <c r="B86" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C86" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="D86" s="1">
-        <v>181124998</v>
+        <v>405779245</v>
       </c>
       <c r="E86" s="1">
-        <v>385583924</v>
+        <v>412290581</v>
       </c>
       <c r="F86" t="s">
         <v>91</v>
@@ -7206,7 +7093,7 @@
         <v>NaN</v>
       </c>
       <c r="H86" s="5">
-        <v>0</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -7220,10 +7107,10 @@
         <v>76</v>
       </c>
       <c r="D87" s="1">
-        <v>54997166</v>
+        <v>751993706</v>
       </c>
       <c r="E87" s="1">
-        <v>303753501</v>
+        <v>1013212614</v>
       </c>
       <c r="F87" t="s">
         <v>91</v>
@@ -7232,7 +7119,7 @@
         <v>NaN</v>
       </c>
       <c r="H87" s="5">
-        <v>0.7827</v>
+        <v>0.3337</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -7240,16 +7127,16 @@
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C88" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D88" s="1">
-        <v>160436214</v>
+        <v>414056068</v>
       </c>
       <c r="E88" s="1">
-        <v>456179013</v>
+        <v>485988414</v>
       </c>
       <c r="F88" t="s">
         <v>91</v>
@@ -7258,7 +7145,7 @@
         <v>NaN</v>
       </c>
       <c r="H88" s="5">
-        <v>0.7827</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -7266,16 +7153,16 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C89" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="D89" s="1">
-        <v>108879836</v>
+        <v>315296707</v>
       </c>
       <c r="E89" s="1">
-        <v>361201485</v>
+        <v>485100246</v>
       </c>
       <c r="F89" t="s">
         <v>91</v>
@@ -7284,7 +7171,7 @@
         <v>NaN</v>
       </c>
       <c r="H89" s="5">
-        <v>0.7827</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -7292,16 +7179,16 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C90" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="D90" s="1">
-        <v>110147608</v>
+        <v>704502354</v>
       </c>
       <c r="E90" s="1">
-        <v>405779245</v>
+        <v>1076341328</v>
       </c>
       <c r="F90" t="s">
         <v>91</v>
@@ -7310,7 +7197,7 @@
         <v>NaN</v>
       </c>
       <c r="H90" s="5">
-        <v>0.7827</v>
+        <v>0.5083</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -7321,13 +7208,13 @@
         <v>161</v>
       </c>
       <c r="C91" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="D91" s="1">
-        <v>751993706</v>
+        <v>954418976</v>
       </c>
       <c r="E91" s="1">
-        <v>985141909</v>
+        <v>1388520134</v>
       </c>
       <c r="F91" t="s">
         <v>91</v>
@@ -7336,7 +7223,7 @@
         <v>NaN</v>
       </c>
       <c r="H91" s="5">
-        <v>0.2961</v>
+        <v>0.4003</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -7344,16 +7231,16 @@
         <v>6</v>
       </c>
       <c r="B92" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C92" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="D92" s="1">
-        <v>414056068</v>
+        <v>708888643</v>
       </c>
       <c r="E92" s="1">
-        <v>487132500</v>
+        <v>801020312</v>
       </c>
       <c r="F92" t="s">
         <v>91</v>
@@ -7362,7 +7249,7 @@
         <v>NaN</v>
       </c>
       <c r="H92" s="5">
-        <v>0.444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -7370,16 +7257,16 @@
         <v>6</v>
       </c>
       <c r="B93" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C93" t="s">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="D93" s="1">
-        <v>315296707</v>
+        <v>275923278</v>
       </c>
       <c r="E93" s="1">
-        <v>466898109</v>
+        <v>275639320</v>
       </c>
       <c r="F93" t="s">
         <v>91</v>
@@ -7388,7 +7275,7 @@
         <v>NaN</v>
       </c>
       <c r="H93" s="5">
-        <v>0.444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -7396,16 +7283,16 @@
         <v>6</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C94" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D94" s="1">
-        <v>704502354</v>
+        <v>440558255</v>
       </c>
       <c r="E94" s="1">
-        <v>1040412062</v>
+        <v>442701115</v>
       </c>
       <c r="F94" t="s">
         <v>91</v>
@@ -7414,7 +7301,7 @@
         <v>NaN</v>
       </c>
       <c r="H94" s="5">
-        <v>0.444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -7422,16 +7309,16 @@
         <v>6</v>
       </c>
       <c r="B95" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C95" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="D95" s="1">
-        <v>954418976</v>
+        <v>443166315</v>
       </c>
       <c r="E95" s="1">
-        <v>1392892642</v>
+        <v>446332480</v>
       </c>
       <c r="F95" t="s">
         <v>91</v>
@@ -7440,7 +7327,7 @@
         <v>NaN</v>
       </c>
       <c r="H95" s="5">
-        <v>0.3922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -7448,16 +7335,16 @@
         <v>6</v>
       </c>
       <c r="B96" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="C96" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="D96" s="1">
-        <v>708888643</v>
+        <v>127303524</v>
       </c>
       <c r="E96" s="1">
-        <v>783215005</v>
+        <v>243246878</v>
       </c>
       <c r="F96" t="s">
         <v>91</v>
@@ -7466,7 +7353,7 @@
         <v>NaN</v>
       </c>
       <c r="H96" s="5">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -7474,16 +7361,16 @@
         <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D97" s="1">
-        <v>205447975</v>
+        <v>147528441</v>
       </c>
       <c r="E97" s="1">
-        <v>282822171</v>
+        <v>288944122</v>
       </c>
       <c r="F97" t="s">
         <v>91</v>
@@ -7492,7 +7379,7 @@
         <v>NaN</v>
       </c>
       <c r="H97" s="5">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -7500,16 +7387,16 @@
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C98" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D98" s="1">
-        <v>594592070</v>
+        <v>157982595</v>
       </c>
       <c r="E98" s="1">
-        <v>746373228</v>
+        <v>308803058</v>
       </c>
       <c r="F98" t="s">
         <v>91</v>
@@ -7518,7 +7405,7 @@
         <v>NaN</v>
       </c>
       <c r="H98" s="5">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -7526,16 +7413,16 @@
         <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D99" s="1">
-        <v>341387682</v>
+        <v>158484700</v>
       </c>
       <c r="E99" s="1">
-        <v>442398214</v>
+        <v>306792507</v>
       </c>
       <c r="F99" t="s">
         <v>91</v>
@@ -7544,7 +7431,7 @@
         <v>NaN</v>
       </c>
       <c r="H99" s="5">
-        <v>0</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -7552,16 +7439,16 @@
         <v>6</v>
       </c>
       <c r="B100" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D100" s="1">
-        <v>174823294</v>
+        <v>319635794</v>
       </c>
       <c r="E100" s="1">
-        <v>216266708</v>
+        <v>391326795</v>
       </c>
       <c r="F100" t="s">
         <v>91</v>
@@ -7578,16 +7465,16 @@
         <v>6</v>
       </c>
       <c r="B101" t="s">
+        <v>124</v>
+      </c>
+      <c r="C101" t="s">
         <v>126</v>
       </c>
-      <c r="C101" t="s">
-        <v>76</v>
-      </c>
       <c r="D101" s="1">
-        <v>127303524</v>
+        <v>279785344</v>
       </c>
       <c r="E101" s="1">
-        <v>244150280</v>
+        <v>361976287</v>
       </c>
       <c r="F101" t="s">
         <v>91</v>
@@ -7596,7 +7483,7 @@
         <v>NaN</v>
       </c>
       <c r="H101" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -7604,16 +7491,16 @@
         <v>6</v>
       </c>
       <c r="B102" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D102" s="1">
-        <v>147528441</v>
+        <v>328000470</v>
       </c>
       <c r="E102" s="1">
-        <v>289249461</v>
+        <v>409014201</v>
       </c>
       <c r="F102" t="s">
         <v>91</v>
@@ -7622,7 +7509,7 @@
         <v>NaN</v>
       </c>
       <c r="H102" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -7630,16 +7517,16 @@
         <v>6</v>
       </c>
       <c r="B103" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D103" s="1">
-        <v>157982595</v>
+        <v>116977839</v>
       </c>
       <c r="E103" s="1">
-        <v>309226906</v>
+        <v>187362563</v>
       </c>
       <c r="F103" t="s">
         <v>91</v>
@@ -7648,7 +7535,7 @@
         <v>NaN</v>
       </c>
       <c r="H103" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -7656,16 +7543,16 @@
         <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C104" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D104" s="1">
-        <v>158484700</v>
+        <v>107476614</v>
       </c>
       <c r="E104" s="1">
-        <v>307546859</v>
+        <v>145514023</v>
       </c>
       <c r="F104" t="s">
         <v>91</v>
@@ -7674,7 +7561,7 @@
         <v>NaN</v>
       </c>
       <c r="H104" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -7682,16 +7569,16 @@
         <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D105" s="1">
-        <v>319635794</v>
+        <v>115110097</v>
       </c>
       <c r="E105" s="1">
-        <v>390945769</v>
+        <v>167820235</v>
       </c>
       <c r="F105" t="s">
         <v>91</v>
@@ -7708,16 +7595,16 @@
         <v>6</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C106" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D106" s="1">
-        <v>279785344</v>
+        <v>60000000</v>
       </c>
       <c r="E106" s="1">
-        <v>361280453</v>
+        <v>82391662</v>
       </c>
       <c r="F106" t="s">
         <v>91</v>
@@ -7726,7 +7613,7 @@
         <v>NaN</v>
       </c>
       <c r="H106" s="5">
-        <v>0</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -7734,16 +7621,16 @@
         <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C107" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="D107" s="1">
-        <v>328000470</v>
+        <v>60000000</v>
       </c>
       <c r="E107" s="1">
-        <v>408867040</v>
+        <v>90179012</v>
       </c>
       <c r="F107" t="s">
         <v>91</v>
@@ -7752,7 +7639,7 @@
         <v>NaN</v>
       </c>
       <c r="H107" s="5">
-        <v>0</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -7760,16 +7647,16 @@
         <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C108" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="D108" s="1">
-        <v>116977839</v>
+        <v>60000000</v>
       </c>
       <c r="E108" s="1">
-        <v>184334919</v>
+        <v>73920654</v>
       </c>
       <c r="F108" t="s">
         <v>91</v>
@@ -7778,7 +7665,7 @@
         <v>NaN</v>
       </c>
       <c r="H108" s="5">
-        <v>0</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -7786,16 +7673,16 @@
         <v>6</v>
       </c>
       <c r="B109" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="C109" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D109" s="1">
-        <v>107476614</v>
+        <v>60000000</v>
       </c>
       <c r="E109" s="1">
-        <v>144364581</v>
+        <v>83221636</v>
       </c>
       <c r="F109" t="s">
         <v>91</v>
@@ -7804,128 +7691,128 @@
         <v>NaN</v>
       </c>
       <c r="H109" s="5">
-        <v>0</v>
+        <v>0.39909999999999995</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="C110" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="D110" s="1">
-        <v>115110097</v>
+        <v>500000000</v>
       </c>
       <c r="E110" s="1">
-        <v>166555642</v>
+        <v>1165423958</v>
       </c>
       <c r="F110" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="G110" s="5">
         <v>NaN</v>
       </c>
       <c r="H110" s="5">
-        <v>0</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="C111" t="s">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="D111" s="1">
-        <v>60000000</v>
+        <v>500000000</v>
       </c>
       <c r="E111" s="1">
-        <v>82674922</v>
+        <v>1151125436</v>
       </c>
       <c r="F111" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="G111" s="5">
         <v>NaN</v>
       </c>
       <c r="H111" s="5">
-        <v>0.39149999999999996</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="C112" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="D112" s="1">
-        <v>60000000</v>
+        <v>500000000</v>
       </c>
       <c r="E112" s="1">
-        <v>90350775</v>
+        <v>1148829895</v>
       </c>
       <c r="F112" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="G112" s="5">
         <v>NaN</v>
       </c>
       <c r="H112" s="5">
-        <v>0.39149999999999996</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="C113" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="D113" s="1">
-        <v>60000000</v>
+        <v>500000000</v>
       </c>
       <c r="E113" s="1">
-        <v>74789670</v>
+        <v>1186966069</v>
       </c>
       <c r="F113" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="G113" s="5">
         <v>NaN</v>
       </c>
       <c r="H113" s="5">
-        <v>0.39149999999999996</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="C114" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D114" s="1">
-        <v>60000000</v>
+        <v>946084601</v>
       </c>
       <c r="E114" s="1">
-        <v>82224651</v>
+        <v>1255172172</v>
       </c>
       <c r="F114" t="s">
         <v>91</v>
@@ -7934,7 +7821,7 @@
         <v>NaN</v>
       </c>
       <c r="H114" s="5">
-        <v>0.39149999999999996</v>
+        <v>0.6374</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -7942,25 +7829,25 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="C115" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D115" s="1">
-        <v>500000000</v>
+        <v>274323144</v>
       </c>
       <c r="E115" s="1">
-        <v>1353674960</v>
+        <v>374599171</v>
       </c>
       <c r="F115" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G115" s="5">
         <v>NaN</v>
       </c>
       <c r="H115" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.36829999999999996</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -7968,25 +7855,25 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="C116" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="D116" s="1">
-        <v>500000000</v>
+        <v>314964360</v>
       </c>
       <c r="E116" s="1">
-        <v>1334664633</v>
+        <v>337505230</v>
       </c>
       <c r="F116" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G116" s="5">
         <v>NaN</v>
       </c>
       <c r="H116" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.0633</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -7994,25 +7881,25 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="C117" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D117" s="1">
-        <v>500000000</v>
+        <v>1151650255</v>
       </c>
       <c r="E117" s="1">
-        <v>1357369868</v>
+        <v>1214682638</v>
       </c>
       <c r="F117" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G117" s="5">
         <v>NaN</v>
       </c>
       <c r="H117" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.0633</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -8020,25 +7907,25 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>65</v>
+        <v>172</v>
       </c>
       <c r="C118" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="D118" s="1">
-        <v>500000000</v>
+        <v>823846300</v>
       </c>
       <c r="E118" s="1">
-        <v>1391420851</v>
+        <v>997557132</v>
       </c>
       <c r="F118" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G118" s="5">
         <v>NaN</v>
       </c>
       <c r="H118" s="5">
-        <v>1.6469999999999998</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -8046,16 +7933,16 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C119" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D119" s="1">
-        <v>946084601</v>
+        <v>820369757</v>
       </c>
       <c r="E119" s="1">
-        <v>1169142378</v>
+        <v>988168804</v>
       </c>
       <c r="F119" t="s">
         <v>91</v>
@@ -8064,7 +7951,7 @@
         <v>NaN</v>
       </c>
       <c r="H119" s="5">
-        <v>0.6291</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -8072,16 +7959,16 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C120" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="D120" s="1">
-        <v>274323144</v>
+        <v>822731626</v>
       </c>
       <c r="E120" s="1">
-        <v>375820731</v>
+        <v>993985391</v>
       </c>
       <c r="F120" t="s">
         <v>91</v>
@@ -8090,7 +7977,7 @@
         <v>NaN</v>
       </c>
       <c r="H120" s="5">
-        <v>0.3799</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -8098,16 +7985,16 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C121" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D121" s="1">
-        <v>314964360</v>
+        <v>425389351</v>
       </c>
       <c r="E121" s="1">
-        <v>340158477</v>
+        <v>475239009</v>
       </c>
       <c r="F121" t="s">
         <v>91</v>
@@ -8116,7 +8003,7 @@
         <v>NaN</v>
       </c>
       <c r="H121" s="5">
-        <v>0.0708</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -8124,16 +8011,16 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C122" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D122" s="1">
-        <v>1151650255</v>
+        <v>508571279</v>
       </c>
       <c r="E122" s="1">
-        <v>1226408330</v>
+        <v>578473784</v>
       </c>
       <c r="F122" t="s">
         <v>91</v>
@@ -8142,7 +8029,7 @@
         <v>NaN</v>
       </c>
       <c r="H122" s="5">
-        <v>0.0708</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -8150,16 +8037,16 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C123" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D123" s="1">
-        <v>823846300</v>
+        <v>464478952</v>
       </c>
       <c r="E123" s="1">
-        <v>1015854267</v>
+        <v>511250642</v>
       </c>
       <c r="F123" t="s">
         <v>91</v>
@@ -8168,7 +8055,7 @@
         <v>NaN</v>
       </c>
       <c r="H123" s="5">
-        <v>0.2305</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -8176,16 +8063,16 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C124" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="D124" s="1">
-        <v>820369757</v>
+        <v>627191291</v>
       </c>
       <c r="E124" s="1">
-        <v>1003188508</v>
+        <v>714504487</v>
       </c>
       <c r="F124" t="s">
         <v>91</v>
@@ -8194,7 +8081,7 @@
         <v>NaN</v>
       </c>
       <c r="H124" s="5">
-        <v>0.2305</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -8202,16 +8089,16 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="D125" s="1">
-        <v>822731626</v>
+        <v>425091462</v>
       </c>
       <c r="E125" s="1">
-        <v>1011728502</v>
+        <v>478192278</v>
       </c>
       <c r="F125" t="s">
         <v>91</v>
@@ -8220,7 +8107,7 @@
         <v>NaN</v>
       </c>
       <c r="H125" s="5">
-        <v>0.2305</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -8228,16 +8115,16 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C126" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="D126" s="1">
-        <v>425389351</v>
+        <v>428950000</v>
       </c>
       <c r="E126" s="1">
-        <v>465806981</v>
+        <v>431428553</v>
       </c>
       <c r="F126" t="s">
         <v>91</v>
@@ -8246,7 +8133,7 @@
         <v>NaN</v>
       </c>
       <c r="H126" s="5">
-        <v>0.1182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -8254,16 +8141,16 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C127" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D127" s="1">
-        <v>508571279</v>
+        <v>462463907</v>
       </c>
       <c r="E127" s="1">
-        <v>576500239</v>
+        <v>466146222</v>
       </c>
       <c r="F127" t="s">
         <v>91</v>
@@ -8272,7 +8159,7 @@
         <v>NaN</v>
       </c>
       <c r="H127" s="5">
-        <v>0.1182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -8280,16 +8167,16 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="D128" s="1">
-        <v>464478952</v>
+        <v>151969815</v>
       </c>
       <c r="E128" s="1">
-        <v>511437288</v>
+        <v>266710574</v>
       </c>
       <c r="F128" t="s">
         <v>91</v>
@@ -8298,7 +8185,7 @@
         <v>NaN</v>
       </c>
       <c r="H128" s="5">
-        <v>0.1182</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -8306,16 +8193,16 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="C129" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D129" s="1">
-        <v>627191291</v>
+        <v>105992843</v>
       </c>
       <c r="E129" s="1">
-        <v>696396775</v>
+        <v>129828838</v>
       </c>
       <c r="F129" t="s">
         <v>91</v>
@@ -8324,7 +8211,7 @@
         <v>NaN</v>
       </c>
       <c r="H129" s="5">
-        <v>0.1013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -8332,16 +8219,16 @@
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="C130" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="D130" s="1">
-        <v>425091462</v>
+        <v>258094745</v>
       </c>
       <c r="E130" s="1">
-        <v>467549834</v>
+        <v>333870078</v>
       </c>
       <c r="F130" t="s">
         <v>91</v>
@@ -8350,7 +8237,7 @@
         <v>NaN</v>
       </c>
       <c r="H130" s="5">
-        <v>0.1013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -8358,16 +8245,16 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C131" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D131" s="1">
-        <v>426766888</v>
+        <v>299312934</v>
       </c>
       <c r="E131" s="1">
-        <v>534717371</v>
+        <v>373139760</v>
       </c>
       <c r="F131" t="s">
         <v>91</v>
@@ -8381,19 +8268,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="C132" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D132" s="1">
-        <v>356338853</v>
+        <v>510820499</v>
       </c>
       <c r="E132" s="1">
-        <v>461631869</v>
+        <v>619202327</v>
       </c>
       <c r="F132" t="s">
         <v>91</v>
@@ -8402,24 +8289,24 @@
         <v>NaN</v>
       </c>
       <c r="H132" s="5">
-        <v>0</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="C133" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="D133" s="1">
-        <v>151969815</v>
+        <v>508402028</v>
       </c>
       <c r="E133" s="1">
-        <v>276713571</v>
+        <v>612836264</v>
       </c>
       <c r="F133" t="s">
         <v>91</v>
@@ -8428,24 +8315,24 @@
         <v>NaN</v>
       </c>
       <c r="H133" s="5">
-        <v>0.7368000000000001</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="C134" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D134" s="1">
-        <v>105992843</v>
+        <v>378735074</v>
       </c>
       <c r="E134" s="1">
-        <v>129701554</v>
+        <v>430909955</v>
       </c>
       <c r="F134" t="s">
         <v>91</v>
@@ -8454,24 +8341,24 @@
         <v>NaN</v>
       </c>
       <c r="H134" s="5">
-        <v>0</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="C135" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D135" s="1">
-        <v>258094745</v>
+        <v>339081835</v>
       </c>
       <c r="E135" s="1">
-        <v>333220326</v>
+        <v>334549088</v>
       </c>
       <c r="F135" t="s">
         <v>91</v>
@@ -8480,24 +8367,24 @@
         <v>NaN</v>
       </c>
       <c r="H135" s="5">
-        <v>0</v>
+        <v>-0.0173</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C136" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="D136" s="1">
-        <v>299312934</v>
+        <v>151227051</v>
       </c>
       <c r="E136" s="1">
-        <v>373078137</v>
+        <v>265114862</v>
       </c>
       <c r="F136" t="s">
         <v>91</v>
@@ -8506,7 +8393,7 @@
         <v>NaN</v>
       </c>
       <c r="H136" s="5">
-        <v>0</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -8514,16 +8401,16 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C137" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="D137" s="1">
-        <v>510820499</v>
+        <v>159277445</v>
       </c>
       <c r="E137" s="1">
-        <v>630545983</v>
+        <v>304979599</v>
       </c>
       <c r="F137" t="s">
         <v>91</v>
@@ -8532,7 +8419,7 @@
         <v>NaN</v>
       </c>
       <c r="H137" s="5">
-        <v>0.2305</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -8540,16 +8427,16 @@
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="D138" s="1">
-        <v>508402028</v>
+        <v>159101214</v>
       </c>
       <c r="E138" s="1">
-        <v>622185342</v>
+        <v>311496128</v>
       </c>
       <c r="F138" t="s">
         <v>91</v>
@@ -8558,7 +8445,7 @@
         <v>NaN</v>
       </c>
       <c r="H138" s="5">
-        <v>0.2305</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -8566,16 +8453,16 @@
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="C139" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="D139" s="1">
-        <v>378735074</v>
+        <v>159382615</v>
       </c>
       <c r="E139" s="1">
-        <v>419989262</v>
+        <v>311580226</v>
       </c>
       <c r="F139" t="s">
         <v>91</v>
@@ -8584,7 +8471,7 @@
         <v>NaN</v>
       </c>
       <c r="H139" s="5">
-        <v>0.1013</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -8592,16 +8479,16 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="C140" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D140" s="1">
-        <v>339081835</v>
+        <v>159708987</v>
       </c>
       <c r="E140" s="1">
-        <v>333967279</v>
+        <v>309819784</v>
       </c>
       <c r="F140" t="s">
         <v>91</v>
@@ -8610,7 +8497,7 @@
         <v>NaN</v>
       </c>
       <c r="H140" s="5">
-        <v>-0.019799999999999998</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -8618,16 +8505,16 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
+        <v>124</v>
+      </c>
+      <c r="C141" t="s">
         <v>125</v>
       </c>
-      <c r="C141" t="s">
-        <v>76</v>
-      </c>
       <c r="D141" s="1">
-        <v>151227051</v>
+        <v>106848757</v>
       </c>
       <c r="E141" s="1">
-        <v>274997024</v>
+        <v>130862848</v>
       </c>
       <c r="F141" t="s">
         <v>91</v>
@@ -8636,7 +8523,7 @@
         <v>NaN</v>
       </c>
       <c r="H141" s="5">
-        <v>0.7368000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -8644,16 +8531,16 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
+        <v>124</v>
+      </c>
+      <c r="C142" t="s">
         <v>126</v>
       </c>
-      <c r="C142" t="s">
-        <v>76</v>
-      </c>
       <c r="D142" s="1">
-        <v>159277445</v>
+        <v>134102607</v>
       </c>
       <c r="E142" s="1">
-        <v>306168404</v>
+        <v>174702263</v>
       </c>
       <c r="F142" t="s">
         <v>91</v>
@@ -8662,7 +8549,7 @@
         <v>NaN</v>
       </c>
       <c r="H142" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -8670,16 +8557,16 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C143" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D143" s="1">
-        <v>159101214</v>
+        <v>257027478</v>
       </c>
       <c r="E143" s="1">
-        <v>311826973</v>
+        <v>319545179</v>
       </c>
       <c r="F143" t="s">
         <v>91</v>
@@ -8688,7 +8575,7 @@
         <v>NaN</v>
       </c>
       <c r="H143" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -8696,16 +8583,16 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D144" s="1">
-        <v>159382615</v>
+        <v>160873068</v>
       </c>
       <c r="E144" s="1">
-        <v>312073795</v>
+        <v>257650149</v>
       </c>
       <c r="F144" t="s">
         <v>91</v>
@@ -8714,7 +8601,7 @@
         <v>NaN</v>
       </c>
       <c r="H144" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -8722,16 +8609,16 @@
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C145" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D145" s="1">
-        <v>159708987</v>
+        <v>163472383</v>
       </c>
       <c r="E145" s="1">
-        <v>310633245</v>
+        <v>221410107</v>
       </c>
       <c r="F145" t="s">
         <v>91</v>
@@ -8740,7 +8627,7 @@
         <v>NaN</v>
       </c>
       <c r="H145" s="5">
-        <v>0.9181999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -8748,16 +8635,16 @@
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="C146" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D146" s="1">
-        <v>106848757</v>
+        <v>161120051</v>
       </c>
       <c r="E146" s="1">
-        <v>130738321</v>
+        <v>234838962</v>
       </c>
       <c r="F146" t="s">
         <v>91</v>
@@ -8774,16 +8661,16 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="C147" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="D147" s="1">
-        <v>134102607</v>
+        <v>149737366</v>
       </c>
       <c r="E147" s="1">
-        <v>174360065</v>
+        <v>220527203</v>
       </c>
       <c r="F147" t="s">
         <v>91</v>
@@ -8800,16 +8687,16 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C148" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D148" s="1">
-        <v>257027478</v>
+        <v>170770415</v>
       </c>
       <c r="E148" s="1">
-        <v>319402813</v>
+        <v>169160821</v>
       </c>
       <c r="F148" t="s">
         <v>91</v>
@@ -8818,7 +8705,7 @@
         <v>NaN</v>
       </c>
       <c r="H148" s="5">
-        <v>0</v>
+        <v>-0.0070999999999999995</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -8826,16 +8713,16 @@
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="C149" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D149" s="1">
-        <v>160873068</v>
+        <v>92866928</v>
       </c>
       <c r="E149" s="1">
-        <v>253501997</v>
+        <v>92150680</v>
       </c>
       <c r="F149" t="s">
         <v>91</v>
@@ -8844,7 +8731,7 @@
         <v>NaN</v>
       </c>
       <c r="H149" s="5">
-        <v>0</v>
+        <v>-0.0070999999999999995</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -8852,16 +8739,16 @@
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="C150" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D150" s="1">
-        <v>163472383</v>
+        <v>116515080</v>
       </c>
       <c r="E150" s="1">
-        <v>219664914</v>
+        <v>115478381</v>
       </c>
       <c r="F150" t="s">
         <v>91</v>
@@ -8870,7 +8757,7 @@
         <v>NaN</v>
       </c>
       <c r="H150" s="5">
-        <v>0</v>
+        <v>-0.0070999999999999995</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -8878,16 +8765,16 @@
         <v>8</v>
       </c>
       <c r="B151" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="C151" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D151" s="1">
-        <v>161120051</v>
+        <v>60000000</v>
       </c>
       <c r="E151" s="1">
-        <v>233042002</v>
+        <v>76839686</v>
       </c>
       <c r="F151" t="s">
         <v>91</v>
@@ -8904,16 +8791,16 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="C152" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D152" s="1">
-        <v>149737366</v>
+        <v>60000000</v>
       </c>
       <c r="E152" s="1">
-        <v>210177476</v>
+        <v>72935938</v>
       </c>
       <c r="F152" t="s">
         <v>91</v>
@@ -8930,16 +8817,16 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C153" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="D153" s="1">
-        <v>170770415</v>
+        <v>120000000</v>
       </c>
       <c r="E153" s="1">
-        <v>171873906</v>
+        <v>146792233</v>
       </c>
       <c r="F153" t="s">
         <v>91</v>
@@ -8948,7 +8835,7 @@
         <v>NaN</v>
       </c>
       <c r="H153" s="5">
-        <v>0.008100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -8956,16 +8843,16 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C154" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D154" s="1">
-        <v>92866928</v>
+        <v>100000000</v>
       </c>
       <c r="E154" s="1">
-        <v>93625625</v>
+        <v>133483168</v>
       </c>
       <c r="F154" t="s">
         <v>91</v>
@@ -8974,7 +8861,7 @@
         <v>NaN</v>
       </c>
       <c r="H154" s="5">
-        <v>0.008100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -8982,16 +8869,16 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="C155" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="D155" s="1">
-        <v>116515080</v>
+        <v>60000000</v>
       </c>
       <c r="E155" s="1">
-        <v>117313547</v>
+        <v>75654265</v>
       </c>
       <c r="F155" t="s">
         <v>91</v>
@@ -9000,7 +8887,7 @@
         <v>NaN</v>
       </c>
       <c r="H155" s="5">
-        <v>0.008100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -9008,16 +8895,16 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C156" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="D156" s="1">
         <v>60000000</v>
       </c>
       <c r="E156" s="1">
-        <v>78961584</v>
+        <v>89122293</v>
       </c>
       <c r="F156" t="s">
         <v>91</v>
@@ -9026,7 +8913,7 @@
         <v>NaN</v>
       </c>
       <c r="H156" s="5">
-        <v>0</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -9034,16 +8921,16 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C157" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="D157" s="1">
         <v>60000000</v>
       </c>
       <c r="E157" s="1">
-        <v>73420942</v>
+        <v>85570319</v>
       </c>
       <c r="F157" t="s">
         <v>91</v>
@@ -9052,7 +8939,7 @@
         <v>NaN</v>
       </c>
       <c r="H157" s="5">
-        <v>0</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -9060,16 +8947,16 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C158" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="D158" s="1">
-        <v>120000000</v>
+        <v>60000000</v>
       </c>
       <c r="E158" s="1">
-        <v>146628667</v>
+        <v>87308547</v>
       </c>
       <c r="F158" t="s">
         <v>91</v>
@@ -9078,7 +8965,7 @@
         <v>NaN</v>
       </c>
       <c r="H158" s="5">
-        <v>0</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -9086,16 +8973,16 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C159" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D159" s="1">
-        <v>100000000</v>
+        <v>60000000</v>
       </c>
       <c r="E159" s="1">
-        <v>133508568</v>
+        <v>84636837</v>
       </c>
       <c r="F159" t="s">
         <v>91</v>
@@ -9104,7 +8991,7 @@
         <v>NaN</v>
       </c>
       <c r="H159" s="5">
-        <v>0</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -9112,16 +8999,16 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C160" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D160" s="1">
         <v>60000000</v>
       </c>
       <c r="E160" s="1">
-        <v>76140188</v>
+        <v>88954199</v>
       </c>
       <c r="F160" t="s">
         <v>91</v>
@@ -9130,7 +9017,7 @@
         <v>NaN</v>
       </c>
       <c r="H160" s="5">
-        <v>0</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -9138,16 +9025,16 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="C161" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="D161" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E161" s="1">
-        <v>90358868</v>
+        <v>134048105</v>
       </c>
       <c r="F161" t="s">
         <v>91</v>
@@ -9156,7 +9043,7 @@
         <v>NaN</v>
       </c>
       <c r="H161" s="5">
-        <v>0.7422</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -9164,16 +9051,16 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="C162" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="D162" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E162" s="1">
-        <v>86521083</v>
+        <v>136597280</v>
       </c>
       <c r="F162" t="s">
         <v>91</v>
@@ -9182,7 +9069,7 @@
         <v>NaN</v>
       </c>
       <c r="H162" s="5">
-        <v>0.7422</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -9190,16 +9077,16 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="C163" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="D163" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E163" s="1">
-        <v>87780067</v>
+        <v>137179366</v>
       </c>
       <c r="F163" t="s">
         <v>91</v>
@@ -9208,7 +9095,7 @@
         <v>NaN</v>
       </c>
       <c r="H163" s="5">
-        <v>0.7422</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -9216,16 +9103,16 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="C164" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="D164" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E164" s="1">
-        <v>84395282</v>
+        <v>136973911</v>
       </c>
       <c r="F164" t="s">
         <v>91</v>
@@ -9234,137 +9121,7 @@
         <v>NaN</v>
       </c>
       <c r="H164" s="5">
-        <v>0.7422</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>8</v>
-      </c>
-      <c r="B165" t="s">
-        <v>179</v>
-      </c>
-      <c r="C165" t="s">
-        <v>110</v>
-      </c>
-      <c r="D165" s="1">
-        <v>60000000</v>
-      </c>
-      <c r="E165" s="1">
-        <v>89772081</v>
-      </c>
-      <c r="F165" t="s">
-        <v>91</v>
-      </c>
-      <c r="G165" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H165" s="5">
-        <v>0.7422</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>8</v>
-      </c>
-      <c r="B166" t="s">
-        <v>148</v>
-      </c>
-      <c r="C166" t="s">
-        <v>149</v>
-      </c>
-      <c r="D166" s="1">
-        <v>100000000</v>
-      </c>
-      <c r="E166" s="1">
-        <v>134226586</v>
-      </c>
-      <c r="F166" t="s">
-        <v>91</v>
-      </c>
-      <c r="G166" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H166" s="5">
-        <v>0.434</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>8</v>
-      </c>
-      <c r="B167" t="s">
-        <v>148</v>
-      </c>
-      <c r="C167" t="s">
-        <v>173</v>
-      </c>
-      <c r="D167" s="1">
-        <v>100000000</v>
-      </c>
-      <c r="E167" s="1">
-        <v>136542859</v>
-      </c>
-      <c r="F167" t="s">
-        <v>91</v>
-      </c>
-      <c r="G167" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H167" s="5">
-        <v>0.434</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>8</v>
-      </c>
-      <c r="B168" t="s">
-        <v>148</v>
-      </c>
-      <c r="C168" t="s">
-        <v>100</v>
-      </c>
-      <c r="D168" s="1">
-        <v>100000000</v>
-      </c>
-      <c r="E168" s="1">
-        <v>136846292</v>
-      </c>
-      <c r="F168" t="s">
-        <v>91</v>
-      </c>
-      <c r="G168" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H168" s="5">
-        <v>0.434</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>8</v>
-      </c>
-      <c r="B169" t="s">
-        <v>148</v>
-      </c>
-      <c r="C169" t="s">
-        <v>115</v>
-      </c>
-      <c r="D169" s="1">
-        <v>100000000</v>
-      </c>
-      <c r="E169" s="1">
-        <v>136738423</v>
-      </c>
-      <c r="F169" t="s">
-        <v>91</v>
-      </c>
-      <c r="G169" s="5">
-        <v>NaN</v>
-      </c>
-      <c r="H169" s="5">
-        <v>0.434</v>
+        <v>0.4351</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/勞動基金月度揭露_可持續更新.xlsx
+++ b/downloads/勞動基金月度揭露_可持續更新.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="187">
   <si>
     <t>勞動基金運用局｜四大基金月度儀表板</t>
   </si>
@@ -73,31 +73,31 @@
     <t>國外投資</t>
   </si>
   <si>
-    <t>自行運用-固定收益</t>
-  </si>
-  <si>
-    <t>自行運用-權益證券</t>
-  </si>
-  <si>
-    <t>自行運用-另類投資</t>
+    <t>自行運用-國外-固定收益</t>
+  </si>
+  <si>
+    <t>自行運用-國外-權益證券</t>
+  </si>
+  <si>
+    <t>自行運用-國外-另類投資</t>
   </si>
   <si>
     <t>委託經營</t>
   </si>
   <si>
-    <t>國內委託經營</t>
+    <t>委託經營-國內-權益證券</t>
   </si>
   <si>
     <t>國外委託經營</t>
   </si>
   <si>
-    <t>委託經營-固定收益</t>
-  </si>
-  <si>
-    <t>委託經營-權益證券</t>
-  </si>
-  <si>
-    <t>委託經營-另類投資</t>
+    <t>委託經營-國外-固定收益</t>
+  </si>
+  <si>
+    <t>委託經營-國外-權益證券</t>
+  </si>
+  <si>
+    <t>委託經營-國外-另類投資</t>
   </si>
   <si>
     <t>合計</t>
@@ -292,6 +292,9 @@
     <t>106年第一次委託經營(續約)</t>
   </si>
   <si>
+    <t>新增</t>
+  </si>
+  <si>
     <t>解約</t>
   </si>
   <si>
@@ -334,9 +337,6 @@
     <t>100-1全球基本面指數被動股票型（續約3）</t>
   </si>
   <si>
-    <t>新增</t>
-  </si>
-  <si>
     <t>100-1全球不動產有價證券型（續約2）</t>
   </si>
   <si>
@@ -439,7 +439,7 @@
     <t>CBRE</t>
   </si>
   <si>
-    <t>Clearbridge</t>
+    <t>ClearBridge</t>
   </si>
   <si>
     <t>110-1全球多元資產型</t>
@@ -533,9 +533,6 @@
   </si>
   <si>
     <t>107-1絕對報酬股票型(續約)</t>
-  </si>
-  <si>
-    <t>ClearBridge</t>
   </si>
   <si>
     <t>100年全球主動股票型(續約2)</t>
@@ -1721,7 +1718,7 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C47" s="1">
         <v>68461127545</v>
@@ -1987,7 +1984,7 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C66" s="1">
         <v>100575817739</v>
@@ -2116,7 +2113,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
@@ -5158,122 +5155,122 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C102" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D102" s="1">
-        <v>3000000000</v>
+        <v>500000000</v>
       </c>
       <c r="E102" s="1">
-        <v>3958912304</v>
+        <v>1165423958</v>
       </c>
       <c r="F102" s="7">
-        <v>1380163332</v>
+        <v>1165423958</v>
       </c>
       <c r="G102" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H102" t="s">
         <v>45</v>
       </c>
       <c r="I102" s="5"/>
       <c r="J102" s="5">
-        <v>1.1673</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C103" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D103" s="1">
-        <v>3000000000</v>
+        <v>500000000</v>
       </c>
       <c r="E103" s="1">
-        <v>3975895368</v>
+        <v>1151125436</v>
       </c>
       <c r="F103" s="7">
-        <v>1397858568</v>
+        <v>1151125436</v>
       </c>
       <c r="G103" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H103" t="s">
         <v>45</v>
       </c>
       <c r="I103" s="5"/>
       <c r="J103" s="5">
-        <v>1.1673</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C104" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="D104" s="1">
-        <v>400000000</v>
+        <v>500000000</v>
       </c>
       <c r="E104" s="1">
-        <v>381187393</v>
+        <v>1148829895</v>
       </c>
       <c r="F104" s="7">
-        <v>-30591888</v>
+        <v>1148829895</v>
       </c>
       <c r="G104" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H104" t="s">
         <v>45</v>
       </c>
       <c r="I104" s="5"/>
       <c r="J104" s="5">
-        <v>0.009000000000000001</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C105" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D105" s="1">
-        <v>400000000</v>
+        <v>500000000</v>
       </c>
       <c r="E105" s="1">
-        <v>333326095</v>
+        <v>1186966069</v>
       </c>
       <c r="F105" s="7">
-        <v>-59815011</v>
+        <v>1186966069</v>
       </c>
       <c r="G105" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H105" t="s">
         <v>45</v>
       </c>
       <c r="I105" s="5"/>
       <c r="J105" s="5">
-        <v>0.009000000000000001</v>
+        <v>1.2554</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -5281,19 +5278,19 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D106" s="1">
-        <v>400000000</v>
+        <v>3000000000</v>
       </c>
       <c r="E106" s="1">
-        <v>341538111</v>
+        <v>3958912304</v>
       </c>
       <c r="F106" s="7">
-        <v>-55332604</v>
+        <v>1380163332</v>
       </c>
       <c r="G106" t="s">
         <v>44</v>
@@ -5303,120 +5300,240 @@
       </c>
       <c r="I106" s="5"/>
       <c r="J106" s="5">
-        <v>0.009000000000000001</v>
+        <v>1.1673</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C107" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D107" s="1">
-        <v>0</v>
+        <v>3000000000</v>
       </c>
       <c r="E107" s="1">
-        <v>0</v>
+        <v>3975895368</v>
       </c>
       <c r="F107" s="7">
-        <v>-1528889549</v>
+        <v>1397858568</v>
       </c>
       <c r="G107" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H107" t="s">
         <v>45</v>
       </c>
       <c r="I107" s="5"/>
-      <c r="J107" s="5"/>
+      <c r="J107" s="5">
+        <v>1.1673</v>
+      </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B108" t="s">
         <v>80</v>
       </c>
       <c r="C108" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D108" s="1">
-        <v>0</v>
+        <v>400000000</v>
       </c>
       <c r="E108" s="1">
-        <v>0</v>
+        <v>381187393</v>
       </c>
       <c r="F108" s="7">
-        <v>-1474347055</v>
+        <v>-30591888</v>
       </c>
       <c r="G108" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H108" t="s">
         <v>45</v>
       </c>
       <c r="I108" s="5"/>
-      <c r="J108" s="5"/>
+      <c r="J108" s="5">
+        <v>0.009000000000000001</v>
+      </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B109" t="s">
         <v>80</v>
       </c>
       <c r="C109" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D109" s="1">
-        <v>0</v>
+        <v>400000000</v>
       </c>
       <c r="E109" s="1">
-        <v>0</v>
+        <v>333326095</v>
       </c>
       <c r="F109" s="7">
-        <v>-1489331693</v>
+        <v>-59815011</v>
       </c>
       <c r="G109" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="H109" t="s">
         <v>45</v>
       </c>
       <c r="I109" s="5"/>
-      <c r="J109" s="5"/>
+      <c r="J109" s="5">
+        <v>0.009000000000000001</v>
+      </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B110" t="s">
         <v>80</v>
       </c>
       <c r="C110" t="s">
+        <v>43</v>
+      </c>
+      <c r="D110" s="1">
+        <v>400000000</v>
+      </c>
+      <c r="E110" s="1">
+        <v>341538111</v>
+      </c>
+      <c r="F110" s="7">
+        <v>-55332604</v>
+      </c>
+      <c r="G110" t="s">
+        <v>44</v>
+      </c>
+      <c r="H110" t="s">
+        <v>45</v>
+      </c>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5">
+        <v>0.009000000000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>80</v>
+      </c>
+      <c r="C111" t="s">
+        <v>60</v>
+      </c>
+      <c r="D111" s="1">
+        <v>0</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0</v>
+      </c>
+      <c r="F111" s="7">
+        <v>-1528889549</v>
+      </c>
+      <c r="G111" t="s">
+        <v>93</v>
+      </c>
+      <c r="H111" t="s">
+        <v>45</v>
+      </c>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>80</v>
+      </c>
+      <c r="C112" t="s">
+        <v>66</v>
+      </c>
+      <c r="D112" s="1">
+        <v>0</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0</v>
+      </c>
+      <c r="F112" s="7">
+        <v>-1474347055</v>
+      </c>
+      <c r="G112" t="s">
+        <v>93</v>
+      </c>
+      <c r="H112" t="s">
+        <v>45</v>
+      </c>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>80</v>
+      </c>
+      <c r="C113" t="s">
+        <v>43</v>
+      </c>
+      <c r="D113" s="1">
+        <v>0</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
+      <c r="F113" s="7">
+        <v>-1489331693</v>
+      </c>
+      <c r="G113" t="s">
+        <v>93</v>
+      </c>
+      <c r="H113" t="s">
+        <v>45</v>
+      </c>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>80</v>
+      </c>
+      <c r="C114" t="s">
         <v>77</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D114" s="1">
         <v>0</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E114" s="1">
         <v>0</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F114" s="7">
         <v>-1492945981</v>
       </c>
-      <c r="G110" t="s">
-        <v>92</v>
-      </c>
-      <c r="H110" t="s">
-        <v>45</v>
-      </c>
-      <c r="I110" s="5"/>
-      <c r="J110" s="5"/>
+      <c r="G114" t="s">
+        <v>93</v>
+      </c>
+      <c r="H114" t="s">
+        <v>45</v>
+      </c>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5473,10 +5590,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" s="1">
         <v>900495639</v>
@@ -5491,7 +5608,7 @@
         <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5">
@@ -5503,10 +5620,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3" s="1">
         <v>1338657958</v>
@@ -5521,7 +5638,7 @@
         <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5">
@@ -5533,10 +5650,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1">
         <v>2408967886</v>
@@ -5551,7 +5668,7 @@
         <v>44</v>
       </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5">
@@ -5563,7 +5680,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
@@ -5581,7 +5698,7 @@
         <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5">
@@ -5593,10 +5710,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D6" s="1">
         <v>1585120883</v>
@@ -5611,7 +5728,7 @@
         <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
@@ -5623,10 +5740,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" s="1">
         <v>656507639</v>
@@ -5641,7 +5758,7 @@
         <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
@@ -5653,7 +5770,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
         <v>79</v>
@@ -5671,7 +5788,7 @@
         <v>44</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
@@ -5683,10 +5800,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1">
         <v>1783655177</v>
@@ -5701,7 +5818,7 @@
         <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
@@ -5713,10 +5830,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" t="s">
         <v>105</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
       </c>
       <c r="D10" s="1">
         <v>1683240295</v>
@@ -5728,10 +5845,10 @@
         <v>1714089252</v>
       </c>
       <c r="G10" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
@@ -5743,7 +5860,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
         <v>79</v>
@@ -5758,10 +5875,10 @@
         <v>1711777799</v>
       </c>
       <c r="G11" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
@@ -5791,7 +5908,7 @@
         <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -5804,7 +5921,7 @@
         <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" s="1">
         <v>1417127452</v>
@@ -5819,7 +5936,7 @@
         <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
@@ -5847,7 +5964,7 @@
         <v>44</v>
       </c>
       <c r="H14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
@@ -5862,7 +5979,7 @@
         <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1">
         <v>1263392347</v>
@@ -5877,7 +5994,7 @@
         <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
@@ -5907,7 +6024,7 @@
         <v>44</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5">
@@ -5937,7 +6054,7 @@
         <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
@@ -5967,7 +6084,7 @@
         <v>44</v>
       </c>
       <c r="H18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
@@ -5997,7 +6114,7 @@
         <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
@@ -6027,7 +6144,7 @@
         <v>44</v>
       </c>
       <c r="H20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5">
@@ -6057,7 +6174,7 @@
         <v>44</v>
       </c>
       <c r="H21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5">
@@ -6087,7 +6204,7 @@
         <v>44</v>
       </c>
       <c r="H22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5">
@@ -6117,7 +6234,7 @@
         <v>44</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5">
@@ -6144,10 +6261,10 @@
         <v>3866001108</v>
       </c>
       <c r="G24" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5">
@@ -6177,7 +6294,7 @@
         <v>44</v>
       </c>
       <c r="H25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5">
@@ -6204,10 +6321,10 @@
         <v>1318692011</v>
       </c>
       <c r="G26" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
@@ -6234,10 +6351,10 @@
         <v>1836404740</v>
       </c>
       <c r="G27" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
@@ -6267,7 +6384,7 @@
         <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5">
@@ -6297,7 +6414,7 @@
         <v>44</v>
       </c>
       <c r="H29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5">
@@ -6327,7 +6444,7 @@
         <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
@@ -6342,7 +6459,7 @@
         <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D31" s="1">
         <v>849045562</v>
@@ -6357,7 +6474,7 @@
         <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5">
@@ -6387,7 +6504,7 @@
         <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5">
@@ -6417,7 +6534,7 @@
         <v>44</v>
       </c>
       <c r="H33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -6445,7 +6562,7 @@
         <v>44</v>
       </c>
       <c r="H34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
@@ -6473,7 +6590,7 @@
         <v>44</v>
       </c>
       <c r="H35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -6486,7 +6603,7 @@
         <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D36" s="1">
         <v>1006698949</v>
@@ -6501,7 +6618,7 @@
         <v>44</v>
       </c>
       <c r="H36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5">
@@ -6531,7 +6648,7 @@
         <v>44</v>
       </c>
       <c r="H37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5">
@@ -6561,7 +6678,7 @@
         <v>44</v>
       </c>
       <c r="H38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5">
@@ -6576,7 +6693,7 @@
         <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D39" s="1">
         <v>806462703</v>
@@ -6591,7 +6708,7 @@
         <v>44</v>
       </c>
       <c r="H39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5">
@@ -6621,7 +6738,7 @@
         <v>44</v>
       </c>
       <c r="H40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5">
@@ -6651,7 +6768,7 @@
         <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5">
@@ -6666,7 +6783,7 @@
         <v>133</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D42" s="1">
         <v>441937598</v>
@@ -6681,7 +6798,7 @@
         <v>44</v>
       </c>
       <c r="H42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5">
@@ -6711,7 +6828,7 @@
         <v>44</v>
       </c>
       <c r="H43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5">
@@ -6726,7 +6843,7 @@
         <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D44" s="1">
         <v>558802476</v>
@@ -6741,7 +6858,7 @@
         <v>44</v>
       </c>
       <c r="H44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5">
@@ -6756,7 +6873,7 @@
         <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D45" s="1">
         <v>674765647</v>
@@ -6771,7 +6888,7 @@
         <v>44</v>
       </c>
       <c r="H45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5">
@@ -6801,7 +6918,7 @@
         <v>44</v>
       </c>
       <c r="H46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5">
@@ -6831,7 +6948,7 @@
         <v>44</v>
       </c>
       <c r="H47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5">
@@ -6861,7 +6978,7 @@
         <v>44</v>
       </c>
       <c r="H48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5">
@@ -6891,7 +7008,7 @@
         <v>44</v>
       </c>
       <c r="H49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5">
@@ -6921,7 +7038,7 @@
         <v>44</v>
       </c>
       <c r="H50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
@@ -6934,7 +7051,7 @@
         <v>142</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D51" s="1">
         <v>400000000</v>
@@ -6949,7 +7066,7 @@
         <v>44</v>
       </c>
       <c r="H51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -6977,7 +7094,7 @@
         <v>44</v>
       </c>
       <c r="H52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
@@ -7005,7 +7122,7 @@
         <v>44</v>
       </c>
       <c r="H53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
@@ -7033,7 +7150,7 @@
         <v>44</v>
       </c>
       <c r="H54" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
@@ -7061,7 +7178,7 @@
         <v>44</v>
       </c>
       <c r="H55" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
@@ -7089,7 +7206,7 @@
         <v>44</v>
       </c>
       <c r="H56" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
@@ -7117,7 +7234,7 @@
         <v>44</v>
       </c>
       <c r="H57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -7145,7 +7262,7 @@
         <v>44</v>
       </c>
       <c r="H58" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -7173,7 +7290,7 @@
         <v>44</v>
       </c>
       <c r="H59" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -7201,7 +7318,7 @@
         <v>44</v>
       </c>
       <c r="H60" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
@@ -7229,7 +7346,7 @@
         <v>44</v>
       </c>
       <c r="H61" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
@@ -7242,7 +7359,7 @@
         <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D62" s="1">
         <v>500000000</v>
@@ -7257,7 +7374,7 @@
         <v>44</v>
       </c>
       <c r="H62" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -7285,7 +7402,7 @@
         <v>44</v>
       </c>
       <c r="H63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
@@ -7313,7 +7430,7 @@
         <v>44</v>
       </c>
       <c r="H64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
@@ -7341,7 +7458,7 @@
         <v>44</v>
       </c>
       <c r="H65" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
@@ -7369,7 +7486,7 @@
         <v>44</v>
       </c>
       <c r="H66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5">
@@ -7396,10 +7513,10 @@
         <v>544159304</v>
       </c>
       <c r="G67" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H67" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5">
@@ -7414,7 +7531,7 @@
         <v>151</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D68" s="1">
         <v>400000000</v>
@@ -7429,7 +7546,7 @@
         <v>44</v>
       </c>
       <c r="H68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5">
@@ -7459,7 +7576,7 @@
         <v>44</v>
       </c>
       <c r="H69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5">
@@ -7489,7 +7606,7 @@
         <v>44</v>
       </c>
       <c r="H70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I70" s="5"/>
       <c r="J70" s="5">
@@ -7519,7 +7636,7 @@
         <v>44</v>
       </c>
       <c r="H71" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="5">
@@ -7549,7 +7666,7 @@
         <v>44</v>
       </c>
       <c r="H72" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5">
@@ -7579,7 +7696,7 @@
         <v>44</v>
       </c>
       <c r="H73" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5">
@@ -7609,7 +7726,7 @@
         <v>44</v>
       </c>
       <c r="H74" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I74" s="5"/>
       <c r="J74" s="5">
@@ -7639,7 +7756,7 @@
         <v>44</v>
       </c>
       <c r="H75" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I75" s="5"/>
       <c r="J75" s="5">
@@ -7654,7 +7771,7 @@
         <v>155</v>
       </c>
       <c r="C76" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D76" s="1">
         <v>400000000</v>
@@ -7669,7 +7786,7 @@
         <v>44</v>
       </c>
       <c r="H76" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I76" s="5"/>
       <c r="J76" s="5">
@@ -7699,7 +7816,7 @@
         <v>44</v>
       </c>
       <c r="H77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5">
@@ -7729,7 +7846,7 @@
         <v>44</v>
       </c>
       <c r="H78" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5">
@@ -7744,7 +7861,7 @@
         <v>159</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D79" s="1">
         <v>1003724736</v>
@@ -7759,7 +7876,7 @@
         <v>44</v>
       </c>
       <c r="H79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I79" s="5"/>
       <c r="J79" s="5">
@@ -7789,7 +7906,7 @@
         <v>44</v>
       </c>
       <c r="H80" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I80" s="5"/>
       <c r="J80" s="5">
@@ -7819,7 +7936,7 @@
         <v>44</v>
       </c>
       <c r="H81" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I81" s="5"/>
       <c r="J81" s="5">
@@ -7834,7 +7951,7 @@
         <v>161</v>
       </c>
       <c r="C82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D82" s="1">
         <v>181124998</v>
@@ -7849,7 +7966,7 @@
         <v>44</v>
       </c>
       <c r="H82" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
@@ -7874,10 +7991,10 @@
         <v>308345333</v>
       </c>
       <c r="G83" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H83" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I83" s="5"/>
       <c r="J83" s="5">
@@ -7892,7 +8009,7 @@
         <v>162</v>
       </c>
       <c r="C84" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D84" s="1">
         <v>456179013</v>
@@ -7904,10 +8021,10 @@
         <v>464380516</v>
       </c>
       <c r="G84" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H84" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I84" s="5"/>
       <c r="J84" s="5">
@@ -7934,10 +8051,10 @@
         <v>367521178</v>
       </c>
       <c r="G85" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H85" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I85" s="5"/>
       <c r="J85" s="5">
@@ -7964,10 +8081,10 @@
         <v>412290581</v>
       </c>
       <c r="G86" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H86" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I86" s="5"/>
       <c r="J86" s="5">
@@ -7997,7 +8114,7 @@
         <v>44</v>
       </c>
       <c r="H87" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I87" s="5"/>
       <c r="J87" s="5">
@@ -8027,7 +8144,7 @@
         <v>44</v>
       </c>
       <c r="H88" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I88" s="5"/>
       <c r="J88" s="5">
@@ -8057,7 +8174,7 @@
         <v>44</v>
       </c>
       <c r="H89" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I89" s="5"/>
       <c r="J89" s="5">
@@ -8087,7 +8204,7 @@
         <v>44</v>
       </c>
       <c r="H90" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I90" s="5"/>
       <c r="J90" s="5">
@@ -8117,7 +8234,7 @@
         <v>44</v>
       </c>
       <c r="H91" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I91" s="5"/>
       <c r="J91" s="5">
@@ -8147,7 +8264,7 @@
         <v>44</v>
       </c>
       <c r="H92" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
@@ -8172,10 +8289,10 @@
         <v>275639320</v>
       </c>
       <c r="G93" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H93" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
@@ -8188,7 +8305,7 @@
         <v>170</v>
       </c>
       <c r="C94" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D94" s="1">
         <v>440558255</v>
@@ -8200,10 +8317,10 @@
         <v>442701115</v>
       </c>
       <c r="G94" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
@@ -8228,10 +8345,10 @@
         <v>446332480</v>
       </c>
       <c r="G95" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="H95" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
@@ -8259,7 +8376,7 @@
         <v>44</v>
       </c>
       <c r="H96" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I96" s="5"/>
       <c r="J96" s="5">
@@ -8289,7 +8406,7 @@
         <v>44</v>
       </c>
       <c r="H97" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I97" s="5"/>
       <c r="J97" s="5">
@@ -8304,7 +8421,7 @@
         <v>127</v>
       </c>
       <c r="C98" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D98" s="1">
         <v>157982595</v>
@@ -8319,7 +8436,7 @@
         <v>44</v>
       </c>
       <c r="H98" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I98" s="5"/>
       <c r="J98" s="5">
@@ -8349,7 +8466,7 @@
         <v>44</v>
       </c>
       <c r="H99" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I99" s="5"/>
       <c r="J99" s="5">
@@ -8379,7 +8496,7 @@
         <v>44</v>
       </c>
       <c r="H100" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
@@ -8407,7 +8524,7 @@
         <v>44</v>
       </c>
       <c r="H101" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
@@ -8435,7 +8552,7 @@
         <v>44</v>
       </c>
       <c r="H102" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
@@ -8448,7 +8565,7 @@
         <v>172</v>
       </c>
       <c r="C103" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D103" s="1">
         <v>116977839</v>
@@ -8463,7 +8580,7 @@
         <v>44</v>
       </c>
       <c r="H103" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
@@ -8491,7 +8608,7 @@
         <v>44</v>
       </c>
       <c r="H104" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
@@ -8519,7 +8636,7 @@
         <v>44</v>
       </c>
       <c r="H105" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
@@ -8547,7 +8664,7 @@
         <v>44</v>
       </c>
       <c r="H106" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I106" s="5"/>
       <c r="J106" s="5">
@@ -8562,7 +8679,7 @@
         <v>139</v>
       </c>
       <c r="C107" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D107" s="1">
         <v>60000000</v>
@@ -8577,7 +8694,7 @@
         <v>44</v>
       </c>
       <c r="H107" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I107" s="5"/>
       <c r="J107" s="5">
@@ -8607,7 +8724,7 @@
         <v>44</v>
       </c>
       <c r="H108" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I108" s="5"/>
       <c r="J108" s="5">
@@ -8637,7 +8754,7 @@
         <v>44</v>
       </c>
       <c r="H109" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I109" s="5"/>
       <c r="J109" s="5">
@@ -8649,29 +8766,29 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="C110" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="D110" s="1">
-        <v>500000000</v>
+        <v>946084601</v>
       </c>
       <c r="E110" s="1">
-        <v>1165423958</v>
+        <v>1255172172</v>
       </c>
       <c r="F110" s="7">
-        <v>-188251002</v>
+        <v>86029794</v>
       </c>
       <c r="G110" t="s">
         <v>44</v>
       </c>
       <c r="H110" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I110" s="5"/>
       <c r="J110" s="5">
-        <v>1.2554</v>
+        <v>0.6374</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -8679,29 +8796,29 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="C111" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D111" s="1">
-        <v>500000000</v>
+        <v>274323144</v>
       </c>
       <c r="E111" s="1">
-        <v>1151125436</v>
+        <v>374599171</v>
       </c>
       <c r="F111" s="7">
-        <v>-183539197</v>
+        <v>-1221560</v>
       </c>
       <c r="G111" t="s">
         <v>44</v>
       </c>
       <c r="H111" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I111" s="5"/>
       <c r="J111" s="5">
-        <v>1.2554</v>
+        <v>0.36829999999999996</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -8709,29 +8826,29 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>68</v>
+        <v>175</v>
       </c>
       <c r="C112" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="D112" s="1">
-        <v>500000000</v>
+        <v>314964360</v>
       </c>
       <c r="E112" s="1">
-        <v>1148829895</v>
+        <v>337505230</v>
       </c>
       <c r="F112" s="7">
-        <v>-208539973</v>
+        <v>-2653247</v>
       </c>
       <c r="G112" t="s">
         <v>44</v>
       </c>
       <c r="H112" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I112" s="5"/>
       <c r="J112" s="5">
-        <v>1.2554</v>
+        <v>0.0633</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -8739,29 +8856,29 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>68</v>
+        <v>175</v>
       </c>
       <c r="C113" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="D113" s="1">
-        <v>500000000</v>
+        <v>1151650255</v>
       </c>
       <c r="E113" s="1">
-        <v>1186966069</v>
+        <v>1214682638</v>
       </c>
       <c r="F113" s="7">
-        <v>-204454782</v>
+        <v>-11725692</v>
       </c>
       <c r="G113" t="s">
         <v>44</v>
       </c>
       <c r="H113" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="I113" s="5"/>
       <c r="J113" s="5">
-        <v>1.2554</v>
+        <v>0.0633</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -8769,29 +8886,29 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C114" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D114" s="1">
-        <v>946084601</v>
+        <v>823846300</v>
       </c>
       <c r="E114" s="1">
-        <v>1255172172</v>
+        <v>997557132</v>
       </c>
       <c r="F114" s="7">
-        <v>86029794</v>
+        <v>-18297135</v>
       </c>
       <c r="G114" t="s">
         <v>44</v>
       </c>
       <c r="H114" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I114" s="5"/>
       <c r="J114" s="5">
-        <v>0.6374</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -8799,29 +8916,29 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C115" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D115" s="1">
-        <v>274323144</v>
+        <v>820369757</v>
       </c>
       <c r="E115" s="1">
-        <v>374599171</v>
+        <v>988168804</v>
       </c>
       <c r="F115" s="7">
-        <v>-1221560</v>
+        <v>-15019704</v>
       </c>
       <c r="G115" t="s">
         <v>44</v>
       </c>
       <c r="H115" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I115" s="5"/>
       <c r="J115" s="5">
-        <v>0.36829999999999996</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -8832,26 +8949,26 @@
         <v>176</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D116" s="1">
-        <v>314964360</v>
+        <v>822731626</v>
       </c>
       <c r="E116" s="1">
-        <v>337505230</v>
+        <v>993985391</v>
       </c>
       <c r="F116" s="7">
-        <v>-2653247</v>
+        <v>-17743111</v>
       </c>
       <c r="G116" t="s">
         <v>44</v>
       </c>
       <c r="H116" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I116" s="5"/>
       <c r="J116" s="5">
-        <v>0.0633</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -8859,29 +8976,29 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C117" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D117" s="1">
-        <v>1151650255</v>
+        <v>425389351</v>
       </c>
       <c r="E117" s="1">
-        <v>1214682638</v>
+        <v>475239009</v>
       </c>
       <c r="F117" s="7">
-        <v>-11725692</v>
+        <v>9432028</v>
       </c>
       <c r="G117" t="s">
         <v>44</v>
       </c>
       <c r="H117" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I117" s="5"/>
       <c r="J117" s="5">
-        <v>0.0633</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -8892,26 +9009,26 @@
         <v>177</v>
       </c>
       <c r="C118" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D118" s="1">
-        <v>823846300</v>
+        <v>508571279</v>
       </c>
       <c r="E118" s="1">
-        <v>997557132</v>
+        <v>578473784</v>
       </c>
       <c r="F118" s="7">
-        <v>-18297135</v>
+        <v>1973545</v>
       </c>
       <c r="G118" t="s">
         <v>44</v>
       </c>
       <c r="H118" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I118" s="5"/>
       <c r="J118" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -8922,26 +9039,26 @@
         <v>177</v>
       </c>
       <c r="C119" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D119" s="1">
-        <v>820369757</v>
+        <v>464478952</v>
       </c>
       <c r="E119" s="1">
-        <v>988168804</v>
+        <v>511250642</v>
       </c>
       <c r="F119" s="7">
-        <v>-15019704</v>
+        <v>-186646</v>
       </c>
       <c r="G119" t="s">
         <v>44</v>
       </c>
       <c r="H119" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I119" s="5"/>
       <c r="J119" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -8949,29 +9066,29 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C120" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D120" s="1">
-        <v>822731626</v>
+        <v>627191291</v>
       </c>
       <c r="E120" s="1">
-        <v>993985391</v>
+        <v>714504487</v>
       </c>
       <c r="F120" s="7">
-        <v>-17743111</v>
+        <v>18107712</v>
       </c>
       <c r="G120" t="s">
         <v>44</v>
       </c>
       <c r="H120" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I120" s="5"/>
       <c r="J120" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -8982,26 +9099,26 @@
         <v>178</v>
       </c>
       <c r="C121" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="D121" s="1">
-        <v>425389351</v>
+        <v>425091462</v>
       </c>
       <c r="E121" s="1">
-        <v>475239009</v>
+        <v>478192278</v>
       </c>
       <c r="F121" s="7">
-        <v>9432028</v>
+        <v>10642444</v>
       </c>
       <c r="G121" t="s">
         <v>44</v>
       </c>
       <c r="H121" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I121" s="5"/>
       <c r="J121" s="5">
-        <v>0.1247</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -9009,89 +9126,85 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C122" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D122" s="1">
-        <v>508571279</v>
+        <v>428950000</v>
       </c>
       <c r="E122" s="1">
-        <v>578473784</v>
+        <v>431428553</v>
       </c>
       <c r="F122" s="7">
-        <v>1973545</v>
+        <v>431428553</v>
       </c>
       <c r="G122" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H122" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I122" s="5"/>
-      <c r="J122" s="5">
-        <v>0.1247</v>
-      </c>
+      <c r="J122" s="5"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C123" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D123" s="1">
-        <v>464478952</v>
+        <v>462463907</v>
       </c>
       <c r="E123" s="1">
-        <v>511250642</v>
+        <v>466146222</v>
       </c>
       <c r="F123" s="7">
-        <v>-186646</v>
+        <v>466146222</v>
       </c>
       <c r="G123" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H123" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I123" s="5"/>
-      <c r="J123" s="5">
-        <v>0.1247</v>
-      </c>
+      <c r="J123" s="5"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="D124" s="1">
-        <v>627191291</v>
+        <v>151969815</v>
       </c>
       <c r="E124" s="1">
-        <v>714504487</v>
+        <v>266710574</v>
       </c>
       <c r="F124" s="7">
-        <v>18107712</v>
+        <v>-10002997</v>
       </c>
       <c r="G124" t="s">
         <v>44</v>
       </c>
       <c r="H124" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I124" s="5"/>
       <c r="J124" s="5">
-        <v>0.1307</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -9099,55 +9212,53 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="D125" s="1">
-        <v>425091462</v>
+        <v>105992843</v>
       </c>
       <c r="E125" s="1">
-        <v>478192278</v>
+        <v>129828838</v>
       </c>
       <c r="F125" s="7">
-        <v>10642444</v>
+        <v>127284</v>
       </c>
       <c r="G125" t="s">
         <v>44</v>
       </c>
       <c r="H125" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I125" s="5"/>
-      <c r="J125" s="5">
-        <v>0.1307</v>
-      </c>
+      <c r="J125" s="5"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="C126" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D126" s="1">
-        <v>428950000</v>
+        <v>258094745</v>
       </c>
       <c r="E126" s="1">
-        <v>431428553</v>
+        <v>333870078</v>
       </c>
       <c r="F126" s="7">
-        <v>431428553</v>
+        <v>649752</v>
       </c>
       <c r="G126" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="H126" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
@@ -9157,171 +9268,177 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="C127" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D127" s="1">
-        <v>462463907</v>
+        <v>299312934</v>
       </c>
       <c r="E127" s="1">
-        <v>466146222</v>
+        <v>373139760</v>
       </c>
       <c r="F127" s="7">
-        <v>466146222</v>
+        <v>61623</v>
       </c>
       <c r="G127" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="H127" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="C128" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D128" s="1">
-        <v>151969815</v>
+        <v>510820499</v>
       </c>
       <c r="E128" s="1">
-        <v>266710574</v>
+        <v>619202327</v>
       </c>
       <c r="F128" s="7">
-        <v>-10002997</v>
+        <v>-11343656</v>
       </c>
       <c r="G128" t="s">
         <v>44</v>
       </c>
       <c r="H128" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I128" s="5"/>
       <c r="J128" s="5">
-        <v>0.6866</v>
+        <v>0.21989999999999998</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="C129" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D129" s="1">
-        <v>105992843</v>
+        <v>508402028</v>
       </c>
       <c r="E129" s="1">
-        <v>129828838</v>
+        <v>612836264</v>
       </c>
       <c r="F129" s="7">
-        <v>127284</v>
+        <v>-9349078</v>
       </c>
       <c r="G129" t="s">
         <v>44</v>
       </c>
       <c r="H129" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I129" s="5"/>
-      <c r="J129" s="5"/>
+      <c r="J129" s="5">
+        <v>0.21989999999999998</v>
+      </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="C130" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D130" s="1">
-        <v>258094745</v>
+        <v>378735074</v>
       </c>
       <c r="E130" s="1">
-        <v>333870078</v>
+        <v>430909955</v>
       </c>
       <c r="F130" s="7">
-        <v>649752</v>
+        <v>10920693</v>
       </c>
       <c r="G130" t="s">
         <v>44</v>
       </c>
       <c r="H130" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I130" s="5"/>
-      <c r="J130" s="5"/>
+      <c r="J130" s="5">
+        <v>0.1307</v>
+      </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="C131" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D131" s="1">
-        <v>299312934</v>
+        <v>339081835</v>
       </c>
       <c r="E131" s="1">
-        <v>373139760</v>
+        <v>334549088</v>
       </c>
       <c r="F131" s="7">
-        <v>61623</v>
+        <v>334549088</v>
       </c>
       <c r="G131" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H131" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I131" s="5"/>
-      <c r="J131" s="5"/>
+      <c r="J131" s="5">
+        <v>-0.0173</v>
+      </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="C132" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="D132" s="1">
-        <v>510820499</v>
+        <v>151227051</v>
       </c>
       <c r="E132" s="1">
-        <v>619202327</v>
+        <v>265114862</v>
       </c>
       <c r="F132" s="7">
-        <v>-11343656</v>
+        <v>-9882162</v>
       </c>
       <c r="G132" t="s">
         <v>44</v>
       </c>
       <c r="H132" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I132" s="5"/>
       <c r="J132" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.6866</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -9329,29 +9446,29 @@
         <v>8</v>
       </c>
       <c r="B133" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="C133" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D133" s="1">
-        <v>508402028</v>
+        <v>159277445</v>
       </c>
       <c r="E133" s="1">
-        <v>612836264</v>
+        <v>304979599</v>
       </c>
       <c r="F133" s="7">
-        <v>-9349078</v>
+        <v>-1188805</v>
       </c>
       <c r="G133" t="s">
         <v>44</v>
       </c>
       <c r="H133" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I133" s="5"/>
       <c r="J133" s="5">
-        <v>0.21989999999999998</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -9359,29 +9476,29 @@
         <v>8</v>
       </c>
       <c r="B134" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="C134" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D134" s="1">
-        <v>378735074</v>
+        <v>159101214</v>
       </c>
       <c r="E134" s="1">
-        <v>430909955</v>
+        <v>311496128</v>
       </c>
       <c r="F134" s="7">
-        <v>10920693</v>
+        <v>-330845</v>
       </c>
       <c r="G134" t="s">
         <v>44</v>
       </c>
       <c r="H134" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I134" s="5"/>
       <c r="J134" s="5">
-        <v>0.1307</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -9389,29 +9506,29 @@
         <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="C135" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D135" s="1">
-        <v>339081835</v>
+        <v>159382615</v>
       </c>
       <c r="E135" s="1">
-        <v>334549088</v>
+        <v>311580226</v>
       </c>
       <c r="F135" s="7">
-        <v>334549088</v>
+        <v>-493569</v>
       </c>
       <c r="G135" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="H135" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I135" s="5"/>
       <c r="J135" s="5">
-        <v>-0.0173</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -9419,29 +9536,29 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C136" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D136" s="1">
-        <v>151227051</v>
+        <v>159708987</v>
       </c>
       <c r="E136" s="1">
-        <v>265114862</v>
+        <v>309819784</v>
       </c>
       <c r="F136" s="7">
-        <v>-9882162</v>
+        <v>-813461</v>
       </c>
       <c r="G136" t="s">
         <v>44</v>
       </c>
       <c r="H136" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I136" s="5"/>
       <c r="J136" s="5">
-        <v>0.6866</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -9449,145 +9566,137 @@
         <v>8</v>
       </c>
       <c r="B137" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C137" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="D137" s="1">
-        <v>159277445</v>
+        <v>106848757</v>
       </c>
       <c r="E137" s="1">
-        <v>304979599</v>
+        <v>130862848</v>
       </c>
       <c r="F137" s="7">
-        <v>-1188805</v>
+        <v>124527</v>
       </c>
       <c r="G137" t="s">
         <v>44</v>
       </c>
       <c r="H137" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I137" s="5"/>
-      <c r="J137" s="5">
-        <v>0.914</v>
-      </c>
+      <c r="J137" s="5"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C138" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D138" s="1">
-        <v>159101214</v>
+        <v>134102607</v>
       </c>
       <c r="E138" s="1">
-        <v>311496128</v>
+        <v>174702263</v>
       </c>
       <c r="F138" s="7">
-        <v>-330845</v>
+        <v>342198</v>
       </c>
       <c r="G138" t="s">
         <v>44</v>
       </c>
       <c r="H138" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I138" s="5"/>
-      <c r="J138" s="5">
-        <v>0.914</v>
-      </c>
+      <c r="J138" s="5"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>8</v>
       </c>
       <c r="B139" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C139" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="D139" s="1">
-        <v>159382615</v>
+        <v>257027478</v>
       </c>
       <c r="E139" s="1">
-        <v>311580226</v>
+        <v>319545179</v>
       </c>
       <c r="F139" s="7">
-        <v>-493569</v>
+        <v>142366</v>
       </c>
       <c r="G139" t="s">
         <v>44</v>
       </c>
       <c r="H139" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I139" s="5"/>
-      <c r="J139" s="5">
-        <v>0.914</v>
-      </c>
+      <c r="J139" s="5"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="C140" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D140" s="1">
-        <v>159708987</v>
+        <v>160873068</v>
       </c>
       <c r="E140" s="1">
-        <v>309819784</v>
+        <v>257650149</v>
       </c>
       <c r="F140" s="7">
-        <v>-813461</v>
+        <v>4148152</v>
       </c>
       <c r="G140" t="s">
         <v>44</v>
       </c>
       <c r="H140" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I140" s="5"/>
-      <c r="J140" s="5">
-        <v>0.914</v>
-      </c>
+      <c r="J140" s="5"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="C141" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D141" s="1">
-        <v>106848757</v>
+        <v>163472383</v>
       </c>
       <c r="E141" s="1">
-        <v>130862848</v>
+        <v>221410107</v>
       </c>
       <c r="F141" s="7">
-        <v>124527</v>
+        <v>1745193</v>
       </c>
       <c r="G141" t="s">
         <v>44</v>
       </c>
       <c r="H141" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
@@ -9597,25 +9706,25 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="C142" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D142" s="1">
-        <v>134102607</v>
+        <v>161120051</v>
       </c>
       <c r="E142" s="1">
-        <v>174702263</v>
+        <v>234838962</v>
       </c>
       <c r="F142" s="7">
-        <v>342198</v>
+        <v>1796960</v>
       </c>
       <c r="G142" t="s">
         <v>44</v>
       </c>
       <c r="H142" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
@@ -9625,25 +9734,25 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="C143" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="D143" s="1">
-        <v>257027478</v>
+        <v>149737366</v>
       </c>
       <c r="E143" s="1">
-        <v>319545179</v>
+        <v>220527203</v>
       </c>
       <c r="F143" s="7">
-        <v>142366</v>
+        <v>10349727</v>
       </c>
       <c r="G143" t="s">
         <v>44</v>
       </c>
       <c r="H143" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
@@ -9653,109 +9762,115 @@
         <v>8</v>
       </c>
       <c r="B144" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C144" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="D144" s="1">
-        <v>160873068</v>
+        <v>170770415</v>
       </c>
       <c r="E144" s="1">
-        <v>257650149</v>
+        <v>169160821</v>
       </c>
       <c r="F144" s="7">
-        <v>4148152</v>
+        <v>-2713085</v>
       </c>
       <c r="G144" t="s">
         <v>44</v>
       </c>
       <c r="H144" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I144" s="5"/>
-      <c r="J144" s="5"/>
+      <c r="J144" s="5">
+        <v>-0.0070999999999999995</v>
+      </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>8</v>
       </c>
       <c r="B145" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C145" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D145" s="1">
-        <v>163472383</v>
+        <v>92866928</v>
       </c>
       <c r="E145" s="1">
-        <v>221410107</v>
+        <v>92150680</v>
       </c>
       <c r="F145" s="7">
-        <v>1745193</v>
+        <v>-1474945</v>
       </c>
       <c r="G145" t="s">
         <v>44</v>
       </c>
       <c r="H145" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I145" s="5"/>
-      <c r="J145" s="5"/>
+      <c r="J145" s="5">
+        <v>-0.0070999999999999995</v>
+      </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>8</v>
       </c>
       <c r="B146" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C146" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D146" s="1">
-        <v>161120051</v>
+        <v>116515080</v>
       </c>
       <c r="E146" s="1">
-        <v>234838962</v>
+        <v>115478381</v>
       </c>
       <c r="F146" s="7">
-        <v>1796960</v>
+        <v>-1835166</v>
       </c>
       <c r="G146" t="s">
         <v>44</v>
       </c>
       <c r="H146" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I146" s="5"/>
-      <c r="J146" s="5"/>
+      <c r="J146" s="5">
+        <v>-0.0070999999999999995</v>
+      </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="C147" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="D147" s="1">
-        <v>149737366</v>
+        <v>60000000</v>
       </c>
       <c r="E147" s="1">
-        <v>220527203</v>
+        <v>76839686</v>
       </c>
       <c r="F147" s="7">
-        <v>10349727</v>
+        <v>-2121898</v>
       </c>
       <c r="G147" t="s">
         <v>44</v>
       </c>
       <c r="H147" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
@@ -9765,90 +9880,84 @@
         <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C148" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="D148" s="1">
-        <v>170770415</v>
+        <v>60000000</v>
       </c>
       <c r="E148" s="1">
-        <v>169160821</v>
+        <v>72935938</v>
       </c>
       <c r="F148" s="7">
-        <v>-2713085</v>
+        <v>-73692729</v>
       </c>
       <c r="G148" t="s">
         <v>44</v>
       </c>
       <c r="H148" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I148" s="5"/>
-      <c r="J148" s="5">
-        <v>-0.0070999999999999995</v>
-      </c>
+      <c r="J148" s="5"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>8</v>
       </c>
       <c r="B149" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C149" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D149" s="1">
-        <v>92866928</v>
+        <v>120000000</v>
       </c>
       <c r="E149" s="1">
-        <v>92150680</v>
+        <v>146792233</v>
       </c>
       <c r="F149" s="7">
-        <v>-1474945</v>
+        <v>163566</v>
       </c>
       <c r="G149" t="s">
         <v>44</v>
       </c>
       <c r="H149" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I149" s="5"/>
-      <c r="J149" s="5">
-        <v>-0.0070999999999999995</v>
-      </c>
+      <c r="J149" s="5"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>8</v>
       </c>
       <c r="B150" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C150" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="D150" s="1">
-        <v>116515080</v>
+        <v>100000000</v>
       </c>
       <c r="E150" s="1">
-        <v>115478381</v>
+        <v>133483168</v>
       </c>
       <c r="F150" s="7">
-        <v>-1835166</v>
+        <v>-25400</v>
       </c>
       <c r="G150" t="s">
         <v>44</v>
       </c>
       <c r="H150" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I150" s="5"/>
-      <c r="J150" s="5">
-        <v>-0.0070999999999999995</v>
-      </c>
+      <c r="J150" s="5"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
@@ -9858,22 +9967,22 @@
         <v>142</v>
       </c>
       <c r="C151" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D151" s="1">
         <v>60000000</v>
       </c>
       <c r="E151" s="1">
-        <v>76839686</v>
+        <v>75654265</v>
       </c>
       <c r="F151" s="7">
-        <v>-2121898</v>
+        <v>-485923</v>
       </c>
       <c r="G151" t="s">
         <v>44</v>
       </c>
       <c r="H151" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
@@ -9883,137 +9992,145 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C152" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="D152" s="1">
         <v>60000000</v>
       </c>
       <c r="E152" s="1">
-        <v>72935938</v>
+        <v>89122293</v>
       </c>
       <c r="F152" s="7">
-        <v>-73692729</v>
+        <v>-1236575</v>
       </c>
       <c r="G152" t="s">
         <v>44</v>
       </c>
       <c r="H152" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I152" s="5"/>
-      <c r="J152" s="5"/>
+      <c r="J152" s="5">
+        <v>0.7315</v>
+      </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C153" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D153" s="1">
-        <v>120000000</v>
+        <v>60000000</v>
       </c>
       <c r="E153" s="1">
-        <v>146792233</v>
+        <v>85570319</v>
       </c>
       <c r="F153" s="7">
-        <v>163566</v>
+        <v>-950764</v>
       </c>
       <c r="G153" t="s">
         <v>44</v>
       </c>
       <c r="H153" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I153" s="5"/>
-      <c r="J153" s="5"/>
+      <c r="J153" s="5">
+        <v>0.7315</v>
+      </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C154" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D154" s="1">
-        <v>100000000</v>
+        <v>60000000</v>
       </c>
       <c r="E154" s="1">
-        <v>133483168</v>
+        <v>87308547</v>
       </c>
       <c r="F154" s="7">
-        <v>-25400</v>
+        <v>-471520</v>
       </c>
       <c r="G154" t="s">
         <v>44</v>
       </c>
       <c r="H154" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I154" s="5"/>
-      <c r="J154" s="5"/>
+      <c r="J154" s="5">
+        <v>0.7315</v>
+      </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C155" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D155" s="1">
         <v>60000000</v>
       </c>
       <c r="E155" s="1">
-        <v>75654265</v>
+        <v>84636837</v>
       </c>
       <c r="F155" s="7">
-        <v>-485923</v>
+        <v>241555</v>
       </c>
       <c r="G155" t="s">
         <v>44</v>
       </c>
       <c r="H155" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I155" s="5"/>
-      <c r="J155" s="5"/>
+      <c r="J155" s="5">
+        <v>0.7315</v>
+      </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C156" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="D156" s="1">
         <v>60000000</v>
       </c>
       <c r="E156" s="1">
-        <v>89122293</v>
+        <v>88954199</v>
       </c>
       <c r="F156" s="7">
-        <v>-1236575</v>
+        <v>-817882</v>
       </c>
       <c r="G156" t="s">
         <v>44</v>
       </c>
       <c r="H156" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I156" s="5"/>
       <c r="J156" s="5">
@@ -10025,29 +10142,29 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="C157" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="D157" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E157" s="1">
-        <v>85570319</v>
+        <v>134048105</v>
       </c>
       <c r="F157" s="7">
-        <v>-950764</v>
+        <v>-178481</v>
       </c>
       <c r="G157" t="s">
         <v>44</v>
       </c>
       <c r="H157" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I157" s="5"/>
       <c r="J157" s="5">
-        <v>0.7315</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -10055,29 +10172,29 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="C158" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="D158" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E158" s="1">
-        <v>87308547</v>
+        <v>136597280</v>
       </c>
       <c r="F158" s="7">
-        <v>-471520</v>
+        <v>54421</v>
       </c>
       <c r="G158" t="s">
         <v>44</v>
       </c>
       <c r="H158" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I158" s="5"/>
       <c r="J158" s="5">
-        <v>0.7315</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -10085,29 +10202,29 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="C159" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="D159" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E159" s="1">
-        <v>84636837</v>
+        <v>137179366</v>
       </c>
       <c r="F159" s="7">
-        <v>241555</v>
+        <v>333074</v>
       </c>
       <c r="G159" t="s">
         <v>44</v>
       </c>
       <c r="H159" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I159" s="5"/>
       <c r="J159" s="5">
-        <v>0.7315</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -10115,150 +10232,142 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="C160" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D160" s="1">
-        <v>60000000</v>
+        <v>100000000</v>
       </c>
       <c r="E160" s="1">
-        <v>88954199</v>
+        <v>136973911</v>
       </c>
       <c r="F160" s="7">
-        <v>-817882</v>
+        <v>235488</v>
       </c>
       <c r="G160" t="s">
         <v>44</v>
       </c>
       <c r="H160" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I160" s="5"/>
       <c r="J160" s="5">
-        <v>0.7315</v>
+        <v>0.4351</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B161" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C161" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="D161" s="1">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="E161" s="1">
-        <v>134048105</v>
+        <v>0</v>
       </c>
       <c r="F161" s="7">
-        <v>-178481</v>
+        <v>-1683240295</v>
       </c>
       <c r="G161" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="H161" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I161" s="5"/>
-      <c r="J161" s="5">
-        <v>0.4351</v>
-      </c>
+      <c r="J161" s="5"/>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B162" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C162" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D162" s="1">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="E162" s="1">
-        <v>136597280</v>
+        <v>0</v>
       </c>
       <c r="F162" s="7">
-        <v>54421</v>
+        <v>-1687228552</v>
       </c>
       <c r="G162" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="H162" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I162" s="5"/>
-      <c r="J162" s="5">
-        <v>0.4351</v>
-      </c>
+      <c r="J162" s="5"/>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="C163" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="D163" s="1">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="E163" s="1">
-        <v>137179366</v>
+        <v>0</v>
       </c>
       <c r="F163" s="7">
-        <v>333074</v>
+        <v>-3924793719</v>
       </c>
       <c r="G163" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="H163" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I163" s="5"/>
-      <c r="J163" s="5">
-        <v>0.4351</v>
-      </c>
+      <c r="J163" s="5"/>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B164" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C164" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D164" s="1">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="E164" s="1">
-        <v>136973911</v>
+        <v>0</v>
       </c>
       <c r="F164" s="7">
-        <v>235488</v>
+        <v>-1314198402</v>
       </c>
       <c r="G164" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="H164" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I164" s="5"/>
-      <c r="J164" s="5">
-        <v>0.4351</v>
-      </c>
+      <c r="J164" s="5"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
@@ -10268,7 +10377,7 @@
         <v>182</v>
       </c>
       <c r="C165" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
@@ -10277,13 +10386,13 @@
         <v>0</v>
       </c>
       <c r="F165" s="7">
-        <v>-1683240295</v>
+        <v>-1837050463</v>
       </c>
       <c r="G165" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H165" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
@@ -10293,10 +10402,10 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C166" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -10305,13 +10414,13 @@
         <v>0</v>
       </c>
       <c r="F166" s="7">
-        <v>-1687228552</v>
+        <v>-1216881012</v>
       </c>
       <c r="G166" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H166" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
@@ -10321,10 +10430,10 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>119</v>
+        <v>183</v>
       </c>
       <c r="C167" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
@@ -10333,13 +10442,13 @@
         <v>0</v>
       </c>
       <c r="F167" s="7">
-        <v>-3924793719</v>
+        <v>-2051054273</v>
       </c>
       <c r="G167" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H167" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
@@ -10352,7 +10461,7 @@
         <v>183</v>
       </c>
       <c r="C168" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
@@ -10361,13 +10470,13 @@
         <v>0</v>
       </c>
       <c r="F168" s="7">
-        <v>-1314198402</v>
+        <v>-1508632702</v>
       </c>
       <c r="G168" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H168" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
@@ -10380,7 +10489,7 @@
         <v>183</v>
       </c>
       <c r="C169" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
@@ -10389,13 +10498,13 @@
         <v>0</v>
       </c>
       <c r="F169" s="7">
-        <v>-1837050463</v>
+        <v>-422609458</v>
       </c>
       <c r="G169" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H169" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
@@ -10405,10 +10514,10 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C170" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D170" s="1">
         <v>0</v>
@@ -10417,26 +10526,26 @@
         <v>0</v>
       </c>
       <c r="F170" s="7">
-        <v>-1216881012</v>
+        <v>-543970609</v>
       </c>
       <c r="G170" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H170" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C171" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
@@ -10445,26 +10554,26 @@
         <v>0</v>
       </c>
       <c r="F171" s="7">
-        <v>-2051054273</v>
+        <v>-303753501</v>
       </c>
       <c r="G171" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H171" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C172" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
@@ -10473,26 +10582,26 @@
         <v>0</v>
       </c>
       <c r="F172" s="7">
-        <v>-1508632702</v>
+        <v>-456179013</v>
       </c>
       <c r="G172" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H172" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C173" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
@@ -10501,26 +10610,26 @@
         <v>0</v>
       </c>
       <c r="F173" s="7">
-        <v>-422609458</v>
+        <v>-361201485</v>
       </c>
       <c r="G173" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H173" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="C174" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
@@ -10529,13 +10638,13 @@
         <v>0</v>
       </c>
       <c r="F174" s="7">
-        <v>-543970609</v>
+        <v>-405779245</v>
       </c>
       <c r="G174" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H174" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
@@ -10545,10 +10654,10 @@
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C175" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="D175" s="1">
         <v>0</v>
@@ -10557,13 +10666,13 @@
         <v>0</v>
       </c>
       <c r="F175" s="7">
-        <v>-303753501</v>
+        <v>-282822171</v>
       </c>
       <c r="G175" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H175" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
@@ -10573,10 +10682,10 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C176" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D176" s="1">
         <v>0</v>
@@ -10585,13 +10694,13 @@
         <v>0</v>
       </c>
       <c r="F176" s="7">
-        <v>-456179013</v>
+        <v>-746373228</v>
       </c>
       <c r="G176" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H176" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
@@ -10601,10 +10710,10 @@
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C177" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="D177" s="1">
         <v>0</v>
@@ -10613,13 +10722,13 @@
         <v>0</v>
       </c>
       <c r="F177" s="7">
-        <v>-361201485</v>
+        <v>-442398214</v>
       </c>
       <c r="G177" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H177" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
@@ -10629,10 +10738,10 @@
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C178" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="D178" s="1">
         <v>0</v>
@@ -10641,26 +10750,26 @@
         <v>0</v>
       </c>
       <c r="F178" s="7">
-        <v>-405779245</v>
+        <v>-216266708</v>
       </c>
       <c r="G178" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H178" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I178" s="5"/>
       <c r="J178" s="5"/>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B179" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="C179" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="D179" s="1">
         <v>0</v>
@@ -10669,26 +10778,26 @@
         <v>0</v>
       </c>
       <c r="F179" s="7">
-        <v>-282822171</v>
+        <v>-1353674960</v>
       </c>
       <c r="G179" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H179" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B180" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="C180" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="D180" s="1">
         <v>0</v>
@@ -10697,26 +10806,26 @@
         <v>0</v>
       </c>
       <c r="F180" s="7">
-        <v>-746373228</v>
+        <v>-1334664633</v>
       </c>
       <c r="G180" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H180" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B181" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="C181" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="D181" s="1">
         <v>0</v>
@@ -10725,26 +10834,26 @@
         <v>0</v>
       </c>
       <c r="F181" s="7">
-        <v>-442398214</v>
+        <v>-1357369868</v>
       </c>
       <c r="G181" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H181" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B182" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="C182" t="s">
-        <v>185</v>
+        <v>50</v>
       </c>
       <c r="D182" s="1">
         <v>0</v>
@@ -10753,13 +10862,13 @@
         <v>0</v>
       </c>
       <c r="F182" s="7">
-        <v>-216266708</v>
+        <v>-1391420851</v>
       </c>
       <c r="G182" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H182" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
@@ -10769,10 +10878,10 @@
         <v>7</v>
       </c>
       <c r="B183" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C183" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D183" s="1">
         <v>0</v>
@@ -10784,10 +10893,10 @@
         <v>-534717371</v>
       </c>
       <c r="G183" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H183" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
@@ -10797,7 +10906,7 @@
         <v>7</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C184" t="s">
         <v>128</v>
@@ -10812,10 +10921,10 @@
         <v>-461631869</v>
       </c>
       <c r="G184" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H184" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I184" s="5"/>
       <c r="J184" s="5"/>
@@ -10825,7 +10934,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C185" t="s">
         <v>118</v>
@@ -10840,10 +10949,10 @@
         <v>-333967279</v>
       </c>
       <c r="G185" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H185" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I185" s="5"/>
       <c r="J185" s="5"/>
@@ -10868,10 +10977,10 @@
         <v>-73420942</v>
       </c>
       <c r="G186" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>

--- a/downloads/勞動基金月度揭露_可持續更新.xlsx
+++ b/downloads/勞動基金月度揭露_可持續更新.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="185">
   <si>
     <t>勞動基金運用局｜四大基金月度儀表板</t>
   </si>
@@ -505,9 +505,6 @@
     <t>100-1全球基本面指數被動股票型(續約3)</t>
   </si>
   <si>
-    <t>瑞銀</t>
-  </si>
-  <si>
     <t>101-1全球低波動指數被動股票型(續約2)</t>
   </si>
   <si>
@@ -551,9 +548,6 @@
   </si>
   <si>
     <t>104-2全球不動產有價證券型(續約2)</t>
-  </si>
-  <si>
-    <t>信安環球</t>
   </si>
   <si>
     <t>111-1全球氣候變遷股票型</t>
@@ -8039,7 +8033,7 @@
         <v>162</v>
       </c>
       <c r="C85" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D85" s="1">
         <v>361201485</v>
@@ -8096,7 +8090,7 @@
         <v>6</v>
       </c>
       <c r="B87" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C87" t="s">
         <v>79</v>
@@ -8126,7 +8120,7 @@
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C88" t="s">
         <v>113</v>
@@ -8156,7 +8150,7 @@
         <v>6</v>
       </c>
       <c r="B89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C89" t="s">
         <v>114</v>
@@ -8186,7 +8180,7 @@
         <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C90" t="s">
         <v>115</v>
@@ -8216,10 +8210,10 @@
         <v>6</v>
       </c>
       <c r="B91" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" t="s">
         <v>166</v>
-      </c>
-      <c r="C91" t="s">
-        <v>167</v>
       </c>
       <c r="D91" s="1">
         <v>954418976</v>
@@ -8246,10 +8240,10 @@
         <v>6</v>
       </c>
       <c r="B92" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" t="s">
         <v>168</v>
-      </c>
-      <c r="C92" t="s">
-        <v>169</v>
       </c>
       <c r="D92" s="1">
         <v>708888643</v>
@@ -8274,10 +8268,10 @@
         <v>6</v>
       </c>
       <c r="B93" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" t="s">
         <v>170</v>
-      </c>
-      <c r="C93" t="s">
-        <v>171</v>
       </c>
       <c r="D93" s="1">
         <v>275923278</v>
@@ -8302,7 +8296,7 @@
         <v>6</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C94" t="s">
         <v>101</v>
@@ -8330,7 +8324,7 @@
         <v>6</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C95" t="s">
         <v>128</v>
@@ -8562,7 +8556,7 @@
         <v>6</v>
       </c>
       <c r="B103" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C103" t="s">
         <v>103</v>
@@ -8590,7 +8584,7 @@
         <v>6</v>
       </c>
       <c r="B104" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C104" t="s">
         <v>115</v>
@@ -8618,7 +8612,7 @@
         <v>6</v>
       </c>
       <c r="B105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C105" t="s">
         <v>134</v>
@@ -8766,7 +8760,7 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C110" t="s">
         <v>114</v>
@@ -8796,7 +8790,7 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C111" t="s">
         <v>97</v>
@@ -8826,7 +8820,7 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C112" t="s">
         <v>115</v>
@@ -8856,7 +8850,7 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C113" t="s">
         <v>99</v>
@@ -8886,7 +8880,7 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C114" t="s">
         <v>120</v>
@@ -8916,7 +8910,7 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C115" t="s">
         <v>121</v>
@@ -8946,7 +8940,7 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C116" t="s">
         <v>122</v>
@@ -8976,7 +8970,7 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C117" t="s">
         <v>135</v>
@@ -9006,7 +9000,7 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C118" t="s">
         <v>124</v>
@@ -9036,7 +9030,7 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C119" t="s">
         <v>125</v>
@@ -9066,7 +9060,7 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C120" t="s">
         <v>140</v>
@@ -9096,10 +9090,10 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C121" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D121" s="1">
         <v>425091462</v>
@@ -9126,7 +9120,7 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C122" t="s">
         <v>101</v>
@@ -9154,7 +9148,7 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C123" t="s">
         <v>128</v>
@@ -9296,7 +9290,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C128" t="s">
         <v>120</v>
@@ -9326,7 +9320,7 @@
         <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C129" t="s">
         <v>121</v>
@@ -9356,7 +9350,7 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C130" t="s">
         <v>140</v>
@@ -9386,7 +9380,7 @@
         <v>8</v>
       </c>
       <c r="B131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C131" t="s">
         <v>118</v>
@@ -9650,7 +9644,7 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C140" t="s">
         <v>103</v>
@@ -9678,7 +9672,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C141" t="s">
         <v>115</v>
@@ -9706,7 +9700,7 @@
         <v>8</v>
       </c>
       <c r="B142" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C142" t="s">
         <v>134</v>
@@ -9734,7 +9728,7 @@
         <v>8</v>
       </c>
       <c r="B143" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C143" t="s">
         <v>105</v>
@@ -9992,7 +9986,7 @@
         <v>8</v>
       </c>
       <c r="B152" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C152" t="s">
         <v>59</v>
@@ -10022,7 +10016,7 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C153" t="s">
         <v>121</v>
@@ -10052,7 +10046,7 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C154" t="s">
         <v>148</v>
@@ -10082,7 +10076,7 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C155" t="s">
         <v>144</v>
@@ -10112,7 +10106,7 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C156" t="s">
         <v>115</v>
@@ -10262,7 +10256,7 @@
         <v>5</v>
       </c>
       <c r="B161" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C161" t="s">
         <v>105</v>
@@ -10290,7 +10284,7 @@
         <v>5</v>
       </c>
       <c r="B162" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C162" t="s">
         <v>79</v>
@@ -10346,7 +10340,7 @@
         <v>5</v>
       </c>
       <c r="B164" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C164" t="s">
         <v>124</v>
@@ -10374,7 +10368,7 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C165" t="s">
         <v>125</v>
@@ -10402,10 +10396,10 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C166" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
@@ -10430,7 +10424,7 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C167" t="s">
         <v>101</v>
@@ -10458,7 +10452,7 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C168" t="s">
         <v>128</v>
@@ -10486,10 +10480,10 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C169" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
@@ -10542,7 +10536,7 @@
         <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C171" t="s">
         <v>79</v>
@@ -10570,7 +10564,7 @@
         <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C172" t="s">
         <v>105</v>
@@ -10598,10 +10592,10 @@
         <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C173" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
@@ -10626,7 +10620,7 @@
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C174" t="s">
         <v>135</v>
@@ -10654,10 +10648,10 @@
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C175" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D175" s="1">
         <v>0</v>
@@ -10682,7 +10676,7 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C176" t="s">
         <v>101</v>
@@ -10710,7 +10704,7 @@
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C177" t="s">
         <v>128</v>
@@ -10738,10 +10732,10 @@
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C178" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D178" s="1">
         <v>0</v>
@@ -10769,7 +10763,7 @@
         <v>68</v>
       </c>
       <c r="C179" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="D179" s="1">
         <v>0</v>
@@ -10825,7 +10819,7 @@
         <v>68</v>
       </c>
       <c r="C181" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="D181" s="1">
         <v>0</v>
@@ -10878,7 +10872,7 @@
         <v>7</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C183" t="s">
         <v>101</v>
@@ -10906,7 +10900,7 @@
         <v>7</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C184" t="s">
         <v>128</v>
@@ -10934,7 +10928,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C185" t="s">
         <v>118</v>
